--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Matriz 28 clases" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Ponentes - datos aval" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Vacantes por cubrir" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matriz 28 clases" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ponentes - datos aval" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vacantes por cubrir" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -168,7 +168,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -205,6 +205,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -232,7 +237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -343,6 +348,30 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -708,7 +737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="B2:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -717,7 +746,6 @@
     <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -746,7 +774,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -792,7 +819,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="B12" s="5" t="inlineStr">
         <is>
@@ -850,7 +876,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="B18" s="5" t="inlineStr">
         <is>
@@ -960,7 +985,6 @@
         <v/>
       </c>
     </row>
-    <row r="27"/>
     <row r="28" ht="40" customHeight="1">
       <c r="B28" s="18" t="inlineStr">
         <is>
@@ -1855,14 +1879,10 @@
           <t>Conceptos actuales; insuficiencia cardíaca; beneficios CV y renales de nuevas terapias</t>
         </is>
       </c>
-      <c r="E25" s="24" t="inlineStr">
-        <is>
-          <t>Dr. Harold (falta apellido)</t>
-        </is>
-      </c>
-      <c r="F25" s="30" t="inlineStr">
-        <is>
-          <t>DATO INCOMPLETO</t>
+      <c r="E25" s="28" t="n"/>
+      <c r="F25" s="29" t="inlineStr">
+        <is>
+          <t>VACANTE</t>
         </is>
       </c>
       <c r="G25" s="23" t="n">
@@ -1870,7 +1890,7 @@
       </c>
       <c r="H25" s="24" t="inlineStr">
         <is>
-          <t>CRÍTICO: en el PDF aparece solo como «Dr. Harold». Se necesita nombre completo.</t>
+          <t>SIN PONENTE. El Dr. Harold declinó (19/09/2026). Candidato natural: Dr. Chen Ku coordina el grupo de complicaciones cardio-reno-metabólicas de ALAD y ya está en M6·C2.</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2066,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="C32" s="31" t="inlineStr">
         <is>
@@ -2102,7 +2121,6 @@
         <v/>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="C38" s="34" t="inlineStr">
         <is>
@@ -2139,7 +2157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2316,13 +2334,21 @@
       <c r="A6" s="38" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="39" t="inlineStr">
-        <is>
-          <t>Dra. Jhoana Piedra</t>
-        </is>
-      </c>
-      <c r="C6" s="41" t="n"/>
-      <c r="D6" s="41" t="n"/>
+      <c r="B6" s="52" t="inlineStr">
+        <is>
+          <t>Dra. Johanna Piedra Bravo</t>
+        </is>
+      </c>
+      <c r="C6" s="53" t="inlineStr">
+        <is>
+          <t>Nutrición clínica · Magíster en Diabetes</t>
+        </is>
+      </c>
+      <c r="D6" s="53" t="inlineStr">
+        <is>
+          <t>Hospital del Río y Hospital Vicente Corral Moscoso · Cuenca, Ecuador</t>
+        </is>
+      </c>
       <c r="E6" s="41" t="n"/>
       <c r="F6" s="41" t="n"/>
       <c r="G6" s="41" t="n"/>
@@ -2332,7 +2358,11 @@
           <t>M2 · C2</t>
         </is>
       </c>
-      <c r="J6" s="42" t="n"/>
+      <c r="J6" s="54" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
       <c r="K6" s="42" t="n"/>
       <c r="L6" s="42" t="n"/>
       <c r="M6" s="42" t="n"/>
@@ -2382,7 +2412,11 @@
         </is>
       </c>
       <c r="C8" s="41" t="n"/>
-      <c r="D8" s="41" t="n"/>
+      <c r="D8" s="53" t="inlineStr">
+        <is>
+          <t>México (institución por confirmar)</t>
+        </is>
+      </c>
       <c r="E8" s="41" t="n"/>
       <c r="F8" s="41" t="n"/>
       <c r="G8" s="41" t="n"/>
@@ -2406,23 +2440,43 @@
       <c r="A9" s="38" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="39" t="inlineStr">
-        <is>
-          <t>Dra. Josefa Palacios</t>
-        </is>
-      </c>
-      <c r="C9" s="41" t="n"/>
-      <c r="D9" s="41" t="n"/>
+      <c r="B9" s="52" t="inlineStr">
+        <is>
+          <t>Dra. Josefa Elizabeth Palacio Riofrío</t>
+        </is>
+      </c>
+      <c r="C9" s="53" t="inlineStr">
+        <is>
+          <t>Endocrinología · Diabetes y Metabolismo</t>
+        </is>
+      </c>
+      <c r="D9" s="53" t="inlineStr">
+        <is>
+          <t>Omni Hospital e Interhospital · Guayaquil, Ecuador</t>
+        </is>
+      </c>
       <c r="E9" s="41" t="n"/>
-      <c r="F9" s="41" t="n"/>
-      <c r="G9" s="41" t="n"/>
+      <c r="F9" s="53" t="inlineStr">
+        <is>
+          <t>+593 96 816 1654</t>
+        </is>
+      </c>
+      <c r="G9" s="53" t="inlineStr">
+        <is>
+          <t>1103520233</t>
+        </is>
+      </c>
       <c r="H9" s="41" t="n"/>
       <c r="I9" s="40" t="inlineStr">
         <is>
           <t>M4 · C2</t>
         </is>
       </c>
-      <c r="J9" s="42" t="n"/>
+      <c r="J9" s="54" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
       <c r="K9" s="42" t="n"/>
       <c r="L9" s="42" t="n"/>
       <c r="M9" s="42" t="n"/>
@@ -2436,13 +2490,21 @@
       <c r="A10" s="38" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="39" t="inlineStr">
-        <is>
-          <t>Dr. Chih Hao Chen Ku</t>
-        </is>
-      </c>
-      <c r="C10" s="41" t="n"/>
-      <c r="D10" s="41" t="n"/>
+      <c r="B10" s="52" t="inlineStr">
+        <is>
+          <t>Dr. Chih Hao Chen Ku, M.Sc.</t>
+        </is>
+      </c>
+      <c r="C10" s="53" t="inlineStr">
+        <is>
+          <t>Endocrinología · Farmacología</t>
+        </is>
+      </c>
+      <c r="D10" s="53" t="inlineStr">
+        <is>
+          <t>Clínica Los Yoses · San José, Costa Rica</t>
+        </is>
+      </c>
       <c r="E10" s="41" t="n"/>
       <c r="F10" s="41" t="n"/>
       <c r="G10" s="41" t="n"/>
@@ -2452,7 +2514,11 @@
           <t>M6 · C2</t>
         </is>
       </c>
-      <c r="J10" s="42" t="n"/>
+      <c r="J10" s="54" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
       <c r="K10" s="42" t="n"/>
       <c r="L10" s="42" t="n"/>
       <c r="M10" s="42" t="n"/>
@@ -2496,15 +2562,31 @@
       <c r="A12" s="38" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="39" t="inlineStr">
-        <is>
-          <t>Dra. Lizbet Ruilova</t>
-        </is>
-      </c>
-      <c r="C12" s="41" t="n"/>
-      <c r="D12" s="41" t="n"/>
-      <c r="E12" s="41" t="n"/>
-      <c r="F12" s="41" t="n"/>
+      <c r="B12" s="52" t="inlineStr">
+        <is>
+          <t>Dra. Lizbet Yolanda Ruilova González</t>
+        </is>
+      </c>
+      <c r="C12" s="53" t="inlineStr">
+        <is>
+          <t>Endocrinología · Medicina Interna</t>
+        </is>
+      </c>
+      <c r="D12" s="53" t="inlineStr">
+        <is>
+          <t>SOLCA, Hospital Monte Sinaí y Universidad de Cuenca · Cuenca, Ecuador</t>
+        </is>
+      </c>
+      <c r="E12" s="53" t="inlineStr">
+        <is>
+          <t>lizrg@hotmail.com</t>
+        </is>
+      </c>
+      <c r="F12" s="53" t="inlineStr">
+        <is>
+          <t>+593 99 907 3471</t>
+        </is>
+      </c>
       <c r="G12" s="41" t="n"/>
       <c r="H12" s="41" t="n"/>
       <c r="I12" s="40" t="inlineStr">
@@ -2512,7 +2594,11 @@
           <t>M1 · C1  /  M5 · C4</t>
         </is>
       </c>
-      <c r="J12" s="42" t="n"/>
+      <c r="J12" s="54" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
       <c r="K12" s="42" t="n"/>
       <c r="L12" s="42" t="n"/>
       <c r="M12" s="42" t="n"/>
@@ -2673,118 +2759,40 @@
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="38" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="39" t="inlineStr">
-        <is>
-          <t>Dr. Harold  ← FALTA APELLIDO</t>
-        </is>
-      </c>
-      <c r="C18" s="41" t="n"/>
-      <c r="D18" s="41" t="n"/>
-      <c r="E18" s="41" t="n"/>
-      <c r="F18" s="41" t="n"/>
-      <c r="G18" s="41" t="n"/>
-      <c r="H18" s="41" t="n"/>
-      <c r="I18" s="40" t="inlineStr">
-        <is>
-          <t>M6 · C3</t>
-        </is>
-      </c>
-      <c r="J18" s="42" t="n"/>
-      <c r="K18" s="42" t="n"/>
-      <c r="L18" s="42" t="n"/>
-      <c r="M18" s="42" t="n"/>
-      <c r="N18" s="45" t="inlineStr">
-        <is>
-          <t>DATO INCOMPLETO</t>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
+      <c r="A18" s="54" t="n"/>
+      <c r="B18" s="52" t="n"/>
+      <c r="C18" s="53" t="n"/>
+      <c r="D18" s="53" t="n"/>
+      <c r="E18" s="53" t="n"/>
+      <c r="F18" s="53" t="n"/>
+      <c r="G18" s="53" t="n"/>
+      <c r="H18" s="53" t="n"/>
+      <c r="I18" s="53" t="n"/>
+      <c r="J18" s="54" t="n"/>
+      <c r="K18" s="54" t="n"/>
+      <c r="L18" s="54" t="n"/>
+      <c r="M18" s="54" t="n"/>
+      <c r="N18" s="55" t="n"/>
+    </row>
     <row r="20">
-      <c r="A20" s="46" t="inlineStr">
-        <is>
-          <t>EJ.</t>
-        </is>
-      </c>
-      <c r="B20" s="47" t="inlineStr">
-        <is>
-          <t>Dra. Nombre Apellido, MD, Especialista en Endocrinología</t>
-        </is>
-      </c>
-      <c r="C20" s="47" t="inlineStr">
-        <is>
-          <t>Endocrinología y Metabolismo</t>
-        </is>
-      </c>
-      <c r="D20" s="47" t="inlineStr">
-        <is>
-          <t>Hospital XXX · Cuenca, Ecuador</t>
-        </is>
-      </c>
-      <c r="E20" s="47" t="inlineStr">
-        <is>
-          <t>nombre.apellido@correo.com</t>
-        </is>
-      </c>
-      <c r="F20" s="47" t="inlineStr">
-        <is>
-          <t>+593 99 123 4567</t>
-        </is>
-      </c>
-      <c r="G20" s="47" t="inlineStr">
-        <is>
-          <t>0102030405</t>
-        </is>
-      </c>
-      <c r="H20" s="47" t="inlineStr">
-        <is>
-          <t>1005-2015-1234567</t>
-        </is>
-      </c>
-      <c r="I20" s="47" t="inlineStr">
-        <is>
-          <t>M2 · C3</t>
-        </is>
-      </c>
-      <c r="J20" s="47" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
-      <c r="K20" s="47" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
-      <c r="L20" s="47" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
-      <c r="M20" s="47" t="inlineStr">
-        <is>
-          <t>20/09/2026</t>
-        </is>
-      </c>
-      <c r="N20" s="47" t="inlineStr">
-        <is>
-          <t>CONFIRMADO</t>
-        </is>
-      </c>
+      <c r="A20" s="46" t="n"/>
+      <c r="B20" s="47" t="n"/>
+      <c r="C20" s="47" t="n"/>
+      <c r="D20" s="47" t="n"/>
+      <c r="E20" s="47" t="n"/>
+      <c r="F20" s="47" t="n"/>
+      <c r="G20" s="47" t="n"/>
+      <c r="H20" s="47" t="n"/>
+      <c r="I20" s="47" t="n"/>
+      <c r="J20" s="47" t="n"/>
+      <c r="K20" s="47" t="n"/>
+      <c r="L20" s="47" t="n"/>
+      <c r="M20" s="47" t="n"/>
+      <c r="N20" s="47" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="48" t="inlineStr">
-        <is>
-          <t>↑ Fila de EJEMPLO: muestra el formato esperado. No es una persona real. Borrarla antes de enviar el archivo a la Universidad.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
+      <c r="B21" s="48" t="n"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="J4:L18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -2801,7 +2809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3071,6 +3079,31 @@
       <c r="F12" s="41" t="n"/>
       <c r="G12" s="41" t="n"/>
     </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B13" s="57" t="inlineStr">
+        <is>
+          <t>M6 · C3</t>
+        </is>
+      </c>
+      <c r="C13" s="58" t="inlineStr">
+        <is>
+          <t>Síndrome cardiorrenometabólico</t>
+        </is>
+      </c>
+      <c r="D13" s="58" t="inlineStr">
+        <is>
+          <t>Endocrinología o cardiología — el Dr. Harold declinó el 19/09/2026</t>
+        </is>
+      </c>
+      <c r="E13" s="59" t="n"/>
+      <c r="F13" s="59" t="n"/>
+      <c r="G13" s="59" t="n"/>
+    </row>
     <row r="14">
       <c r="C14" s="51" t="inlineStr">
         <is>
@@ -3078,6 +3111,11 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -237,7 +237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -371,6 +371,9 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2350,7 +2353,11 @@
         </is>
       </c>
       <c r="E6" s="41" t="n"/>
-      <c r="F6" s="41" t="n"/>
+      <c r="F6" s="60" t="inlineStr">
+        <is>
+          <t>+593 98 765 4330</t>
+        </is>
+      </c>
       <c r="G6" s="41" t="n"/>
       <c r="H6" s="41" t="n"/>
       <c r="I6" s="40" t="inlineStr">
@@ -2582,7 +2589,7 @@
           <t>lizrg@hotmail.com</t>
         </is>
       </c>
-      <c r="F12" s="53" t="inlineStr">
+      <c r="F12" s="60" t="inlineStr">
         <is>
           <t>+593 99 907 3471</t>
         </is>
@@ -2809,7 +2816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3111,11 +3118,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -2513,7 +2513,11 @@
         </is>
       </c>
       <c r="E10" s="41" t="n"/>
-      <c r="F10" s="41" t="n"/>
+      <c r="F10" s="60" t="inlineStr">
+        <is>
+          <t>+506 8392 7083</t>
+        </is>
+      </c>
       <c r="G10" s="41" t="n"/>
       <c r="H10" s="41" t="n"/>
       <c r="I10" s="40" t="inlineStr">

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -2630,8 +2630,16 @@
       </c>
       <c r="C13" s="41" t="n"/>
       <c r="D13" s="41" t="n"/>
-      <c r="E13" s="41" t="n"/>
-      <c r="F13" s="41" t="n"/>
+      <c r="E13" s="60" t="inlineStr">
+        <is>
+          <t>pablo.vanegas90@gmail.com</t>
+        </is>
+      </c>
+      <c r="F13" s="60" t="inlineStr">
+        <is>
+          <t>+593 98 765 3136</t>
+        </is>
+      </c>
       <c r="G13" s="41" t="n"/>
       <c r="H13" s="41" t="n"/>
       <c r="I13" s="40" t="inlineStr">

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -167,6 +167,12 @@
       <color rgb="006B6B6B"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -237,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -373,6 +379,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2281,7 +2290,11 @@
       </c>
       <c r="D4" s="41" t="n"/>
       <c r="E4" s="41" t="n"/>
-      <c r="F4" s="41" t="n"/>
+      <c r="F4" s="61" t="inlineStr">
+        <is>
+          <t>⚠ VERIFICAR — el número recibido coincide con el de la Dra. Astudillo</t>
+        </is>
+      </c>
       <c r="G4" s="41" t="n"/>
       <c r="H4" s="41" t="n"/>
       <c r="I4" s="40" t="inlineStr">
@@ -2315,7 +2328,11 @@
       </c>
       <c r="D5" s="41" t="n"/>
       <c r="E5" s="41" t="n"/>
-      <c r="F5" s="41" t="n"/>
+      <c r="F5" s="60" t="inlineStr">
+        <is>
+          <t>+593 98 736 8816</t>
+        </is>
+      </c>
       <c r="G5" s="41" t="n"/>
       <c r="H5" s="41" t="n"/>
       <c r="I5" s="40" t="inlineStr">
@@ -2669,7 +2686,11 @@
       <c r="C14" s="41" t="n"/>
       <c r="D14" s="41" t="n"/>
       <c r="E14" s="41" t="n"/>
-      <c r="F14" s="41" t="n"/>
+      <c r="F14" s="60" t="inlineStr">
+        <is>
+          <t>+593 99 811 1635</t>
+        </is>
+      </c>
       <c r="G14" s="41" t="n"/>
       <c r="H14" s="41" t="n"/>
       <c r="I14" s="40" t="inlineStr">
@@ -2699,7 +2720,11 @@
       <c r="C15" s="41" t="n"/>
       <c r="D15" s="41" t="n"/>
       <c r="E15" s="41" t="n"/>
-      <c r="F15" s="41" t="n"/>
+      <c r="F15" s="60" t="inlineStr">
+        <is>
+          <t>+593 99 807 8964</t>
+        </is>
+      </c>
       <c r="G15" s="41" t="n"/>
       <c r="H15" s="41" t="n"/>
       <c r="I15" s="40" t="inlineStr">
@@ -2729,7 +2754,11 @@
       <c r="C16" s="41" t="n"/>
       <c r="D16" s="41" t="n"/>
       <c r="E16" s="41" t="n"/>
-      <c r="F16" s="41" t="n"/>
+      <c r="F16" s="60" t="inlineStr">
+        <is>
+          <t>+593 99 862 5711</t>
+        </is>
+      </c>
       <c r="G16" s="41" t="n"/>
       <c r="H16" s="41" t="n"/>
       <c r="I16" s="40" t="inlineStr">

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -2289,10 +2289,14 @@
         </is>
       </c>
       <c r="D4" s="41" t="n"/>
-      <c r="E4" s="41" t="n"/>
-      <c r="F4" s="61" t="inlineStr">
-        <is>
-          <t>⚠ VERIFICAR — el número recibido coincide con el de la Dra. Astudillo</t>
+      <c r="E4" s="60" t="inlineStr">
+        <is>
+          <t>info@draomidresperez.com</t>
+        </is>
+      </c>
+      <c r="F4" s="60" t="inlineStr">
+        <is>
+          <t>+593 98 206 2988</t>
         </is>
       </c>
       <c r="G4" s="41" t="n"/>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -2533,7 +2533,11 @@
           <t>Clínica Los Yoses · San José, Costa Rica</t>
         </is>
       </c>
-      <c r="E10" s="41" t="n"/>
+      <c r="E10" s="60" t="inlineStr">
+        <is>
+          <t>chenku2409@gmail.com</t>
+        </is>
+      </c>
       <c r="F10" s="60" t="inlineStr">
         <is>
           <t>+506 8392 7083</t>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -173,6 +173,10 @@
       <color rgb="009C0006"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -243,7 +247,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -382,6 +386,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2865,7 +2875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2993,9 +3003,17 @@
           <t>Nutricionista clínico o endocrinólogo; tema de alta demanda</t>
         </is>
       </c>
-      <c r="E6" s="41" t="n"/>
+      <c r="E6" s="62" t="inlineStr">
+        <is>
+          <t>Dra. Janeth Bermeo (propuesta)</t>
+        </is>
+      </c>
       <c r="F6" s="41" t="n"/>
-      <c r="G6" s="41" t="n"/>
+      <c r="G6" s="63" t="inlineStr">
+        <is>
+          <t>Endocrinóloga, Hospital del Río · contacto directo</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="50" t="n">
@@ -3016,9 +3034,17 @@
           <t>Endocrinólogo con experiencia en MCG/tecnología en diabetes</t>
         </is>
       </c>
-      <c r="E7" s="41" t="n"/>
+      <c r="E7" s="62" t="inlineStr">
+        <is>
+          <t>Dra. Janeth Bermeo (propuesta)</t>
+        </is>
+      </c>
       <c r="F7" s="41" t="n"/>
-      <c r="G7" s="41" t="n"/>
+      <c r="G7" s="63" t="inlineStr">
+        <is>
+          <t>Endocrinóloga, Hospital del Río · contacto directo</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="50" t="n">
@@ -3167,6 +3193,11 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -247,7 +247,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -393,6 +393,12 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1333,10 +1339,14 @@
           <t>Hambre fisiológica y emocional; conducta alimentaria; adherencia terapéutica</t>
         </is>
       </c>
-      <c r="E9" s="28" t="inlineStr"/>
-      <c r="F9" s="29" t="inlineStr">
-        <is>
-          <t>VACANTE</t>
+      <c r="E9" s="64" t="inlineStr">
+        <is>
+          <t>Dra. Janeth Bermeo</t>
+        </is>
+      </c>
+      <c r="F9" s="27" t="inlineStr">
+        <is>
+          <t>CONFIRMADO</t>
         </is>
       </c>
       <c r="G9" s="23" t="n">
@@ -1344,7 +1354,7 @@
       </c>
       <c r="H9" s="24" t="inlineStr">
         <is>
-          <t>SIN PONENTE. Perfil sugerido: nutricionista clínico o psicólogo de la conducta alimentaria.</t>
+          <t>Aceptó el 22/09/2026. Endocrinóloga del Hospital del Río. Pendiente: hoja de vida, cédula, foto y declaración COI.</t>
         </is>
       </c>
     </row>
@@ -2825,20 +2835,42 @@
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="54" t="n"/>
-      <c r="B18" s="52" t="n"/>
-      <c r="C18" s="53" t="n"/>
-      <c r="D18" s="53" t="n"/>
-      <c r="E18" s="53" t="n"/>
-      <c r="F18" s="53" t="n"/>
-      <c r="G18" s="53" t="n"/>
-      <c r="H18" s="53" t="n"/>
-      <c r="I18" s="53" t="n"/>
-      <c r="J18" s="54" t="n"/>
-      <c r="K18" s="54" t="n"/>
-      <c r="L18" s="54" t="n"/>
-      <c r="M18" s="54" t="n"/>
-      <c r="N18" s="55" t="n"/>
+      <c r="A18" s="54" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="52" t="inlineStr">
+        <is>
+          <t>Dra. Janeth Bermeo</t>
+        </is>
+      </c>
+      <c r="C18" s="53" t="inlineStr">
+        <is>
+          <t>Endocrinología</t>
+        </is>
+      </c>
+      <c r="D18" s="53" t="inlineStr">
+        <is>
+          <t>Hospital del Río · Cuenca, Ecuador</t>
+        </is>
+      </c>
+      <c r="E18" s="41" t="n"/>
+      <c r="F18" s="41" t="n"/>
+      <c r="G18" s="41" t="n"/>
+      <c r="H18" s="41" t="n"/>
+      <c r="I18" s="54" t="inlineStr">
+        <is>
+          <t>M2 · C3</t>
+        </is>
+      </c>
+      <c r="J18" s="42" t="n"/>
+      <c r="K18" s="42" t="n"/>
+      <c r="L18" s="42" t="n"/>
+      <c r="M18" s="42" t="n"/>
+      <c r="N18" s="65" t="inlineStr">
+        <is>
+          <t>CONFIRMADO</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="46" t="n"/>
@@ -3003,17 +3035,9 @@
           <t>Nutricionista clínico o endocrinólogo; tema de alta demanda</t>
         </is>
       </c>
-      <c r="E6" s="62" t="inlineStr">
-        <is>
-          <t>Dra. Janeth Bermeo (propuesta)</t>
-        </is>
-      </c>
+      <c r="E6" s="62" t="n"/>
       <c r="F6" s="41" t="n"/>
-      <c r="G6" s="63" t="inlineStr">
-        <is>
-          <t>Endocrinóloga, Hospital del Río · contacto directo</t>
-        </is>
-      </c>
+      <c r="G6" s="63" t="n"/>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="50" t="n">
@@ -3034,17 +3058,9 @@
           <t>Endocrinólogo con experiencia en MCG/tecnología en diabetes</t>
         </is>
       </c>
-      <c r="E7" s="62" t="inlineStr">
-        <is>
-          <t>Dra. Janeth Bermeo (propuesta)</t>
-        </is>
-      </c>
+      <c r="E7" s="62" t="n"/>
       <c r="F7" s="41" t="n"/>
-      <c r="G7" s="63" t="inlineStr">
-        <is>
-          <t>Endocrinóloga, Hospital del Río · contacto directo</t>
-        </is>
-      </c>
+      <c r="G7" s="63" t="n"/>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="50" t="n">
@@ -3116,27 +3132,13 @@
       <c r="G10" s="41" t="n"/>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="B11" s="39" t="inlineStr">
-        <is>
-          <t>M2 · C3</t>
-        </is>
-      </c>
-      <c r="C11" s="40" t="inlineStr">
-        <is>
-          <t>Nutrición conductual</t>
-        </is>
-      </c>
-      <c r="D11" s="40" t="inlineStr">
-        <is>
-          <t>Nutricionista clínico o psicólogo de la conducta alimentaria</t>
-        </is>
-      </c>
-      <c r="E11" s="41" t="n"/>
-      <c r="F11" s="41" t="n"/>
-      <c r="G11" s="41" t="n"/>
+      <c r="A11" s="55" t="n"/>
+      <c r="B11" s="52" t="n"/>
+      <c r="C11" s="53" t="n"/>
+      <c r="D11" s="53" t="n"/>
+      <c r="E11" s="53" t="n"/>
+      <c r="F11" s="53" t="n"/>
+      <c r="G11" s="53" t="n"/>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="50" t="n">

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -1911,10 +1911,14 @@
           <t>Conceptos actuales; insuficiencia cardíaca; beneficios CV y renales de nuevas terapias</t>
         </is>
       </c>
-      <c r="E25" s="28" t="n"/>
-      <c r="F25" s="29" t="inlineStr">
-        <is>
-          <t>VACANTE</t>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>Dr. Chih Hao Chen Ku</t>
+        </is>
+      </c>
+      <c r="F25" s="27" t="inlineStr">
+        <is>
+          <t>CONFIRMADO</t>
         </is>
       </c>
       <c r="G25" s="23" t="n">
@@ -1922,7 +1926,7 @@
       </c>
       <c r="H25" s="24" t="inlineStr">
         <is>
-          <t>SIN PONENTE. El Dr. Harold declinó (19/09/2026). Candidato natural: Dr. Chen Ku coordina el grupo de complicaciones cardio-reno-metabólicas de ALAD y ya está en M6·C2.</t>
+          <t>Aceptó el 22/09/2026 por correo, en reemplazo del Dr. Harold (declinó 19/09/2026). Segunda clase del mismo docente. Graba él y envía enlace del video. Faltan pasaporte y fotografía.</t>
         </is>
       </c>
     </row>
@@ -2567,7 +2571,7 @@
       <c r="H10" s="41" t="n"/>
       <c r="I10" s="40" t="inlineStr">
         <is>
-          <t>M6 · C2</t>
+          <t>M6 · C2  /  M6 · C3</t>
         </is>
       </c>
       <c r="J10" s="54" t="inlineStr">
@@ -2576,8 +2580,16 @@
         </is>
       </c>
       <c r="K10" s="42" t="n"/>
-      <c r="L10" s="42" t="n"/>
-      <c r="M10" s="42" t="n"/>
+      <c r="L10" s="42" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="M10" s="42" t="inlineStr">
+        <is>
+          <t>26/11/2026</t>
+        </is>
+      </c>
       <c r="N10" s="43" t="inlineStr">
         <is>
           <t>CONFIRMADO</t>
@@ -2907,7 +2919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3184,9 +3196,21 @@
           <t>Endocrinología o cardiología — el Dr. Harold declinó el 19/09/2026</t>
         </is>
       </c>
-      <c r="E13" s="59" t="n"/>
-      <c r="F13" s="59" t="n"/>
-      <c r="G13" s="59" t="n"/>
+      <c r="E13" s="59" t="inlineStr">
+        <is>
+          <t>Dr. Chih Hao Chen Ku</t>
+        </is>
+      </c>
+      <c r="F13" s="59" t="inlineStr">
+        <is>
+          <t>chenku2409@gmail.com · +506 8392 7083</t>
+        </is>
+      </c>
+      <c r="G13" s="59" t="inlineStr">
+        <is>
+          <t>CUBIERTA — aceptó el 22/09/2026</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="C14" s="51" t="inlineStr">
@@ -3195,11 +3219,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -2434,9 +2434,17 @@
         </is>
       </c>
       <c r="C7" s="41" t="n"/>
-      <c r="D7" s="41" t="n"/>
+      <c r="D7" s="41" t="inlineStr">
+        <is>
+          <t>Perú (institución y ciudad por confirmar)</t>
+        </is>
+      </c>
       <c r="E7" s="41" t="n"/>
-      <c r="F7" s="41" t="n"/>
+      <c r="F7" s="41" t="inlineStr">
+        <is>
+          <t>+51 936 260 715</t>
+        </is>
+      </c>
       <c r="G7" s="41" t="n"/>
       <c r="H7" s="41" t="n"/>
       <c r="I7" s="40" t="inlineStr">
@@ -2470,7 +2478,11 @@
         </is>
       </c>
       <c r="E8" s="41" t="n"/>
-      <c r="F8" s="41" t="n"/>
+      <c r="F8" s="41" t="inlineStr">
+        <is>
+          <t>+52 1 55 5405 6619</t>
+        </is>
+      </c>
       <c r="G8" s="41" t="n"/>
       <c r="H8" s="41" t="n"/>
       <c r="I8" s="40" t="inlineStr">
@@ -2606,9 +2618,17 @@
         </is>
       </c>
       <c r="C11" s="41" t="n"/>
-      <c r="D11" s="41" t="n"/>
+      <c r="D11" s="41" t="inlineStr">
+        <is>
+          <t>Argentina (institución y ciudad por confirmar)</t>
+        </is>
+      </c>
       <c r="E11" s="41" t="n"/>
-      <c r="F11" s="41" t="n"/>
+      <c r="F11" s="41" t="inlineStr">
+        <is>
+          <t>+54 9 11 6708-1708</t>
+        </is>
+      </c>
       <c r="G11" s="41" t="n"/>
       <c r="H11" s="41" t="n"/>
       <c r="I11" s="40" t="inlineStr">
@@ -2826,9 +2846,17 @@
         </is>
       </c>
       <c r="C17" s="41" t="n"/>
-      <c r="D17" s="41" t="n"/>
+      <c r="D17" s="41" t="inlineStr">
+        <is>
+          <t>Ecuador (institución y ciudad por confirmar)</t>
+        </is>
+      </c>
       <c r="E17" s="41" t="n"/>
-      <c r="F17" s="41" t="n"/>
+      <c r="F17" s="41" t="inlineStr">
+        <is>
+          <t>+593 98 335 5686</t>
+        </is>
+      </c>
       <c r="G17" s="41" t="n"/>
       <c r="H17" s="41" t="n"/>
       <c r="I17" s="40" t="inlineStr">

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -2894,7 +2894,11 @@
         </is>
       </c>
       <c r="E18" s="41" t="n"/>
-      <c r="F18" s="41" t="n"/>
+      <c r="F18" s="41" t="inlineStr">
+        <is>
+          <t>+593 96 198 1203</t>
+        </is>
+      </c>
       <c r="G18" s="41" t="n"/>
       <c r="H18" s="41" t="n"/>
       <c r="I18" s="54" t="inlineStr">

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -2087,10 +2087,14 @@
           <t>Programas híbridos (teleconsulta y telenutrición); protección de datos; interoperabilidad</t>
         </is>
       </c>
-      <c r="E30" s="28" t="inlineStr"/>
-      <c r="F30" s="29" t="inlineStr">
-        <is>
-          <t>VACANTE</t>
+      <c r="E30" s="24" t="inlineStr">
+        <is>
+          <t>Dra. Omidres Pérez de Carvelli</t>
+        </is>
+      </c>
+      <c r="F30" s="27" t="inlineStr">
+        <is>
+          <t>CONFIRMADO</t>
         </is>
       </c>
       <c r="G30" s="23" t="n">
@@ -2098,7 +2102,7 @@
       </c>
       <c r="H30" s="24" t="inlineStr">
         <is>
-          <t>SIN PONENTE. Perfil sugerido: bioética / derecho sanitario o protección de datos en salud.</t>
+          <t>Asumida por la Dra. Omidres el 23/09/2026. Segunda clase de la misma docente en el módulo 7. Entrega de la grabación: 3 de diciembre.</t>
         </is>
       </c>
     </row>
@@ -2327,13 +2331,17 @@
       <c r="H4" s="41" t="n"/>
       <c r="I4" s="40" t="inlineStr">
         <is>
-          <t>M7 · C1</t>
+          <t>M7 · C1  /  M7 · C4</t>
         </is>
       </c>
       <c r="J4" s="42" t="n"/>
       <c r="K4" s="42" t="n"/>
       <c r="L4" s="42" t="n"/>
-      <c r="M4" s="42" t="n"/>
+      <c r="M4" s="42" t="inlineStr">
+        <is>
+          <t>03/12/2026</t>
+        </is>
+      </c>
       <c r="N4" s="43" t="inlineStr">
         <is>
           <t>CONFIRMADO</t>
@@ -3148,9 +3156,21 @@
           <t>Bioética, derecho sanitario o protección de datos en salud</t>
         </is>
       </c>
-      <c r="E9" s="41" t="n"/>
-      <c r="F9" s="41" t="n"/>
-      <c r="G9" s="41" t="n"/>
+      <c r="E9" s="41" t="inlineStr">
+        <is>
+          <t>Dra. Omidres Pérez de Carvelli</t>
+        </is>
+      </c>
+      <c r="F9" s="41" t="inlineStr">
+        <is>
+          <t>info@draomidresperez.com</t>
+        </is>
+      </c>
+      <c r="G9" s="41" t="inlineStr">
+        <is>
+          <t>CUBIERTA — la asume la Dra. Omidres (23/09/2026)</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="50" t="n">

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -2713,7 +2713,11 @@
           <t>Dr. Pablo Vanegas</t>
         </is>
       </c>
-      <c r="C13" s="41" t="n"/>
+      <c r="C13" s="41" t="inlineStr">
+        <is>
+          <t>Endocrinología</t>
+        </is>
+      </c>
       <c r="D13" s="41" t="n"/>
       <c r="E13" s="60" t="inlineStr">
         <is>
@@ -2751,7 +2755,11 @@
           <t>Dra. María Augusta Astudillo</t>
         </is>
       </c>
-      <c r="C14" s="41" t="n"/>
+      <c r="C14" s="41" t="inlineStr">
+        <is>
+          <t>Endocrinología</t>
+        </is>
+      </c>
       <c r="D14" s="41" t="n"/>
       <c r="E14" s="41" t="n"/>
       <c r="F14" s="60" t="inlineStr">
@@ -2785,7 +2793,11 @@
           <t>Dra. Gabriela Jiménez</t>
         </is>
       </c>
-      <c r="C15" s="41" t="n"/>
+      <c r="C15" s="41" t="inlineStr">
+        <is>
+          <t>Endocrinología</t>
+        </is>
+      </c>
       <c r="D15" s="41" t="n"/>
       <c r="E15" s="41" t="n"/>
       <c r="F15" s="60" t="inlineStr">
@@ -2819,7 +2831,11 @@
           <t>Dr. Juan Molina</t>
         </is>
       </c>
-      <c r="C16" s="41" t="n"/>
+      <c r="C16" s="41" t="inlineStr">
+        <is>
+          <t>Endocrinología</t>
+        </is>
+      </c>
       <c r="D16" s="41" t="n"/>
       <c r="E16" s="41" t="n"/>
       <c r="F16" s="60" t="inlineStr">

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -2359,7 +2359,7 @@
       </c>
       <c r="C5" s="40" t="inlineStr">
         <is>
-          <t>Nutrición clínica</t>
+          <t>Nutriología</t>
         </is>
       </c>
       <c r="D5" s="41" t="n"/>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="C6" s="53" t="inlineStr">
         <is>
-          <t>Nutrición clínica · Magíster en Diabetes</t>
+          <t>Nutriología y Diabetología · Magíster en Diabetes</t>
         </is>
       </c>
       <c r="D6" s="53" t="inlineStr">

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -3080,9 +3080,17 @@
           <t>Nutricionista clínico con experiencia en diabetes</t>
         </is>
       </c>
-      <c r="E5" s="41" t="n"/>
+      <c r="E5" s="41" t="inlineStr">
+        <is>
+          <t>Gaby Villavicencio — nutrióloga</t>
+        </is>
+      </c>
       <c r="F5" s="41" t="n"/>
-      <c r="G5" s="41" t="n"/>
+      <c r="G5" s="41" t="inlineStr">
+        <is>
+          <t>INVITADO 23/09/2026 · esperando respuesta</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="50" t="n">
@@ -3207,9 +3215,17 @@
           <t>Cirujano bariátrico y metabólico acreditado</t>
         </is>
       </c>
-      <c r="E10" s="41" t="n"/>
+      <c r="E10" s="41" t="inlineStr">
+        <is>
+          <t>Dr. Verdugo — cirujano</t>
+        </is>
+      </c>
       <c r="F10" s="41" t="n"/>
-      <c r="G10" s="41" t="n"/>
+      <c r="G10" s="41" t="inlineStr">
+        <is>
+          <t>INVITADO 23/09/2026 · esperando respuesta</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="55" t="n"/>
@@ -3239,9 +3255,17 @@
           <t>Medicina del deporte, fisiatría o fisioterapia</t>
         </is>
       </c>
-      <c r="E12" s="41" t="n"/>
+      <c r="E12" s="41" t="inlineStr">
+        <is>
+          <t>Dr. César Dommar — fisioterapeuta</t>
+        </is>
+      </c>
       <c r="F12" s="41" t="n"/>
-      <c r="G12" s="41" t="n"/>
+      <c r="G12" s="41" t="inlineStr">
+        <is>
+          <t>INVITADO 23/09/2026 · esperando respuesta</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="32" customHeight="1">
       <c r="A13" s="56" t="inlineStr">

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -3057,9 +3057,17 @@
           <t>Nutricionista clínico o endocrinólogo con línea en nutrición de precisión</t>
         </is>
       </c>
-      <c r="E4" s="41" t="n"/>
+      <c r="E4" s="41" t="inlineStr">
+        <is>
+          <t>Lcda. Daniela Vintimilla — Directora de la Carrera de Nutrición, Universidad de Cuenca</t>
+        </is>
+      </c>
       <c r="F4" s="41" t="n"/>
-      <c r="G4" s="41" t="n"/>
+      <c r="G4" s="41" t="inlineStr">
+        <is>
+          <t>INVITADA 23/09/2026 (registro formal) · esperando respuesta</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="50" t="n">

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -973,7 +973,7 @@
       </c>
       <c r="C23" s="16" t="n"/>
       <c r="D23" s="17">
-        <f>COUNTA('Ponentes - datos aval'!B4:B18)</f>
+        <f>COUNTA('Ponentes - datos aval'!B4:B20)</f>
         <v/>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" s="16" t="n"/>
       <c r="D24" s="17">
-        <f>COUNTIF('Ponentes - datos aval'!J4:J18,"SÍ")</f>
+        <f>COUNTIF('Ponentes - datos aval'!J4:J20,"SÍ")</f>
         <v/>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="C25" s="16" t="n"/>
       <c r="D25" s="17">
-        <f>COUNTA('Ponentes - datos aval'!F4:F18)</f>
+        <f>COUNTA('Ponentes - datos aval'!F4:F20)</f>
         <v/>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="C26" s="16" t="n"/>
       <c r="D26" s="17">
-        <f>COUNTIF('Ponentes - datos aval'!L4:L18,"SÍ")</f>
+        <f>COUNTIF('Ponentes - datos aval'!L4:L20,"SÍ")</f>
         <v/>
       </c>
     </row>
@@ -2482,7 +2482,7 @@
       <c r="C8" s="41" t="n"/>
       <c r="D8" s="53" t="inlineStr">
         <is>
-          <t>México (institución por confirmar)</t>
+          <t>México (institución y ciudad por confirmar)</t>
         </is>
       </c>
       <c r="E8" s="41" t="n"/>
@@ -2940,21 +2940,73 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="54" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="52" t="inlineStr">
+        <is>
+          <t>Dra. María Paz Castillo</t>
+        </is>
+      </c>
+      <c r="C19" s="53" t="inlineStr">
+        <is>
+          <t>Endocrinología</t>
+        </is>
+      </c>
+      <c r="D19" s="53" t="n"/>
+      <c r="E19" s="41" t="n"/>
+      <c r="F19" s="41" t="n"/>
+      <c r="G19" s="41" t="n"/>
+      <c r="H19" s="41" t="n"/>
+      <c r="I19" s="54" t="inlineStr">
+        <is>
+          <t>POR ASIGNAR</t>
+        </is>
+      </c>
+      <c r="J19" s="42" t="n"/>
+      <c r="K19" s="42" t="n"/>
+      <c r="L19" s="42" t="n"/>
+      <c r="M19" s="42" t="n"/>
+      <c r="N19" s="65" t="inlineStr">
+        <is>
+          <t>ACEPTÓ — falta tema y datos de contacto</t>
+        </is>
+      </c>
+    </row>
     <row r="20">
-      <c r="A20" s="46" t="n"/>
-      <c r="B20" s="47" t="n"/>
-      <c r="C20" s="47" t="n"/>
-      <c r="D20" s="47" t="n"/>
-      <c r="E20" s="47" t="n"/>
-      <c r="F20" s="47" t="n"/>
-      <c r="G20" s="47" t="n"/>
-      <c r="H20" s="47" t="n"/>
-      <c r="I20" s="47" t="n"/>
-      <c r="J20" s="47" t="n"/>
-      <c r="K20" s="47" t="n"/>
-      <c r="L20" s="47" t="n"/>
-      <c r="M20" s="47" t="n"/>
-      <c r="N20" s="47" t="n"/>
+      <c r="A20" s="54" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="52" t="inlineStr">
+        <is>
+          <t>Dr. Cristian Castillo</t>
+        </is>
+      </c>
+      <c r="C20" s="53" t="inlineStr">
+        <is>
+          <t>Cirugía bariátrica y metabólica</t>
+        </is>
+      </c>
+      <c r="D20" s="53" t="n"/>
+      <c r="E20" s="41" t="n"/>
+      <c r="F20" s="41" t="n"/>
+      <c r="G20" s="41" t="n"/>
+      <c r="H20" s="41" t="n"/>
+      <c r="I20" s="54" t="inlineStr">
+        <is>
+          <t>M3 · C4 (en conflicto con el Dr. Verdugo)</t>
+        </is>
+      </c>
+      <c r="J20" s="42" t="n"/>
+      <c r="K20" s="42" t="n"/>
+      <c r="L20" s="42" t="n"/>
+      <c r="M20" s="42" t="n"/>
+      <c r="N20" s="65" t="inlineStr">
+        <is>
+          <t>ACEPTÓ — falta resolver duplicidad y datos de contacto</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="B21" s="48" t="n"/>
@@ -3225,13 +3277,13 @@
       </c>
       <c r="E10" s="41" t="inlineStr">
         <is>
-          <t>Dr. Verdugo — cirujano</t>
+          <t>CONFLICTO: Dr. Verdugo (invitado por Omidres) y Dr. Cristian Castillo (aceptó vía Lizbeth)</t>
         </is>
       </c>
       <c r="F10" s="41" t="n"/>
       <c r="G10" s="41" t="inlineStr">
         <is>
-          <t>INVITADO 23/09/2026 · esperando respuesta</t>
+          <t>DOS CANDIDATOS PARA UNA CLASE · resolver antes de pedirles documentos</t>
         </is>
       </c>
     </row>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -973,7 +973,7 @@
       </c>
       <c r="C23" s="16" t="n"/>
       <c r="D23" s="17">
-        <f>COUNTA('Ponentes - datos aval'!B4:B20)</f>
+        <f>COUNTA('Ponentes - datos aval'!B4:B21)</f>
         <v/>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" s="16" t="n"/>
       <c r="D24" s="17">
-        <f>COUNTIF('Ponentes - datos aval'!J4:J20,"SÍ")</f>
+        <f>COUNTIF('Ponentes - datos aval'!J4:J21,"SÍ")</f>
         <v/>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="C25" s="16" t="n"/>
       <c r="D25" s="17">
-        <f>COUNTA('Ponentes - datos aval'!F4:F20)</f>
+        <f>COUNTA('Ponentes - datos aval'!F4:F21)</f>
         <v/>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="C26" s="16" t="n"/>
       <c r="D26" s="17">
-        <f>COUNTIF('Ponentes - datos aval'!L4:L20,"SÍ")</f>
+        <f>COUNTIF('Ponentes - datos aval'!L4:L21,"SÍ")</f>
         <v/>
       </c>
     </row>
@@ -1375,10 +1375,14 @@
           <t>Ejercicio aeróbico; entrenamiento de fuerza; prescripción de ejercicio</t>
         </is>
       </c>
-      <c r="E10" s="28" t="inlineStr"/>
-      <c r="F10" s="29" t="inlineStr">
-        <is>
-          <t>VACANTE</t>
+      <c r="E10" s="64" t="inlineStr">
+        <is>
+          <t>Dra. Julia Castro</t>
+        </is>
+      </c>
+      <c r="F10" s="27" t="inlineStr">
+        <is>
+          <t>CONFIRMADO</t>
         </is>
       </c>
       <c r="G10" s="23" t="n">
@@ -1386,7 +1390,7 @@
       </c>
       <c r="H10" s="24" t="inlineStr">
         <is>
-          <t>SIN PONENTE. Perfil sugerido: medicina del deporte o fisiatría / fisioterapia.</t>
+          <t>Aceptó el 24/09/2026. El Dr. César Dommar, invitado el 23/09, declinó. Faltan especialidad, datos de contacto y toda la documentación del aval. Entrega de la grabación: 29 de octubre, la fecha más apretada del curso.</t>
         </is>
       </c>
     </row>
@@ -1519,10 +1523,14 @@
           <t>Indicaciones; técnicas quirúrgicas; seguimiento metabólico</t>
         </is>
       </c>
-      <c r="E14" s="28" t="inlineStr"/>
-      <c r="F14" s="29" t="inlineStr">
-        <is>
-          <t>VACANTE</t>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>Dr. Cristian Castillo</t>
+        </is>
+      </c>
+      <c r="F14" s="27" t="inlineStr">
+        <is>
+          <t>CONFIRMADO</t>
         </is>
       </c>
       <c r="G14" s="23" t="n">
@@ -1530,7 +1538,7 @@
       </c>
       <c r="H14" s="24" t="inlineStr">
         <is>
-          <t>SIN PONENTE. Perfil sugerido: cirujano bariátrico/metabólico acreditado.</t>
+          <t>Aceptó vía Dra. Lizbet Ruilova (24/09/2026). El Dr. Verdugo, invitado el 23/09, no respondió. Faltan datos de contacto y documentación del aval.</t>
         </is>
       </c>
     </row>
@@ -2995,7 +3003,7 @@
       <c r="H20" s="41" t="n"/>
       <c r="I20" s="54" t="inlineStr">
         <is>
-          <t>M3 · C4 (en conflicto con el Dr. Verdugo)</t>
+          <t>M3 · C4</t>
         </is>
       </c>
       <c r="J20" s="42" t="n"/>
@@ -3004,12 +3012,39 @@
       <c r="M20" s="42" t="n"/>
       <c r="N20" s="65" t="inlineStr">
         <is>
-          <t>ACEPTÓ — falta resolver duplicidad y datos de contacto</t>
+          <t>CONFIRMADO — faltan datos de contacto y documentación</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="48" t="n"/>
+      <c r="A21" s="54" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="52" t="inlineStr">
+        <is>
+          <t>Dra. Julia Castro</t>
+        </is>
+      </c>
+      <c r="C21" s="53" t="n"/>
+      <c r="D21" s="53" t="n"/>
+      <c r="E21" s="41" t="n"/>
+      <c r="F21" s="41" t="n"/>
+      <c r="G21" s="41" t="n"/>
+      <c r="H21" s="41" t="n"/>
+      <c r="I21" s="54" t="inlineStr">
+        <is>
+          <t>M2 · C4</t>
+        </is>
+      </c>
+      <c r="J21" s="42" t="n"/>
+      <c r="K21" s="42" t="n"/>
+      <c r="L21" s="42" t="n"/>
+      <c r="M21" s="42" t="n"/>
+      <c r="N21" s="65" t="inlineStr">
+        <is>
+          <t>CONFIRMADO — faltan especialidad, contacto y documentación</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -3277,13 +3312,13 @@
       </c>
       <c r="E10" s="41" t="inlineStr">
         <is>
-          <t>CONFLICTO: Dr. Verdugo (invitado por Omidres) y Dr. Cristian Castillo (aceptó vía Lizbeth)</t>
+          <t>Dr. Cristian Castillo</t>
         </is>
       </c>
       <c r="F10" s="41" t="n"/>
       <c r="G10" s="41" t="inlineStr">
         <is>
-          <t>DOS CANDIDATOS PARA UNA CLASE · resolver antes de pedirles documentos</t>
+          <t>CUBIERTA — aceptó el 24/09/2026 (el Dr. Verdugo no respondió)</t>
         </is>
       </c>
     </row>
@@ -3317,13 +3352,13 @@
       </c>
       <c r="E12" s="41" t="inlineStr">
         <is>
-          <t>Dr. César Dommar — fisioterapeuta</t>
+          <t>Dra. Julia Castro</t>
         </is>
       </c>
       <c r="F12" s="41" t="n"/>
       <c r="G12" s="41" t="inlineStr">
         <is>
-          <t>INVITADO 23/09/2026 · esperando respuesta</t>
+          <t>CUBIERTA — aceptó el 24/09/2026 (el Dr. Dommar declinó)</t>
         </is>
       </c>
     </row>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -3146,13 +3146,13 @@
       </c>
       <c r="E4" s="41" t="inlineStr">
         <is>
-          <t>Lcda. Daniela Vintimilla — Directora de la Carrera de Nutrición, Universidad de Cuenca</t>
+          <t>Lcda. Gabriela Molina — propuesta por la Lcda. Daniela Vintimilla</t>
         </is>
       </c>
       <c r="F4" s="41" t="n"/>
       <c r="G4" s="41" t="inlineStr">
         <is>
-          <t>INVITADA 23/09/2026 (registro formal) · esperando respuesta</t>
+          <t>La Lcda. Vintimilla declinó el 24/09 («no suelo dar conferencias») y propuso a la Lcda. Gabriela Molina, con experiencia en el tema. Falta contactarla. La Carrera de Nutrición de la U. Cuenca ofrece más docentes: pidió la lista de temas.</t>
         </is>
       </c>
     </row>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -2912,12 +2912,12 @@
       </c>
       <c r="B18" s="52" t="inlineStr">
         <is>
-          <t>Dra. Janeth Bermeo</t>
+          <t>Dra. Janneth Bermeo Cabrera</t>
         </is>
       </c>
       <c r="C18" s="53" t="inlineStr">
         <is>
-          <t>Endocrinología</t>
+          <t>Medicina Interna · Subespecialista en Endocrinología · Alta especialidad en Obesidad y Enfermedades Tiroideas (UNAM)</t>
         </is>
       </c>
       <c r="D18" s="53" t="inlineStr">
@@ -2925,7 +2925,11 @@
           <t>Hospital del Río · Cuenca, Ecuador</t>
         </is>
       </c>
-      <c r="E18" s="41" t="n"/>
+      <c r="E18" s="41" t="inlineStr">
+        <is>
+          <t>jbendocrino@hotmail.com</t>
+        </is>
+      </c>
       <c r="F18" s="41" t="inlineStr">
         <is>
           <t>+593 96 198 1203</t>
@@ -2938,13 +2942,17 @@
           <t>M2 · C3</t>
         </is>
       </c>
-      <c r="J18" s="42" t="n"/>
+      <c r="J18" s="42" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
       <c r="K18" s="42" t="n"/>
       <c r="L18" s="42" t="n"/>
       <c r="M18" s="42" t="n"/>
       <c r="N18" s="65" t="inlineStr">
         <is>
-          <t>CONFIRMADO</t>
+          <t>CONFIRMADO — declaración COI llena, pendiente de firma electrónica</t>
         </is>
       </c>
     </row>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -1305,7 +1305,7 @@
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
-          <t>Dra. Jhoana Piedra</t>
+          <t>Dra. Johanna Piedra Bravo</t>
         </is>
       </c>
       <c r="F8" s="27" t="inlineStr">

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -1227,14 +1227,10 @@
           <t>IMC y sus limitaciones; circunferencia abdominal; bioimpedancia; obesidad sarcopénica</t>
         </is>
       </c>
-      <c r="E6" s="24" t="inlineStr">
-        <is>
-          <t>Dra. Gabriela Jiménez</t>
-        </is>
-      </c>
-      <c r="F6" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
+      <c r="E6" s="64" t="n"/>
+      <c r="F6" s="27" t="inlineStr">
+        <is>
+          <t>VACANTE</t>
         </is>
       </c>
       <c r="G6" s="23" t="n">
@@ -1242,7 +1238,7 @@
       </c>
       <c r="H6" s="24" t="inlineStr">
         <is>
-          <t>Pedir aceptación formal, datos de contacto y hoja de vida.</t>
+          <t>La Dra. Gabriela Jiménez declinó el tema (25/09/2026, vía Lizbet Ruilova): «no quiere sarcopenia». Candidata: Dra. Adriana González, tesorera de ALAD, propuesta por la Dra. Adriana Alvarez — ya tiene preparada una charla de sarcopenia que dictó en Curitiba.</t>
         </is>
       </c>
     </row>
@@ -1563,14 +1559,10 @@
           <t>Defectos fisiopatológicos de la DM2; clasificación actual; diagnóstico temprano</t>
         </is>
       </c>
-      <c r="E15" s="24" t="inlineStr">
-        <is>
-          <t>Dra. María Augusta Astudillo</t>
-        </is>
-      </c>
-      <c r="F15" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
+      <c r="E15" s="64" t="n"/>
+      <c r="F15" s="27" t="inlineStr">
+        <is>
+          <t>VACANTE</t>
         </is>
       </c>
       <c r="G15" s="23" t="n">
@@ -1578,7 +1570,7 @@
       </c>
       <c r="H15" s="24" t="inlineStr">
         <is>
-          <t>Segunda charla del mismo docente. Confirmar carga y disponibilidad.</t>
+          <t>La Dra. María Augusta Astudillo declinó este tema (25/09/2026, vía Lizbet Ruilova). Conserva M1 · C3, que no ha rechazado. SIN CANDIDATO.</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1962,7 @@
       </c>
       <c r="H26" s="24" t="inlineStr">
         <is>
-          <t>Solo faltan datos de contacto, hoja de vida y declaración COI.</t>
+          <t>La Dra. Adriana Alvarez confirma MASLD pero NO sarcopenia (25/09/2026). Propuso a la Dra. Adriana González para el tema de sarcopenia. RECOMENDACIÓN: sacar «sarcopenia» del título de esta clase, ya que el programa la cubre en M1 · C4 y M5 · C4. Faltan sus datos y documentación.</t>
         </is>
       </c>
     </row>
@@ -2649,7 +2641,7 @@
       <c r="H11" s="41" t="n"/>
       <c r="I11" s="40" t="inlineStr">
         <is>
-          <t>M6 · C4</t>
+          <t>M6 · C4 (solo MASLD y complicaciones metabólicas)</t>
         </is>
       </c>
       <c r="J11" s="42" t="n"/>
@@ -2658,7 +2650,7 @@
       <c r="M11" s="42" t="n"/>
       <c r="N11" s="43" t="inlineStr">
         <is>
-          <t>CONFIRMADO</t>
+          <t>CONFIRMADO — declina la parte de sarcopenia</t>
         </is>
       </c>
     </row>
@@ -2779,7 +2771,7 @@
       <c r="H14" s="41" t="n"/>
       <c r="I14" s="40" t="inlineStr">
         <is>
-          <t>M1 · C3  /  M4 · C1</t>
+          <t>M1 · C3</t>
         </is>
       </c>
       <c r="J14" s="42" t="n"/>
@@ -2788,7 +2780,7 @@
       <c r="M14" s="42" t="n"/>
       <c r="N14" s="44" t="inlineStr">
         <is>
-          <t>POR CONFIRMAR</t>
+          <t>POR CONFIRMAR — declinó M4 · C1 el 25/09</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2809,7 @@
       <c r="H15" s="41" t="n"/>
       <c r="I15" s="40" t="inlineStr">
         <is>
-          <t>M1 · C4  /  M4 · C3</t>
+          <t>M4 · C3</t>
         </is>
       </c>
       <c r="J15" s="42" t="n"/>
@@ -2826,7 +2818,7 @@
       <c r="M15" s="42" t="n"/>
       <c r="N15" s="44" t="inlineStr">
         <is>
-          <t>POR CONFIRMAR</t>
+          <t>POR CONFIRMAR — declinó M1 · C4 el 25/09</t>
         </is>
       </c>
     </row>
@@ -3070,7 +3062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3331,13 +3323,39 @@
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="55" t="n"/>
-      <c r="B11" s="52" t="n"/>
-      <c r="C11" s="53" t="n"/>
-      <c r="D11" s="53" t="n"/>
-      <c r="E11" s="53" t="n"/>
-      <c r="F11" s="53" t="n"/>
-      <c r="G11" s="53" t="n"/>
+      <c r="A11" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" s="39" t="inlineStr">
+        <is>
+          <t>M1 · C4</t>
+        </is>
+      </c>
+      <c r="C11" s="40" t="inlineStr">
+        <is>
+          <t>Composición corporal y sarcopenia</t>
+        </is>
+      </c>
+      <c r="D11" s="40" t="inlineStr">
+        <is>
+          <t>Endocrinología o nutrición con experiencia en sarcopenia y bioimpedancia</t>
+        </is>
+      </c>
+      <c r="E11" s="41" t="inlineStr">
+        <is>
+          <t>Dra. Adriana González — tesorera de ALAD, Ecuador</t>
+        </is>
+      </c>
+      <c r="F11" s="41" t="inlineStr">
+        <is>
+          <t>contacto enviado por la Dra. Adriana Alvarez</t>
+        </is>
+      </c>
+      <c r="G11" s="41" t="inlineStr">
+        <is>
+          <t>Jiménez declinó 25/09 · candidata con charla ya preparada</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="50" t="n">
@@ -3411,6 +3429,33 @@
       <c r="C14" s="51" t="inlineStr">
         <is>
           <t>Prioridad 1 = módulo completo descubierto · Prioridad 2 = módulo de salud digital · Prioridad 3 = clases sueltas</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="39" t="inlineStr">
+        <is>
+          <t>M4 · C1</t>
+        </is>
+      </c>
+      <c r="C15" s="40" t="inlineStr">
+        <is>
+          <t>Fisiopatología y clasificación de la diabetes</t>
+        </is>
+      </c>
+      <c r="D15" s="40" t="inlineStr">
+        <is>
+          <t>Endocrinología o medicina interna</t>
+        </is>
+      </c>
+      <c r="E15" s="41" t="n"/>
+      <c r="F15" s="41" t="n"/>
+      <c r="G15" s="41" t="inlineStr">
+        <is>
+          <t>Astudillo declinó 25/09 · SIN CANDIDATO</t>
         </is>
       </c>
     </row>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -973,7 +973,7 @@
       </c>
       <c r="C23" s="16" t="n"/>
       <c r="D23" s="17">
-        <f>COUNTA('Ponentes - datos aval'!B4:B21)</f>
+        <f>COUNTA('Ponentes - datos aval'!B4:B22)</f>
         <v/>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" s="16" t="n"/>
       <c r="D24" s="17">
-        <f>COUNTIF('Ponentes - datos aval'!J4:J21,"SÍ")</f>
+        <f>COUNTIF('Ponentes - datos aval'!J4:J22,"SÍ")</f>
         <v/>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="C25" s="16" t="n"/>
       <c r="D25" s="17">
-        <f>COUNTA('Ponentes - datos aval'!F4:F21)</f>
+        <f>COUNTA('Ponentes - datos aval'!F4:F22)</f>
         <v/>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="C26" s="16" t="n"/>
       <c r="D26" s="17">
-        <f>COUNTIF('Ponentes - datos aval'!L4:L21,"SÍ")</f>
+        <f>COUNTIF('Ponentes - datos aval'!L4:L22,"SÍ")</f>
         <v/>
       </c>
     </row>
@@ -1703,10 +1703,14 @@
           <t>Fenotipos metabólicos; individualización nutricional</t>
         </is>
       </c>
-      <c r="E19" s="28" t="inlineStr"/>
-      <c r="F19" s="29" t="inlineStr">
-        <is>
-          <t>VACANTE</t>
+      <c r="E19" s="64" t="inlineStr">
+        <is>
+          <t>Lcda. Gabriela Molina</t>
+        </is>
+      </c>
+      <c r="F19" s="27" t="inlineStr">
+        <is>
+          <t>CONFIRMADO</t>
         </is>
       </c>
       <c r="G19" s="23" t="n">
@@ -1714,7 +1718,7 @@
       </c>
       <c r="H19" s="24" t="inlineStr">
         <is>
-          <t>SIN PONENTE. Módulo 5 es el más descubierto: 3 de 4 clases vacías.</t>
+          <t>Aceptó el 28/09/2026. La propuso la Lcda. Daniela Vintimilla, Directora de la Carrera de Nutrición de la U. Cuenca. Condicionó su participación a recibir certificado de docente, que se le confirmó. Faltan sus documentos.</t>
         </is>
       </c>
     </row>
@@ -2197,7 +2201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3043,6 +3047,48 @@
       <c r="N21" s="65" t="inlineStr">
         <is>
           <t>CONFIRMADO — faltan especialidad, contacto y documentación</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="54" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="52" t="inlineStr">
+        <is>
+          <t>Lcda. Gabriela Molina</t>
+        </is>
+      </c>
+      <c r="C22" s="53" t="inlineStr">
+        <is>
+          <t>Nutrición</t>
+        </is>
+      </c>
+      <c r="D22" s="53" t="inlineStr">
+        <is>
+          <t>MSP · Cuenca, Ecuador (por confirmar el vínculo con la Carrera de Nutrición de la U. Cuenca)</t>
+        </is>
+      </c>
+      <c r="E22" s="41" t="n"/>
+      <c r="F22" s="41" t="inlineStr">
+        <is>
+          <t>+593 99 551 4286</t>
+        </is>
+      </c>
+      <c r="G22" s="41" t="n"/>
+      <c r="H22" s="41" t="n"/>
+      <c r="I22" s="54" t="inlineStr">
+        <is>
+          <t>M5 · C1</t>
+        </is>
+      </c>
+      <c r="J22" s="42" t="n"/>
+      <c r="K22" s="42" t="n"/>
+      <c r="L22" s="42" t="n"/>
+      <c r="M22" s="42" t="n"/>
+      <c r="N22" s="65" t="inlineStr">
+        <is>
+          <t>CONFIRMADO — faltan todos los documentos</t>
         </is>
       </c>
     </row>
@@ -3146,13 +3192,17 @@
       </c>
       <c r="E4" s="41" t="inlineStr">
         <is>
-          <t>Lcda. Gabriela Molina — propuesta por la Lcda. Daniela Vintimilla</t>
-        </is>
-      </c>
-      <c r="F4" s="41" t="n"/>
+          <t>Lcda. Gabriela Molina</t>
+        </is>
+      </c>
+      <c r="F4" s="41" t="inlineStr">
+        <is>
+          <t>+593 99 551 4286</t>
+        </is>
+      </c>
       <c r="G4" s="41" t="inlineStr">
         <is>
-          <t>La Lcda. Vintimilla declinó el 24/09 («no suelo dar conferencias») y propuso a la Lcda. Gabriela Molina, con experiencia en el tema. Falta contactarla. La Carrera de Nutrición de la U. Cuenca ofrece más docentes: pidió la lista de temas.</t>
+          <t>CUBIERTA — aceptó el 28/09/2026</t>
         </is>
       </c>
     </row>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -973,7 +973,7 @@
       </c>
       <c r="C23" s="16" t="n"/>
       <c r="D23" s="17">
-        <f>COUNTA('Ponentes - datos aval'!B4:B22)</f>
+        <f>COUNTA('Ponentes - datos aval'!B4:B23)</f>
         <v/>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" s="16" t="n"/>
       <c r="D24" s="17">
-        <f>COUNTIF('Ponentes - datos aval'!J4:J22,"SÍ")</f>
+        <f>COUNTIF('Ponentes - datos aval'!J4:J23,"SÍ")</f>
         <v/>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="C25" s="16" t="n"/>
       <c r="D25" s="17">
-        <f>COUNTA('Ponentes - datos aval'!F4:F22)</f>
+        <f>COUNTA('Ponentes - datos aval'!F4:F23)</f>
         <v/>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="C26" s="16" t="n"/>
       <c r="D26" s="17">
-        <f>COUNTIF('Ponentes - datos aval'!L4:L22,"SÍ")</f>
+        <f>COUNTIF('Ponentes - datos aval'!L4:L23,"SÍ")</f>
         <v/>
       </c>
     </row>
@@ -1771,10 +1771,14 @@
           <t>Agonistas de GLP-1; tirzepatida; preservación de la masa muscular</t>
         </is>
       </c>
-      <c r="E21" s="28" t="inlineStr"/>
-      <c r="F21" s="29" t="inlineStr">
-        <is>
-          <t>VACANTE</t>
+      <c r="E21" s="64" t="inlineStr">
+        <is>
+          <t>Dra. Gabriela Machado</t>
+        </is>
+      </c>
+      <c r="F21" s="27" t="inlineStr">
+        <is>
+          <t>CONFIRMADO</t>
         </is>
       </c>
       <c r="G21" s="23" t="n">
@@ -1782,7 +1786,7 @@
       </c>
       <c r="H21" s="24" t="inlineStr">
         <is>
-          <t>SIN PONENTE. Tema de alta demanda; buen candidato para ponente invitado de peso.</t>
+          <t>Aceptó el 28/09/2026, a través de la Lcda. Daniela Vintimilla, que lo consultó con su equipo. Faltan especialidad, institución y toda la documentación.</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3089,6 +3093,40 @@
       <c r="N22" s="65" t="inlineStr">
         <is>
           <t>CONFIRMADO — faltan todos los documentos</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="54" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="52" t="inlineStr">
+        <is>
+          <t>Dra. Gabriela Machado</t>
+        </is>
+      </c>
+      <c r="C23" s="53" t="n"/>
+      <c r="D23" s="53" t="n"/>
+      <c r="E23" s="41" t="n"/>
+      <c r="F23" s="41" t="inlineStr">
+        <is>
+          <t>+593 99 502 5774</t>
+        </is>
+      </c>
+      <c r="G23" s="41" t="n"/>
+      <c r="H23" s="41" t="n"/>
+      <c r="I23" s="54" t="inlineStr">
+        <is>
+          <t>M5 · C3</t>
+        </is>
+      </c>
+      <c r="J23" s="42" t="n"/>
+      <c r="K23" s="42" t="n"/>
+      <c r="L23" s="42" t="n"/>
+      <c r="M23" s="42" t="n"/>
+      <c r="N23" s="65" t="inlineStr">
+        <is>
+          <t>CONFIRMADO — faltan especialidad, institución y documentación</t>
         </is>
       </c>
     </row>
@@ -3256,9 +3294,21 @@
           <t>Nutricionista clínico o endocrinólogo; tema de alta demanda</t>
         </is>
       </c>
-      <c r="E6" s="62" t="n"/>
-      <c r="F6" s="41" t="n"/>
-      <c r="G6" s="63" t="n"/>
+      <c r="E6" s="62" t="inlineStr">
+        <is>
+          <t>Dra. Gabriela Machado</t>
+        </is>
+      </c>
+      <c r="F6" s="41" t="inlineStr">
+        <is>
+          <t>+593 99 502 5774</t>
+        </is>
+      </c>
+      <c r="G6" s="63" t="inlineStr">
+        <is>
+          <t>CUBIERTA — aceptó el 28/09/2026</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="50" t="n">

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -3006,7 +3006,11 @@
       </c>
       <c r="D20" s="53" t="n"/>
       <c r="E20" s="41" t="n"/>
-      <c r="F20" s="41" t="n"/>
+      <c r="F20" s="41" t="inlineStr">
+        <is>
+          <t>+593 97 965 3154</t>
+        </is>
+      </c>
       <c r="G20" s="41" t="n"/>
       <c r="H20" s="41" t="n"/>
       <c r="I20" s="54" t="inlineStr">
@@ -3020,7 +3024,7 @@
       <c r="M20" s="42" t="n"/>
       <c r="N20" s="65" t="inlineStr">
         <is>
-          <t>CONFIRMADO — faltan datos de contacto y documentación</t>
+          <t>CONFIRMADO — falta documentación</t>
         </is>
       </c>
     </row>
@@ -3551,11 +3555,19 @@
           <t>Endocrinología o medicina interna</t>
         </is>
       </c>
-      <c r="E15" s="41" t="n"/>
-      <c r="F15" s="41" t="n"/>
+      <c r="E15" s="41" t="inlineStr">
+        <is>
+          <t>Dr. José Luis Valverde — endocrinólogo</t>
+        </is>
+      </c>
+      <c r="F15" s="41" t="inlineStr">
+        <is>
+          <t>+593 99 111 0822 (móvil) · +593 95 903 2963 (anterior)</t>
+        </is>
+      </c>
       <c r="G15" s="41" t="inlineStr">
         <is>
-          <t>Astudillo declinó 25/09 · SIN CANDIDATO</t>
+          <t>Propuesto por la Dra. Lizbet Ruilova el 28/09: está en el grupo de delegados y todavía no tiene charla asignada. PENDIENTE DE INVITAR.</t>
         </is>
       </c>
     </row>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -3452,12 +3452,12 @@
       </c>
       <c r="F11" s="41" t="inlineStr">
         <is>
-          <t>contacto enviado por la Dra. Adriana Alvarez</t>
+          <t>+593 99 602 1221</t>
         </is>
       </c>
       <c r="G11" s="41" t="inlineStr">
         <is>
-          <t>Jiménez declinó 25/09 · candidata con charla ya preparada</t>
+          <t>Jiménez declinó 25/09 · candidata con charla ya preparada · PENDIENTE DE INVITAR</t>
         </is>
       </c>
     </row>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -1957,7 +1957,7 @@
       </c>
       <c r="E26" s="24" t="inlineStr">
         <is>
-          <t>Dra. Adriana Alvarez</t>
+          <t>Dra. Adriana Álvarez</t>
         </is>
       </c>
       <c r="F26" s="27" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="B11" s="39" t="inlineStr">
         <is>
-          <t>Dra. Adriana Alvarez</t>
+          <t>Dra. Adriana Álvarez</t>
         </is>
       </c>
       <c r="C11" s="41" t="n"/>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -1947,12 +1947,12 @@
       </c>
       <c r="C26" s="24" t="inlineStr">
         <is>
-          <t>MASLD, sarcopenia y complicaciones metabólicas</t>
+          <t>MASLD y complicaciones metabólicas</t>
         </is>
       </c>
       <c r="D26" s="24" t="inlineStr">
         <is>
-          <t>MASLD; obesidad sarcopénica; enfermedad osteomuscular; estrategias integrales</t>
+          <t>MASLD; enfermedad osteomuscular asociada a la obesidad; estrategias integrales</t>
         </is>
       </c>
       <c r="E26" s="24" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="H26" s="24" t="inlineStr">
         <is>
-          <t>La Dra. Adriana Alvarez confirma MASLD pero NO sarcopenia (25/09/2026). Propuso a la Dra. Adriana González para el tema de sarcopenia. RECOMENDACIÓN: sacar «sarcopenia» del título de esta clase, ya que el programa la cubre en M1 · C4 y M5 · C4. Faltan sus datos y documentación.</t>
+          <t>La Dra. Adriana Álvarez dicta MASLD. La sarcopenia sale de esta clase por decisión de la Dra. Omidres (28/09/2026): la asume la Dra. Adriana González en M1 · C4. Faltan los datos y la documentación de la Dra. Álvarez.</t>
         </is>
       </c>
     </row>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -2630,13 +2630,17 @@
       </c>
       <c r="B11" s="39" t="inlineStr">
         <is>
-          <t>Dra. Adriana Álvarez</t>
-        </is>
-      </c>
-      <c r="C11" s="41" t="n"/>
+          <t>Dra. Adriana Mabel Álvarez</t>
+        </is>
+      </c>
+      <c r="C11" s="41" t="inlineStr">
+        <is>
+          <t>Endocrinología · Comité de Esteatosis Hepática Metabólica (SAD) · Coordinadora del Grupo Obesidad-MASH de ALAD · Vocal Región Sur de ALAD</t>
+        </is>
+      </c>
       <c r="D11" s="41" t="inlineStr">
         <is>
-          <t>Argentina (institución y ciudad por confirmar)</t>
+          <t>Hospital Italiano de Buenos Aires · Buenos Aires, Argentina</t>
         </is>
       </c>
       <c r="E11" s="41" t="n"/>
@@ -2645,20 +2649,36 @@
           <t>+54 9 11 6708-1708</t>
         </is>
       </c>
-      <c r="G11" s="41" t="n"/>
+      <c r="G11" s="41" t="inlineStr">
+        <is>
+          <t>Pasaporte AAI843846 (vence 28/03/2033) · DNI 14.456.727</t>
+        </is>
+      </c>
       <c r="H11" s="41" t="n"/>
       <c r="I11" s="40" t="inlineStr">
         <is>
-          <t>M6 · C4 (solo MASLD y complicaciones metabólicas)</t>
+          <t>M6 · C4 (MASLD y complicaciones metabólicas)</t>
         </is>
       </c>
       <c r="J11" s="42" t="n"/>
-      <c r="K11" s="42" t="n"/>
-      <c r="L11" s="42" t="n"/>
-      <c r="M11" s="42" t="n"/>
+      <c r="K11" s="42" t="inlineStr">
+        <is>
+          <t>PARCIAL — solo la del pasaporte</t>
+        </is>
+      </c>
+      <c r="L11" s="42" t="inlineStr">
+        <is>
+          <t>PENDIENTE — declaró sin conflicto de palabra; falta el formato firmado</t>
+        </is>
+      </c>
+      <c r="M11" s="42" t="inlineStr">
+        <is>
+          <t>26/11/2026</t>
+        </is>
+      </c>
       <c r="N11" s="43" t="inlineStr">
         <is>
-          <t>CONFIRMADO — declina la parte de sarcopenia</t>
+          <t>CONFIRMADO — faltan hoja de vida, foto profesional y COI firmada</t>
         </is>
       </c>
     </row>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -765,7 +765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D28"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -774,6 +774,7 @@
     <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -802,6 +803,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -847,6 +849,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="B12" s="5" t="inlineStr">
         <is>
@@ -904,6 +907,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="B18" s="5" t="inlineStr">
         <is>
@@ -1013,6 +1017,7 @@
         <v/>
       </c>
     </row>
+    <row r="27"/>
     <row r="28" ht="40" customHeight="1">
       <c r="B28" s="18" t="inlineStr">
         <is>
@@ -1238,7 +1243,7 @@
       </c>
       <c r="H6" s="24" t="inlineStr">
         <is>
-          <t>La Dra. Gabriela Jiménez declinó el tema (25/09/2026, vía Lizbet Ruilova): «no quiere sarcopenia». Candidata: Dra. Adriana González, tesorera de ALAD, propuesta por la Dra. Adriana Alvarez — ya tiene preparada una charla de sarcopenia que dictó en Curitiba.</t>
+          <t>La Dra. Gabriela Jiménez declinó el tema (25/09/2026, vía Lizbet Ruilova): «no quiere sarcopenia». Candidata: Dra. Adriana González, tesorera de ALAD, propuesta por la Dra. Adriana Álvarez — ya tiene preparada una charla de sarcopenia que dictó en Curitiba.</t>
         </is>
       </c>
     </row>
@@ -2114,6 +2119,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="C32" s="31" t="inlineStr">
         <is>
@@ -2169,6 +2175,7 @@
         <v/>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="C38" s="34" t="inlineStr">
         <is>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -765,7 +765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="B2:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -774,7 +774,6 @@
     <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -803,7 +802,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -849,7 +847,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="B12" s="5" t="inlineStr">
         <is>
@@ -907,7 +904,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="B18" s="5" t="inlineStr">
         <is>
@@ -1017,7 +1013,6 @@
         <v/>
       </c>
     </row>
-    <row r="27"/>
     <row r="28" ht="40" customHeight="1">
       <c r="B28" s="18" t="inlineStr">
         <is>
@@ -2119,7 +2114,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="C32" s="31" t="inlineStr">
         <is>
@@ -2175,7 +2169,6 @@
         <v/>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="C38" s="34" t="inlineStr">
         <is>
@@ -3383,9 +3376,17 @@
           <t>Informática médica / IA aplicada a salud</t>
         </is>
       </c>
-      <c r="E8" s="41" t="n"/>
+      <c r="E8" s="41" t="inlineStr">
+        <is>
+          <t>Dr. Fabricio (apellido por confirmar) — linkedin.com/in/fslg</t>
+        </is>
+      </c>
       <c r="F8" s="41" t="n"/>
-      <c r="G8" s="41" t="n"/>
+      <c r="G8" s="41" t="inlineStr">
+        <is>
+          <t>Propuesto por la Dra. Omidres el 29/09 · faltan nombre completo y contacto · PENDIENTE DE INVITAR</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="50" t="n">
@@ -3484,7 +3485,7 @@
       </c>
       <c r="G11" s="41" t="inlineStr">
         <is>
-          <t>Jiménez declinó 25/09 · candidata con charla ya preparada · PENDIENTE DE INVITAR</t>
+          <t>INVITADA el 29/09/2026 · esperando respuesta</t>
         </is>
       </c>
     </row>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -3378,13 +3378,17 @@
       </c>
       <c r="E8" s="41" t="inlineStr">
         <is>
-          <t>Dr. Fabricio (apellido por confirmar) — linkedin.com/in/fslg</t>
-        </is>
-      </c>
-      <c r="F8" s="41" t="n"/>
+          <t>Dr. Fabrizio Salas — médico epidemiólogo, experto en salud digital</t>
+        </is>
+      </c>
+      <c r="F8" s="41" t="inlineStr">
+        <is>
+          <t>+593 99 381 4728</t>
+        </is>
+      </c>
       <c r="G8" s="41" t="inlineStr">
         <is>
-          <t>Propuesto por la Dra. Omidres el 29/09 · faltan nombre completo y contacto · PENDIENTE DE INVITAR</t>
+          <t>Propuesto por la Dra. Omidres el 29/09 · PENDIENTE DE INVITAR</t>
         </is>
       </c>
     </row>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -3353,9 +3353,21 @@
           <t>Endocrinólogo con experiencia en MCG/tecnología en diabetes</t>
         </is>
       </c>
-      <c r="E7" s="62" t="n"/>
-      <c r="F7" s="41" t="n"/>
-      <c r="G7" s="63" t="n"/>
+      <c r="E7" s="62" t="inlineStr">
+        <is>
+          <t>Dra. Ana María Gómez — endocrinóloga, Colombia</t>
+        </is>
+      </c>
+      <c r="F7" s="41" t="inlineStr">
+        <is>
+          <t>+57 310 488 4626</t>
+        </is>
+      </c>
+      <c r="G7" s="63" t="inlineStr">
+        <is>
+          <t>Propuesta por la Dra. Omidres el 29/09: experta en monitoreo de glucosa. PENDIENTE DE INVITAR. Si acepta, sería el QUINTO país extranjero del cuerpo docente y habría que añadir Colombia en el correo a la comisión de avales.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="50" t="n">

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -3365,7 +3365,7 @@
       </c>
       <c r="G7" s="63" t="inlineStr">
         <is>
-          <t>Propuesta por la Dra. Omidres el 29/09: experta en monitoreo de glucosa. PENDIENTE DE INVITAR. Si acepta, sería el QUINTO país extranjero del cuerpo docente y habría que añadir Colombia en el correo a la comisión de avales.</t>
+          <t>INVITADA el 29/09/2026 · esperando respuesta. Si acepta, sería el quinto país extranjero y habría que añadir Colombia en el correo a la comisión de avales.</t>
         </is>
       </c>
     </row>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -3289,13 +3289,17 @@
       </c>
       <c r="E5" s="41" t="inlineStr">
         <is>
-          <t>Gaby Villavicencio — nutrióloga</t>
-        </is>
-      </c>
-      <c r="F5" s="41" t="n"/>
+          <t>Lcda. María Augusta Vásquez — nutrición</t>
+        </is>
+      </c>
+      <c r="F5" s="41" t="inlineStr">
+        <is>
+          <t>+593 99 994 9812</t>
+        </is>
+      </c>
       <c r="G5" s="41" t="inlineStr">
         <is>
-          <t>INVITADO 23/09/2026 · esperando respuesta</t>
+          <t>La Dra. Gaby Villavicencio no respondió en seis días a la invitación del 23/09. Se reasigna la gestión el 29/09. PENDIENTE DE INVITAR.</t>
         </is>
       </c>
     </row>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -973,7 +973,7 @@
       </c>
       <c r="C23" s="16" t="n"/>
       <c r="D23" s="17">
-        <f>COUNTA('Ponentes - datos aval'!B4:B23)</f>
+        <f>COUNTA('Ponentes - datos aval'!B4:B25)</f>
         <v/>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" s="16" t="n"/>
       <c r="D24" s="17">
-        <f>COUNTIF('Ponentes - datos aval'!J4:J23,"SÍ")</f>
+        <f>COUNTIF('Ponentes - datos aval'!J4:J25,"SÍ")</f>
         <v/>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="C25" s="16" t="n"/>
       <c r="D25" s="17">
-        <f>COUNTA('Ponentes - datos aval'!F4:F23)</f>
+        <f>COUNTA('Ponentes - datos aval'!F4:F25)</f>
         <v/>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="C26" s="16" t="n"/>
       <c r="D26" s="17">
-        <f>COUNTIF('Ponentes - datos aval'!L4:L23,"SÍ")</f>
+        <f>COUNTIF('Ponentes - datos aval'!L4:L25,"SÍ")</f>
         <v/>
       </c>
     </row>
@@ -2031,10 +2031,14 @@
           <t>MCG y AGP en entornos digitales; monitoreo remoto (RPM), apps y wearables; salud conectada</t>
         </is>
       </c>
-      <c r="E28" s="28" t="inlineStr"/>
-      <c r="F28" s="29" t="inlineStr">
-        <is>
-          <t>VACANTE</t>
+      <c r="E28" s="24" t="inlineStr">
+        <is>
+          <t>Dra. Ana María Gómez</t>
+        </is>
+      </c>
+      <c r="F28" s="27" t="inlineStr">
+        <is>
+          <t>CONFIRMADO</t>
         </is>
       </c>
       <c r="G28" s="23" t="n">
@@ -2042,7 +2046,7 @@
       </c>
       <c r="H28" s="24" t="inlineStr">
         <is>
-          <t>SIN PONENTE. Puede asumirlo Dra. Omidres o un invitado en tecnología en diabetes.</t>
+          <t>Aceptó el 29/09/2026. Endocrinóloga, Colombia, experta en monitoreo de glucosa. QUINTO PAÍS EXTRANJERO del cuerpo docente. Se le delimitó su clase frente a M4 · C2 en la propia invitación. Falta toda la documentación.</t>
         </is>
       </c>
     </row>
@@ -2063,10 +2067,14 @@
           <t>Terapias digitales (DTx); IA en tamizaje y apoyo a la decisión; educación digital y adherencia</t>
         </is>
       </c>
-      <c r="E29" s="28" t="inlineStr"/>
-      <c r="F29" s="29" t="inlineStr">
-        <is>
-          <t>VACANTE</t>
+      <c r="E29" s="24" t="inlineStr">
+        <is>
+          <t>Dr. Fabrizio Salas</t>
+        </is>
+      </c>
+      <c r="F29" s="27" t="inlineStr">
+        <is>
+          <t>CONFIRMADO</t>
         </is>
       </c>
       <c r="G29" s="23" t="n">
@@ -2074,7 +2082,7 @@
       </c>
       <c r="H29" s="24" t="inlineStr">
         <is>
-          <t>SIN PONENTE. Perfil sugerido: informática médica / IA en salud.</t>
+          <t>Aceptó el 29/09/2026. Médico epidemiólogo, experto en salud digital. ALCANCE ACORDADO: panorama general de los tres puntos, no profundizar en uno. Él propuso acotar; la Dra. Omidres pidió el panorama porque para el público del curso estos temas «se ven como ciencia ficción» y hace falta la base. Pidió la plantilla y coordinar fecha. Falta toda la documentación.</t>
         </is>
       </c>
     </row>
@@ -2205,7 +2213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3151,6 +3159,98 @@
       <c r="N23" s="65" t="inlineStr">
         <is>
           <t>CONFIRMADO — faltan especialidad, institución y documentación</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="54" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="52" t="inlineStr">
+        <is>
+          <t>Dra. Ana María Gómez</t>
+        </is>
+      </c>
+      <c r="C24" s="53" t="inlineStr">
+        <is>
+          <t>Endocrinología · experta en monitoreo de glucosa</t>
+        </is>
+      </c>
+      <c r="D24" s="53" t="inlineStr">
+        <is>
+          <t>Colombia (institución y ciudad por confirmar)</t>
+        </is>
+      </c>
+      <c r="E24" s="41" t="n"/>
+      <c r="F24" s="41" t="inlineStr">
+        <is>
+          <t>+57 310 488 4626</t>
+        </is>
+      </c>
+      <c r="G24" s="41" t="n"/>
+      <c r="H24" s="41" t="n"/>
+      <c r="I24" s="54" t="inlineStr">
+        <is>
+          <t>M7 · C2</t>
+        </is>
+      </c>
+      <c r="J24" s="42" t="n"/>
+      <c r="K24" s="42" t="n"/>
+      <c r="L24" s="42" t="n"/>
+      <c r="M24" s="42" t="inlineStr">
+        <is>
+          <t>03/12/2026</t>
+        </is>
+      </c>
+      <c r="N24" s="65" t="inlineStr">
+        <is>
+          <t>CONFIRMADO — falta toda la documentación</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="54" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="52" t="inlineStr">
+        <is>
+          <t>Dr. Fabrizio Salas</t>
+        </is>
+      </c>
+      <c r="C25" s="53" t="inlineStr">
+        <is>
+          <t>Medicina · Epidemiología · Salud digital e interoperabilidad</t>
+        </is>
+      </c>
+      <c r="D25" s="53" t="inlineStr">
+        <is>
+          <t>Ecuador (institución por confirmar)</t>
+        </is>
+      </c>
+      <c r="E25" s="41" t="n"/>
+      <c r="F25" s="41" t="inlineStr">
+        <is>
+          <t>+593 99 381 4728</t>
+        </is>
+      </c>
+      <c r="G25" s="41" t="n"/>
+      <c r="H25" s="41" t="n"/>
+      <c r="I25" s="54" t="inlineStr">
+        <is>
+          <t>M7 · C3</t>
+        </is>
+      </c>
+      <c r="J25" s="42" t="n"/>
+      <c r="K25" s="42" t="n"/>
+      <c r="L25" s="42" t="n"/>
+      <c r="M25" s="42" t="inlineStr">
+        <is>
+          <t>03/12/2026</t>
+        </is>
+      </c>
+      <c r="N25" s="65" t="inlineStr">
+        <is>
+          <t>CONFIRMADO — falta toda la documentación</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3469,7 @@
       </c>
       <c r="G7" s="63" t="inlineStr">
         <is>
-          <t>INVITADA el 29/09/2026 · esperando respuesta. Si acepta, sería el quinto país extranjero y habría que añadir Colombia en el correo a la comisión de avales.</t>
+          <t>CUBIERTA — aceptó el 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3504,7 @@
       </c>
       <c r="G8" s="41" t="inlineStr">
         <is>
-          <t>Propuesto por la Dra. Omidres el 29/09 · PENDIENTE DE INVITAR</t>
+          <t>CUBIERTA — aceptó el 29/09/2026</t>
         </is>
       </c>
     </row>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -1124,9 +1124,9 @@
           <t>Dra. Lizbet Ruilova</t>
         </is>
       </c>
-      <c r="F3" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
+      <c r="F3" s="27" t="inlineStr">
+        <is>
+          <t>CONFIRMADO</t>
         </is>
       </c>
       <c r="G3" s="23" t="n">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="H3" s="24" t="inlineStr">
         <is>
-          <t>Coordinadora académica. Confirmar por escrito + hoja de vida + declaración COI.</t>
+          <t>Confirmado el 29/09/2026. Coordinadora académica. Confirmar por escrito + hoja de vida + declaración COI.</t>
         </is>
       </c>
     </row>
@@ -1160,9 +1160,9 @@
           <t>Dr. Pablo Vanegas</t>
         </is>
       </c>
-      <c r="F4" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
+      <c r="F4" s="27" t="inlineStr">
+        <is>
+          <t>CONFIRMADO</t>
         </is>
       </c>
       <c r="G4" s="23" t="n">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="H4" s="24" t="inlineStr">
         <is>
-          <t>Coordinador académico. Confirmar por escrito + hoja de vida + declaración COI.</t>
+          <t>Confirmado el 29/09/2026. Coordinador académico. Confirmar por escrito + hoja de vida + declaración COI.</t>
         </is>
       </c>
     </row>
@@ -1196,9 +1196,9 @@
           <t>Dra. María Augusta Astudillo</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
+      <c r="F5" s="27" t="inlineStr">
+        <is>
+          <t>CONFIRMADO</t>
         </is>
       </c>
       <c r="G5" s="23" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="H5" s="24" t="inlineStr">
         <is>
-          <t>Pedir aceptación formal, datos de contacto y hoja de vida.</t>
+          <t>Confirmado el 29/09/2026. Pedir aceptación formal, datos de contacto y hoja de vida.</t>
         </is>
       </c>
     </row>
@@ -1416,9 +1416,9 @@
           <t>Dr. Pablo Vanegas</t>
         </is>
       </c>
-      <c r="F11" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
+      <c r="F11" s="27" t="inlineStr">
+        <is>
+          <t>CONFIRMADO</t>
         </is>
       </c>
       <c r="G11" s="23" t="n">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="H11" s="24" t="inlineStr">
         <is>
-          <t>Segunda charla del mismo docente. Confirmar carga y disponibilidad.</t>
+          <t>Confirmado el 29/09/2026. Segunda charla del mismo docente. Confirmar carga y disponibilidad.</t>
         </is>
       </c>
     </row>
@@ -1632,9 +1632,9 @@
           <t>Dra. Gabriela Jiménez</t>
         </is>
       </c>
-      <c r="F17" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
+      <c r="F17" s="27" t="inlineStr">
+        <is>
+          <t>CONFIRMADO</t>
         </is>
       </c>
       <c r="G17" s="23" t="n">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="H17" s="24" t="inlineStr">
         <is>
-          <t>Segunda charla del mismo docente. Confirmar carga y disponibilidad.</t>
+          <t>Confirmado el 29/09/2026. Segunda charla del mismo docente. Confirmar carga y disponibilidad.</t>
         </is>
       </c>
     </row>
@@ -1668,9 +1668,9 @@
           <t>Dr. Juan Molina</t>
         </is>
       </c>
-      <c r="F18" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
+      <c r="F18" s="27" t="inlineStr">
+        <is>
+          <t>CONFIRMADO</t>
         </is>
       </c>
       <c r="G18" s="23" t="n">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="H18" s="24" t="inlineStr">
         <is>
-          <t>Pedir aceptación formal, datos de contacto y hoja de vida.</t>
+          <t>Confirmado el 29/09/2026. Pedir aceptación formal, datos de contacto y hoja de vida.</t>
         </is>
       </c>
     </row>
@@ -1812,9 +1812,9 @@
           <t>Dra. Lizbet Ruilova</t>
         </is>
       </c>
-      <c r="F22" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
+      <c r="F22" s="27" t="inlineStr">
+        <is>
+          <t>CONFIRMADO</t>
         </is>
       </c>
       <c r="G22" s="23" t="n">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="H22" s="24" t="inlineStr">
         <is>
-          <t>Segunda charla de la coordinadora. Revisar solapamiento con M1·C4 (Dra. Jiménez).</t>
+          <t>Confirmado el 29/09/2026. Segunda charla de la coordinadora. Revisar solapamiento con M1·C4 (Dra. Jiménez).</t>
         </is>
       </c>
     </row>
@@ -1852,9 +1852,9 @@
           <t>Dra. Valeria Andrade</t>
         </is>
       </c>
-      <c r="F23" s="25" t="inlineStr">
-        <is>
-          <t>POR CONFIRMAR</t>
+      <c r="F23" s="27" t="inlineStr">
+        <is>
+          <t>CONFIRMADO</t>
         </is>
       </c>
       <c r="G23" s="23" t="n">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="H23" s="24" t="inlineStr">
         <is>
-          <t>Pedir aceptación formal, datos de contacto y hoja de vida.</t>
+          <t>Confirmado el 29/09/2026. Pedir aceptación formal, datos de contacto y hoja de vida.</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       <c r="M12" s="42" t="n"/>
       <c r="N12" s="44" t="inlineStr">
         <is>
-          <t>POR CONFIRMAR</t>
+          <t>CONFIRMADO</t>
         </is>
       </c>
     </row>
@@ -2778,7 +2778,7 @@
       <c r="M13" s="42" t="n"/>
       <c r="N13" s="44" t="inlineStr">
         <is>
-          <t>POR CONFIRMAR</t>
+          <t>CONFIRMADO</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       <c r="M14" s="42" t="n"/>
       <c r="N14" s="44" t="inlineStr">
         <is>
-          <t>POR CONFIRMAR — declinó M4 · C1 el 25/09</t>
+          <t>CONFIRMADO — declinó M4 · C1 el 25/09</t>
         </is>
       </c>
     </row>
@@ -2854,7 +2854,7 @@
       <c r="M15" s="42" t="n"/>
       <c r="N15" s="44" t="inlineStr">
         <is>
-          <t>POR CONFIRMAR — declinó M1 · C4 el 25/09</t>
+          <t>CONFIRMADO — declinó M1 · C4 el 25/09</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
       <c r="M16" s="42" t="n"/>
       <c r="N16" s="44" t="inlineStr">
         <is>
-          <t>POR CONFIRMAR</t>
+          <t>CONFIRMADO</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       <c r="M17" s="42" t="n"/>
       <c r="N17" s="44" t="inlineStr">
         <is>
-          <t>POR CONFIRMAR</t>
+          <t>CONFIRMADO</t>
         </is>
       </c>
     </row>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -3065,10 +3065,18 @@
           <t>Dra. Julia Castro</t>
         </is>
       </c>
-      <c r="C21" s="53" t="n"/>
+      <c r="C21" s="53" t="inlineStr">
+        <is>
+          <t>Fisioterapia</t>
+        </is>
+      </c>
       <c r="D21" s="53" t="n"/>
       <c r="E21" s="41" t="n"/>
-      <c r="F21" s="41" t="n"/>
+      <c r="F21" s="41" t="inlineStr">
+        <is>
+          <t>+593 99 208 7747</t>
+        </is>
+      </c>
       <c r="G21" s="41" t="n"/>
       <c r="H21" s="41" t="n"/>
       <c r="I21" s="54" t="inlineStr">
@@ -3079,10 +3087,14 @@
       <c r="J21" s="42" t="n"/>
       <c r="K21" s="42" t="n"/>
       <c r="L21" s="42" t="n"/>
-      <c r="M21" s="42" t="n"/>
+      <c r="M21" s="42" t="inlineStr">
+        <is>
+          <t>29/10/2026</t>
+        </is>
+      </c>
       <c r="N21" s="65" t="inlineStr">
         <is>
-          <t>CONFIRMADO — faltan especialidad, contacto y documentación</t>
+          <t>CONFIRMADO — falta documentación · ENTREGA MÁS PRÓXIMA DEL CURSO</t>
         </is>
       </c>
     </row>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -973,7 +973,7 @@
       </c>
       <c r="C23" s="16" t="n"/>
       <c r="D23" s="17">
-        <f>COUNTA('Ponentes - datos aval'!B4:B25)</f>
+        <f>COUNTA('Ponentes - datos aval'!B4:B26)</f>
         <v/>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" s="16" t="n"/>
       <c r="D24" s="17">
-        <f>COUNTIF('Ponentes - datos aval'!J4:J25,"SÍ")</f>
+        <f>COUNTIF('Ponentes - datos aval'!J4:J26,"SÍ")</f>
         <v/>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="C25" s="16" t="n"/>
       <c r="D25" s="17">
-        <f>COUNTA('Ponentes - datos aval'!F4:F25)</f>
+        <f>COUNTA('Ponentes - datos aval'!F4:F26)</f>
         <v/>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="C26" s="16" t="n"/>
       <c r="D26" s="17">
-        <f>COUNTIF('Ponentes - datos aval'!L4:L25,"SÍ")</f>
+        <f>COUNTIF('Ponentes - datos aval'!L4:L26,"SÍ")</f>
         <v/>
       </c>
     </row>
@@ -1227,10 +1227,14 @@
           <t>IMC y sus limitaciones; circunferencia abdominal; bioimpedancia; obesidad sarcopénica</t>
         </is>
       </c>
-      <c r="E6" s="64" t="n"/>
+      <c r="E6" s="24" t="inlineStr">
+        <is>
+          <t>Dra. Adriana González</t>
+        </is>
+      </c>
       <c r="F6" s="27" t="inlineStr">
         <is>
-          <t>VACANTE</t>
+          <t>CONFIRMADO</t>
         </is>
       </c>
       <c r="G6" s="23" t="n">
@@ -1238,7 +1242,7 @@
       </c>
       <c r="H6" s="24" t="inlineStr">
         <is>
-          <t>La Dra. Gabriela Jiménez declinó el tema (25/09/2026, vía Lizbet Ruilova): «no quiere sarcopenia». Candidata: Dra. Adriana González, tesorera de ALAD, propuesta por la Dra. Adriana Álvarez — ya tiene preparada una charla de sarcopenia que dictó en Curitiba.</t>
+          <t>Aceptó el 29/09/2026. Tesorera de ALAD, Ecuador. La propuso la Dra. Adriana Álvarez: ya tenía preparada una charla de sarcopenia dictada en Curitiba. ENTREGA MÁS PRÓXIMA DEL CURSO, junto con el resto del módulo 1 y el 2. Falta toda la documentación.</t>
         </is>
       </c>
     </row>
@@ -2213,7 +2217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3261,6 +3265,52 @@
         </is>
       </c>
       <c r="N25" s="65" t="inlineStr">
+        <is>
+          <t>CONFIRMADO — falta toda la documentación</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="54" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="52" t="inlineStr">
+        <is>
+          <t>Dra. Adriana González</t>
+        </is>
+      </c>
+      <c r="C26" s="53" t="inlineStr">
+        <is>
+          <t>Endocrinología · Tesorera de ALAD</t>
+        </is>
+      </c>
+      <c r="D26" s="53" t="inlineStr">
+        <is>
+          <t>Ecuador (institución y ciudad por confirmar)</t>
+        </is>
+      </c>
+      <c r="E26" s="41" t="n"/>
+      <c r="F26" s="41" t="inlineStr">
+        <is>
+          <t>+593 99 602 1221</t>
+        </is>
+      </c>
+      <c r="G26" s="41" t="n"/>
+      <c r="H26" s="41" t="n"/>
+      <c r="I26" s="54" t="inlineStr">
+        <is>
+          <t>M1 · C4</t>
+        </is>
+      </c>
+      <c r="J26" s="42" t="n"/>
+      <c r="K26" s="42" t="n"/>
+      <c r="L26" s="42" t="n"/>
+      <c r="M26" s="42" t="inlineStr">
+        <is>
+          <t>29/10/2026</t>
+        </is>
+      </c>
+      <c r="N26" s="65" t="inlineStr">
         <is>
           <t>CONFIRMADO — falta toda la documentación</t>
         </is>
@@ -3617,7 +3667,7 @@
       </c>
       <c r="G11" s="41" t="inlineStr">
         <is>
-          <t>INVITADA el 29/09/2026 · esperando respuesta</t>
+          <t>CUBIERTA — aceptó el 29/09/2026</t>
         </is>
       </c>
     </row>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -2994,7 +2994,7 @@
       </c>
       <c r="B19" s="52" t="inlineStr">
         <is>
-          <t>Dra. María Paz Castillo</t>
+          <t>Dra. María Paz Castillo Cabrera</t>
         </is>
       </c>
       <c r="C19" s="53" t="inlineStr">
@@ -3002,9 +3002,17 @@
           <t>Endocrinología</t>
         </is>
       </c>
-      <c r="D19" s="53" t="n"/>
+      <c r="D19" s="53" t="inlineStr">
+        <is>
+          <t>Prefijo +52 (México) — CONFIRMAR dónde ejerce antes de darla por extranjera</t>
+        </is>
+      </c>
       <c r="E19" s="41" t="n"/>
-      <c r="F19" s="41" t="n"/>
+      <c r="F19" s="41" t="inlineStr">
+        <is>
+          <t>+52 1 56 2489 0698</t>
+        </is>
+      </c>
       <c r="G19" s="41" t="n"/>
       <c r="H19" s="41" t="n"/>
       <c r="I19" s="54" t="inlineStr">
@@ -3018,7 +3026,7 @@
       <c r="M19" s="42" t="n"/>
       <c r="N19" s="65" t="inlineStr">
         <is>
-          <t>ACEPTÓ — falta tema y datos de contacto</t>
+          <t>ACEPTÓ — sin tema asignado. La Dra. Ruilova pide incluirla (29/09)</t>
         </is>
       </c>
     </row>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -1563,10 +1563,14 @@
           <t>Defectos fisiopatológicos de la DM2; clasificación actual; diagnóstico temprano</t>
         </is>
       </c>
-      <c r="E15" s="64" t="n"/>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>Dra. María Paz Castillo Cabrera</t>
+        </is>
+      </c>
       <c r="F15" s="27" t="inlineStr">
         <is>
-          <t>VACANTE</t>
+          <t>CONFIRMADO</t>
         </is>
       </c>
       <c r="G15" s="23" t="n">
@@ -1574,7 +1578,7 @@
       </c>
       <c r="H15" s="24" t="inlineStr">
         <is>
-          <t>La Dra. María Augusta Astudillo declinó este tema (25/09/2026, vía Lizbet Ruilova). Conserva M1 · C3, que no ha rechazado. SIN CANDIDATO.</t>
+          <t>Asignada el 29/09/2026 a petición de la Dra. Lizbet Ruilova. El Dr. José Luis Valverde, invitado el 28/09, no respondió. Confirmar si ejerce en México antes de pedirle cédula: su teléfono es +52. Falta toda la documentación.</t>
         </is>
       </c>
     </row>
@@ -3017,16 +3021,20 @@
       <c r="H19" s="41" t="n"/>
       <c r="I19" s="54" t="inlineStr">
         <is>
-          <t>POR ASIGNAR</t>
+          <t>M4 · C1</t>
         </is>
       </c>
       <c r="J19" s="42" t="n"/>
       <c r="K19" s="42" t="n"/>
       <c r="L19" s="42" t="n"/>
-      <c r="M19" s="42" t="n"/>
+      <c r="M19" s="42" t="inlineStr">
+        <is>
+          <t>12/11/2026</t>
+        </is>
+      </c>
       <c r="N19" s="65" t="inlineStr">
         <is>
-          <t>ACEPTÓ — sin tema asignado. La Dra. Ruilova pide incluirla (29/09)</t>
+          <t>CONFIRMADO — falta documentación y confirmar país</t>
         </is>
       </c>
     </row>
@@ -3775,17 +3783,17 @@
       </c>
       <c r="E15" s="41" t="inlineStr">
         <is>
-          <t>Dr. José Luis Valverde — endocrinólogo</t>
+          <t>Dra. María Paz Castillo Cabrera</t>
         </is>
       </c>
       <c r="F15" s="41" t="inlineStr">
         <is>
-          <t>+593 99 111 0822 (móvil) · +593 95 903 2963 (anterior)</t>
+          <t>+52 1 56 2489 0698</t>
         </is>
       </c>
       <c r="G15" s="41" t="inlineStr">
         <is>
-          <t>Propuesto por la Dra. Lizbet Ruilova el 28/09: está en el grupo de delegados y todavía no tiene charla asignada. PENDIENTE DE INVITAR.</t>
+          <t>CUBIERTA — asignada el 29/09/2026 (el Dr. Valverde no respondió)</t>
         </is>
       </c>
     </row>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -1578,7 +1578,7 @@
       </c>
       <c r="H15" s="24" t="inlineStr">
         <is>
-          <t>Asignada el 29/09/2026 a petición de la Dra. Lizbet Ruilova. El Dr. José Luis Valverde, invitado el 28/09, no respondió. Confirmar si ejerce en México antes de pedirle cédula: su teléfono es +52. Falta toda la documentación.</t>
+          <t>Asignada el 29/09/2026 a petición de la Dra. Lizbet Ruilova. El Dr. José Luis Valverde, invitado el 28/09, no respondió. Ejerce en México: ponente internacional, se le pide pasaporte. Falta toda la documentación.</t>
         </is>
       </c>
     </row>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="D19" s="53" t="inlineStr">
         <is>
-          <t>Prefijo +52 (México) — CONFIRMAR dónde ejerce antes de darla por extranjera</t>
+          <t>México (institución y ciudad por confirmar)</t>
         </is>
       </c>
       <c r="E19" s="41" t="n"/>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="N19" s="65" t="inlineStr">
         <is>
-          <t>CONFIRMADO — falta documentación y confirmar país</t>
+          <t>CONFIRMADO — ponente internacional · falta documentación</t>
         </is>
       </c>
     </row>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -1578,7 +1578,7 @@
       </c>
       <c r="H15" s="24" t="inlineStr">
         <is>
-          <t>Asignada el 29/09/2026 a petición de la Dra. Lizbet Ruilova. El Dr. José Luis Valverde, invitado el 28/09, no respondió. Ejerce en México: ponente internacional, se le pide pasaporte. Falta toda la documentación.</t>
+          <t>Asignada el 29/09/2026 a petición de la Dra. Lizbet Ruilova. El Dr. José Luis Valverde, invitado el 28/09, no respondió. EN ESPERA: verificar con la Dra. Ruilova si es la misma María Paz Castillo vinculada al trámite de avales de la Universidad de Cuenca. Si lo es, hay conflicto de interés que declarar y el teléfono +52 no cuadra. No escribirle hasta aclararlo.</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="D19" s="53" t="inlineStr">
         <is>
-          <t>México (institución y ciudad por confirmar)</t>
+          <t>POR VERIFICAR — el teléfono es +52 (México), pero podría ser la misma persona vinculada al trámite de avales en Cuenca</t>
         </is>
       </c>
       <c r="E19" s="41" t="n"/>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="N19" s="65" t="inlineStr">
         <is>
-          <t>CONFIRMADO — ponente internacional · falta documentación</t>
+          <t>CONFIRMADO — identidad y país por verificar con la Dra. Ruilova · posible conflicto de interés</t>
         </is>
       </c>
     </row>
@@ -3332,6 +3332,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="J4:L18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -1578,7 +1578,7 @@
       </c>
       <c r="H15" s="24" t="inlineStr">
         <is>
-          <t>Asignada el 29/09/2026 a petición de la Dra. Lizbet Ruilova. El Dr. José Luis Valverde, invitado el 28/09, no respondió. EN ESPERA: verificar con la Dra. Ruilova si es la misma María Paz Castillo vinculada al trámite de avales de la Universidad de Cuenca. Si lo es, hay conflicto de interés que declarar y el teléfono +52 no cuadra. No escribirle hasta aclararlo.</t>
+          <t>Asignada el 29/09/2026 a petición de la Dra. Lizbet Ruilova. El Dr. José Luis Valverde, invitado el 28/09, no respondió. La Dra. Ruilova confirma el 29/09 que ejerce en CUENCA: ponente nacional, se le pide cédula (el +52 es un número mexicano conservado). PENDIENTE: aclarar si es la misma persona vinculada al trámite de avales de la Universidad de Cuenca. No escribirle hasta resolverlo.</t>
         </is>
       </c>
     </row>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="D19" s="53" t="inlineStr">
         <is>
-          <t>POR VERIFICAR — el teléfono es +52 (México), pero podría ser la misma persona vinculada al trámite de avales en Cuenca</t>
+          <t>Cuenca, Ecuador (institución por confirmar) — confirmado por la Dra. Ruilova el 29/09</t>
         </is>
       </c>
       <c r="E19" s="41" t="n"/>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="N19" s="65" t="inlineStr">
         <is>
-          <t>CONFIRMADO — identidad y país por verificar con la Dra. Ruilova · posible conflicto de interés</t>
+          <t>CONFIRMADO — ponente nacional · PENDIENTE aclarar si interviene en el trámite del aval</t>
         </is>
       </c>
     </row>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -1758,7 +1758,7 @@
       </c>
       <c r="H20" s="24" t="inlineStr">
         <is>
-          <t>SIN PONENTE. Perfil sugerido: nutricionista clínico con experiencia en diabetes.</t>
+          <t>SIN PONENTE. Perfil sugerido: nutricionista clínico con experiencia en diabetes. Historial: la Dra. Gaby Villavicencio no respondió (23/09). La Carrera de Nutrición de la U. Cuenca recibió la lista de temas y no lo tomó. La Lcda. María Augusta Vásquez declinó el 05/10. Se mantiene vacante por decisión de la Dra. Omidres.</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3332,7 +3332,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="J4:L18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -1758,7 +1758,7 @@
       </c>
       <c r="H20" s="24" t="inlineStr">
         <is>
-          <t>SIN PONENTE. Perfil sugerido: nutricionista clínico con experiencia en diabetes. Historial: la Dra. Gaby Villavicencio no respondió (23/09). La Carrera de Nutrición de la U. Cuenca recibió la lista de temas y no lo tomó. La Lcda. María Augusta Vásquez declinó el 05/10. Se mantiene vacante por decisión de la Dra. Omidres.</t>
+          <t>SIN PONENTE. Perfil sugerido: nutricionista clínico con experiencia en diabetes. Historial: la Dra. Gaby Villavicencio declinó y recomendó a otras personas, pendientes de contactar. La Carrera de Nutrición de la U. Cuenca recibió la lista de temas y no la tomó. La Lcda. María Augusta Vásquez declinó el 05/10. Se mantiene vacante por decisión de la Dra. Omidres.</t>
         </is>
       </c>
     </row>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -1758,7 +1758,12 @@
       </c>
       <c r="H20" s="24" t="inlineStr">
         <is>
-          <t>SIN PONENTE. Perfil sugerido: nutricionista clínico con experiencia en diabetes. Historial: la Dra. Gaby Villavicencio declinó y recomendó a otras personas, pendientes de contactar. La Carrera de Nutrición de la U. Cuenca recibió la lista de temas y no la tomó. La Lcda. María Augusta Vásquez declinó el 05/10. Se mantiene vacante por decisión de la Dra. Omidres.</t>
+          <t>SIN PONENTE. Perfil sugerido: nutricionista clínico con experiencia en diabetes.
+HISTORIAL DE GESTIÓN:
+· Dra. Gaby Villavicencio — DECLINÓ. Recomendó a otras personas, pendientes de contactar.
+· Carrera de Nutrición, U. Cuenca (Lcda. Daniela Vintimilla) — recibió la lista de temas el 23/09 y no tomó este.
+· Lcda. María Augusta Vásquez (+593 99 994 9812) — DECLINÓ el 05/10.
+Se mantiene vacante por decisión de la Dra. Omidres. NO volver a contactar a las tres anteriores para este tema.</t>
         </is>
       </c>
     </row>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -2226,7 +2226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2616,7 +2616,11 @@
           <t>+506 8392 7083</t>
         </is>
       </c>
-      <c r="G10" s="41" t="n"/>
+      <c r="G10" s="54" t="inlineStr">
+        <is>
+          <t>Pasaporte de Costa Rica (copia en expediente)</t>
+        </is>
+      </c>
       <c r="H10" s="41" t="n"/>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -2628,7 +2632,11 @@
           <t>SÍ</t>
         </is>
       </c>
-      <c r="K10" s="42" t="n"/>
+      <c r="K10" s="54" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
       <c r="L10" s="42" t="inlineStr">
         <is>
           <t>SÍ</t>
@@ -2717,12 +2725,12 @@
           <t>Endocrinología · Medicina Interna</t>
         </is>
       </c>
-      <c r="D12" s="53" t="inlineStr">
-        <is>
-          <t>SOLCA, Hospital Monte Sinaí y Universidad de Cuenca · Cuenca, Ecuador</t>
-        </is>
-      </c>
-      <c r="E12" s="53" t="inlineStr">
+      <c r="D12" s="54" t="inlineStr">
+        <is>
+          <t>SOLCA Cuenca · Hospital Monte Sinaí · Universidad de Cuenca</t>
+        </is>
+      </c>
+      <c r="E12" s="54" t="inlineStr">
         <is>
           <t>lizrg@hotmail.com</t>
         </is>
@@ -2961,12 +2969,12 @@
           <t>Medicina Interna · Subespecialista en Endocrinología · Alta especialidad en Obesidad y Enfermedades Tiroideas (UNAM)</t>
         </is>
       </c>
-      <c r="D18" s="53" t="inlineStr">
+      <c r="D18" s="42" t="inlineStr">
         <is>
           <t>Hospital del Río · Cuenca, Ecuador</t>
         </is>
       </c>
-      <c r="E18" s="41" t="inlineStr">
+      <c r="E18" s="42" t="inlineStr">
         <is>
           <t>jbendocrino@hotmail.com</t>
         </is>
@@ -2976,7 +2984,11 @@
           <t>+593 96 198 1203</t>
         </is>
       </c>
-      <c r="G18" s="41" t="n"/>
+      <c r="G18" s="42" t="inlineStr">
+        <is>
+          <t>0104851001</t>
+        </is>
+      </c>
       <c r="H18" s="41" t="n"/>
       <c r="I18" s="54" t="inlineStr">
         <is>
@@ -2989,7 +3001,11 @@
         </is>
       </c>
       <c r="K18" s="42" t="n"/>
-      <c r="L18" s="42" t="n"/>
+      <c r="L18" s="42" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
       <c r="M18" s="42" t="n"/>
       <c r="N18" s="65" t="inlineStr">
         <is>
@@ -3337,6 +3353,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="J4:L18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -2959,9 +2959,9 @@
       <c r="A18" s="54" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="52" t="inlineStr">
-        <is>
-          <t>Dra. Janneth Bermeo Cabrera</t>
+      <c r="B18" s="42" t="inlineStr">
+        <is>
+          <t>Dra. Marcia Janneth Bermeo Cabrera</t>
         </is>
       </c>
       <c r="C18" s="53" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="G18" s="42" t="inlineStr">
         <is>
-          <t>0104851001</t>
+          <t>0104851001 (copia de cédula en expediente)</t>
         </is>
       </c>
       <c r="H18" s="41" t="n"/>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -2226,7 +2226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2452,7 +2452,11 @@
           <t>SÍ</t>
         </is>
       </c>
-      <c r="K6" s="42" t="n"/>
+      <c r="K6" s="54" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
       <c r="L6" s="42" t="n"/>
       <c r="M6" s="42" t="n"/>
       <c r="N6" s="43" t="inlineStr">
@@ -2578,7 +2582,11 @@
           <t>SÍ</t>
         </is>
       </c>
-      <c r="K9" s="42" t="n"/>
+      <c r="K9" s="54" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
       <c r="L9" s="42" t="n"/>
       <c r="M9" s="42" t="n"/>
       <c r="N9" s="43" t="inlineStr">
@@ -2752,7 +2760,11 @@
           <t>SÍ</t>
         </is>
       </c>
-      <c r="K12" s="42" t="n"/>
+      <c r="K12" s="54" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
       <c r="L12" s="42" t="n"/>
       <c r="M12" s="42" t="n"/>
       <c r="N12" s="44" t="inlineStr">
@@ -3000,7 +3012,11 @@
           <t>SÍ</t>
         </is>
       </c>
-      <c r="K18" s="42" t="n"/>
+      <c r="K18" s="54" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
       <c r="L18" s="42" t="inlineStr">
         <is>
           <t>SÍ</t>
@@ -3353,7 +3369,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="J4:L18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -2381,34 +2381,62 @@
       <c r="A5" s="38" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="39" t="inlineStr">
-        <is>
-          <t>Lcda. Isabel Reinoso</t>
-        </is>
-      </c>
-      <c r="C5" s="40" t="inlineStr">
-        <is>
-          <t>Nutriología</t>
-        </is>
-      </c>
-      <c r="D5" s="41" t="n"/>
-      <c r="E5" s="41" t="n"/>
+      <c r="B5" s="54" t="inlineStr">
+        <is>
+          <t>Lcda. María Isabel Reinoso Pesántez</t>
+        </is>
+      </c>
+      <c r="C5" s="54" t="inlineStr">
+        <is>
+          <t>Licenciada en Nutrición y Dietética</t>
+        </is>
+      </c>
+      <c r="D5" s="54" t="inlineStr">
+        <is>
+          <t>Hospital del Bosque · Centro de Diálisis Nefrodial · Centro Platinum · Centro Pediatri.Co · consulta privada — Cuenca, Ecuador</t>
+        </is>
+      </c>
+      <c r="E5" s="54" t="inlineStr">
+        <is>
+          <t>isareinosonutricion@gmail.com</t>
+        </is>
+      </c>
       <c r="F5" s="60" t="inlineStr">
         <is>
           <t>+593 98 736 8816</t>
         </is>
       </c>
-      <c r="G5" s="41" t="n"/>
+      <c r="G5" s="54" t="inlineStr">
+        <is>
+          <t>0104473368</t>
+        </is>
+      </c>
       <c r="H5" s="41" t="n"/>
       <c r="I5" s="40" t="inlineStr">
         <is>
           <t>M2 · C1</t>
         </is>
       </c>
-      <c r="J5" s="42" t="n"/>
-      <c r="K5" s="42" t="n"/>
-      <c r="L5" s="42" t="n"/>
-      <c r="M5" s="42" t="n"/>
+      <c r="J5" s="54" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="K5" s="54" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="L5" s="54" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="M5" s="54" t="inlineStr">
+        <is>
+          <t>Jueves 29 de octubre de 2026</t>
+        </is>
+      </c>
       <c r="N5" s="43" t="inlineStr">
         <is>
           <t>CONFIRMADO</t>
@@ -2434,7 +2462,11 @@
           <t>Hospital del Río y Hospital Vicente Corral Moscoso · Cuenca, Ecuador</t>
         </is>
       </c>
-      <c r="E6" s="41" t="n"/>
+      <c r="E6" s="54" t="inlineStr">
+        <is>
+          <t>drajohannapiedra@gmail.com</t>
+        </is>
+      </c>
       <c r="F6" s="60" t="inlineStr">
         <is>
           <t>+593 98 765 4330</t>
@@ -2457,7 +2489,11 @@
           <t>SÍ</t>
         </is>
       </c>
-      <c r="L6" s="42" t="n"/>
+      <c r="L6" s="54" t="inlineStr">
+        <is>
+          <t>RECIBIDA por correo el 06/10 — falta abrir el PDF y verificar que esté completa y firmada</t>
+        </is>
+      </c>
       <c r="M6" s="42" t="n"/>
       <c r="N6" s="43" t="inlineStr">
         <is>
@@ -2765,7 +2801,11 @@
           <t>SÍ</t>
         </is>
       </c>
-      <c r="L12" s="42" t="n"/>
+      <c r="L12" s="54" t="inlineStr">
+        <is>
+          <t>EN BLANCO — el formato llegó sin llenar, sin casilla marcada y sin firma. Debe rehacerla.</t>
+        </is>
+      </c>
       <c r="M12" s="42" t="n"/>
       <c r="N12" s="44" t="inlineStr">
         <is>
@@ -2895,34 +2935,62 @@
       <c r="A16" s="38" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="39" t="inlineStr">
-        <is>
-          <t>Dr. Juan Molina</t>
-        </is>
-      </c>
-      <c r="C16" s="41" t="inlineStr">
-        <is>
-          <t>Endocrinología</t>
-        </is>
-      </c>
-      <c r="D16" s="41" t="n"/>
-      <c r="E16" s="41" t="n"/>
+      <c r="B16" s="54" t="inlineStr">
+        <is>
+          <t>Dr. Juan Fernando Molina Galarza</t>
+        </is>
+      </c>
+      <c r="C16" s="54" t="inlineStr">
+        <is>
+          <t>Medicina Interna · Endocrinología · Máster en infección por VIH</t>
+        </is>
+      </c>
+      <c r="D16" s="54" t="inlineStr">
+        <is>
+          <t>Hospital General Vicente Corral Moscoso · Corporación Médica Monte Sinaí — Cuenca, Ecuador</t>
+        </is>
+      </c>
+      <c r="E16" s="54" t="inlineStr">
+        <is>
+          <t>molinagalarza.jf@gmail.com</t>
+        </is>
+      </c>
       <c r="F16" s="60" t="inlineStr">
         <is>
           <t>+593 99 862 5711</t>
         </is>
       </c>
-      <c r="G16" s="41" t="n"/>
+      <c r="G16" s="54" t="inlineStr">
+        <is>
+          <t>0104904313</t>
+        </is>
+      </c>
       <c r="H16" s="41" t="n"/>
       <c r="I16" s="40" t="inlineStr">
         <is>
           <t>M4 · C4</t>
         </is>
       </c>
-      <c r="J16" s="42" t="n"/>
-      <c r="K16" s="42" t="n"/>
-      <c r="L16" s="42" t="n"/>
-      <c r="M16" s="42" t="n"/>
+      <c r="J16" s="54" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="K16" s="54" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="L16" s="54" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="M16" s="54" t="inlineStr">
+        <is>
+          <t>12 de noviembre de 2026</t>
+        </is>
+      </c>
       <c r="N16" s="44" t="inlineStr">
         <is>
           <t>CONFIRMADO</t>
@@ -3159,38 +3227,62 @@
       <c r="A22" s="54" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="52" t="inlineStr">
-        <is>
-          <t>Lcda. Gabriela Molina</t>
-        </is>
-      </c>
-      <c r="C22" s="53" t="inlineStr">
-        <is>
-          <t>Nutrición</t>
-        </is>
-      </c>
-      <c r="D22" s="53" t="inlineStr">
-        <is>
-          <t>MSP · Cuenca, Ecuador (por confirmar el vínculo con la Carrera de Nutrición de la U. Cuenca)</t>
-        </is>
-      </c>
-      <c r="E22" s="41" t="n"/>
+      <c r="B22" s="54" t="inlineStr">
+        <is>
+          <t>Lcda. Gabriela Estefanía Molina Ochoa, Mgt.</t>
+        </is>
+      </c>
+      <c r="C22" s="54" t="inlineStr">
+        <is>
+          <t>Nutrición · Diplomado en Educación en Diabetes · Máster en Antropología · Máster en Salud Pública</t>
+        </is>
+      </c>
+      <c r="D22" s="54" t="inlineStr">
+        <is>
+          <t>Universidad de Cuenca — Cuenca, Ecuador</t>
+        </is>
+      </c>
+      <c r="E22" s="54" t="inlineStr">
+        <is>
+          <t>gabrielamolinaochoa@gmail.com</t>
+        </is>
+      </c>
       <c r="F22" s="41" t="inlineStr">
         <is>
           <t>+593 99 551 4286</t>
         </is>
       </c>
-      <c r="G22" s="41" t="n"/>
+      <c r="G22" s="54" t="inlineStr">
+        <is>
+          <t>0105111827</t>
+        </is>
+      </c>
       <c r="H22" s="41" t="n"/>
       <c r="I22" s="54" t="inlineStr">
         <is>
           <t>M5 · C1</t>
         </is>
       </c>
-      <c r="J22" s="42" t="n"/>
-      <c r="K22" s="42" t="n"/>
-      <c r="L22" s="42" t="n"/>
-      <c r="M22" s="42" t="n"/>
+      <c r="J22" s="54" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="K22" s="54" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="L22" s="54" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="M22" s="54" t="inlineStr">
+        <is>
+          <t>Jueves 19 de noviembre de 2026</t>
+        </is>
+      </c>
       <c r="N22" s="65" t="inlineStr">
         <is>
           <t>CONFIRMADO — faltan todos los documentos</t>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -2472,7 +2472,11 @@
           <t>+593 98 765 4330</t>
         </is>
       </c>
-      <c r="G6" s="41" t="n"/>
+      <c r="G6" s="54" t="inlineStr">
+        <is>
+          <t>POSIBLE — llegó una imagen de WhatsApp sin identificar el 06/10; hay que abrirla</t>
+        </is>
+      </c>
       <c r="H6" s="41" t="n"/>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -2859,9 +2863,9 @@
       <c r="A14" s="38" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="39" t="inlineStr">
-        <is>
-          <t>Dra. María Augusta Astudillo</t>
+      <c r="B14" s="54" t="inlineStr">
+        <is>
+          <t>Dra. María Augusta Astudillo Calle</t>
         </is>
       </c>
       <c r="C14" s="41" t="inlineStr">
@@ -2870,7 +2874,11 @@
         </is>
       </c>
       <c r="D14" s="41" t="n"/>
-      <c r="E14" s="41" t="n"/>
+      <c r="E14" s="54" t="inlineStr">
+        <is>
+          <t>medimagu@yahoo.com</t>
+        </is>
+      </c>
       <c r="F14" s="60" t="inlineStr">
         <is>
           <t>+593 99 811 1635</t>
@@ -2883,8 +2891,16 @@
           <t>M1 · C3</t>
         </is>
       </c>
-      <c r="J14" s="42" t="n"/>
-      <c r="K14" s="42" t="n"/>
+      <c r="J14" s="54" t="inlineStr">
+        <is>
+          <t>SÍ — el archivo sigue en el correo, falta guardarlo en el expediente</t>
+        </is>
+      </c>
+      <c r="K14" s="54" t="inlineStr">
+        <is>
+          <t>SÍ — el archivo sigue en el correo, falta guardarlo en el expediente</t>
+        </is>
+      </c>
       <c r="L14" s="42" t="n"/>
       <c r="M14" s="42" t="n"/>
       <c r="N14" s="44" t="inlineStr">
@@ -3196,20 +3212,32 @@
         </is>
       </c>
       <c r="D21" s="53" t="n"/>
-      <c r="E21" s="41" t="n"/>
+      <c r="E21" s="54" t="inlineStr">
+        <is>
+          <t>castromezajulia@gmail.com</t>
+        </is>
+      </c>
       <c r="F21" s="41" t="inlineStr">
         <is>
           <t>+593 99 208 7747</t>
         </is>
       </c>
-      <c r="G21" s="41" t="n"/>
+      <c r="G21" s="54" t="inlineStr">
+        <is>
+          <t>SÍ — el archivo sigue en el correo, falta guardarlo en el expediente</t>
+        </is>
+      </c>
       <c r="H21" s="41" t="n"/>
       <c r="I21" s="54" t="inlineStr">
         <is>
           <t>M2 · C4</t>
         </is>
       </c>
-      <c r="J21" s="42" t="n"/>
+      <c r="J21" s="54" t="inlineStr">
+        <is>
+          <t>SÍ — el archivo sigue en el correo, falta guardarlo en el expediente</t>
+        </is>
+      </c>
       <c r="K21" s="42" t="n"/>
       <c r="L21" s="42" t="n"/>
       <c r="M21" s="42" t="inlineStr">

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -2408,7 +2408,7 @@
       </c>
       <c r="G5" s="54" t="inlineStr">
         <is>
-          <t>0104473368</t>
+          <t>0104473368 — copia de la cédula archivada y verificada contra el documento</t>
         </is>
       </c>
       <c r="H5" s="41" t="n"/>
@@ -2978,7 +2978,7 @@
       </c>
       <c r="G16" s="54" t="inlineStr">
         <is>
-          <t>0104904313</t>
+          <t>0104904313 — la copia está en Drive (formulario), falta guardarla en el expediente</t>
         </is>
       </c>
       <c r="H16" s="41" t="n"/>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -3201,20 +3201,24 @@
       <c r="A21" s="54" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="52" t="inlineStr">
-        <is>
-          <t>Dra. Julia Castro</t>
-        </is>
-      </c>
-      <c r="C21" s="53" t="inlineStr">
-        <is>
-          <t>Fisioterapia</t>
-        </is>
-      </c>
-      <c r="D21" s="53" t="n"/>
+      <c r="B21" s="54" t="inlineStr">
+        <is>
+          <t>Dra. Julia Castro de González</t>
+        </is>
+      </c>
+      <c r="C21" s="54" t="inlineStr">
+        <is>
+          <t>Medicina Física y Rehabilitación</t>
+        </is>
+      </c>
+      <c r="D21" s="54" t="inlineStr">
+        <is>
+          <t>Instituto Ecuatoriano de Seguridad Social (IESS) — Cuenca, Ecuador</t>
+        </is>
+      </c>
       <c r="E21" s="54" t="inlineStr">
         <is>
-          <t>castromezajulia@gmail.com</t>
+          <t>dracastrorehabilitacion@gmail.com (escribió desde castromezajulia@gmail.com — confirmar cuál usar)</t>
         </is>
       </c>
       <c r="F21" s="41" t="inlineStr">
@@ -3224,7 +3228,7 @@
       </c>
       <c r="G21" s="54" t="inlineStr">
         <is>
-          <t>SÍ — el archivo sigue en el correo, falta guardarlo en el expediente</t>
+          <t>0151826435 — dígito verificador correcto; copia enviada por correo, falta guardarla en el expediente</t>
         </is>
       </c>
       <c r="H21" s="41" t="n"/>
@@ -3239,10 +3243,14 @@
         </is>
       </c>
       <c r="K21" s="42" t="n"/>
-      <c r="L21" s="42" t="n"/>
-      <c r="M21" s="42" t="inlineStr">
-        <is>
-          <t>29/10/2026</t>
+      <c r="L21" s="54" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="M21" s="54" t="inlineStr">
+        <is>
+          <t>29 de octubre de 2026</t>
         </is>
       </c>
       <c r="N21" s="65" t="inlineStr">

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -3242,7 +3242,11 @@
           <t>SÍ — el archivo sigue en el correo, falta guardarlo en el expediente</t>
         </is>
       </c>
-      <c r="K21" s="42" t="n"/>
+      <c r="K21" s="54" t="inlineStr">
+        <is>
+          <t>PROVISIONAL — solo hay una miniatura de 150×150 px (4 KB), insuficiente para el expediente. Pedirle el archivo original.</t>
+        </is>
+      </c>
       <c r="L21" s="54" t="inlineStr">
         <is>
           <t>SÍ</t>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -2495,7 +2495,7 @@
       </c>
       <c r="L6" s="54" t="inlineStr">
         <is>
-          <t>RECIBIDA por correo el 06/10 — falta abrir el PDF y verificar que esté completa y firmada</t>
+          <t>SÍ — recibida firmada por correo el 06/10; falta abrirla y archivarla</t>
         </is>
       </c>
       <c r="M6" s="42" t="n"/>
@@ -3163,9 +3163,9 @@
       <c r="A20" s="54" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="52" t="inlineStr">
-        <is>
-          <t>Dr. Cristian Castillo</t>
+      <c r="B20" s="54" t="inlineStr">
+        <is>
+          <t>Dr. Cristian Castillo Cabrera</t>
         </is>
       </c>
       <c r="C20" s="53" t="inlineStr">
@@ -3174,22 +3174,42 @@
         </is>
       </c>
       <c r="D20" s="53" t="n"/>
-      <c r="E20" s="41" t="n"/>
+      <c r="E20" s="54" t="inlineStr">
+        <is>
+          <t>cristiancastillodr@gmail.com</t>
+        </is>
+      </c>
       <c r="F20" s="41" t="inlineStr">
         <is>
           <t>+593 97 965 3154</t>
         </is>
       </c>
-      <c r="G20" s="41" t="n"/>
+      <c r="G20" s="54" t="inlineStr">
+        <is>
+          <t>SÍ — el archivo sigue en el correo, falta guardarlo en el expediente</t>
+        </is>
+      </c>
       <c r="H20" s="41" t="n"/>
       <c r="I20" s="54" t="inlineStr">
         <is>
           <t>M3 · C4</t>
         </is>
       </c>
-      <c r="J20" s="42" t="n"/>
-      <c r="K20" s="42" t="n"/>
-      <c r="L20" s="42" t="n"/>
+      <c r="J20" s="54" t="inlineStr">
+        <is>
+          <t>SÍ — el archivo sigue en el correo, falta guardarlo en el expediente</t>
+        </is>
+      </c>
+      <c r="K20" s="54" t="inlineStr">
+        <is>
+          <t>SÍ — el archivo sigue en el correo, falta guardarlo en el expediente</t>
+        </is>
+      </c>
+      <c r="L20" s="54" t="inlineStr">
+        <is>
+          <t>SÍ — recibida por correo el 07/10; el PDF no dice «signed» en el nombre, hay que abrirlo y confirmar que esté llena y firmada</t>
+        </is>
+      </c>
       <c r="M20" s="42" t="n"/>
       <c r="N20" s="65" t="inlineStr">
         <is>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -2821,18 +2821,22 @@
       <c r="A13" s="38" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="39" t="inlineStr">
-        <is>
-          <t>Dr. Pablo Vanegas</t>
-        </is>
-      </c>
-      <c r="C13" s="41" t="inlineStr">
-        <is>
-          <t>Endocrinología</t>
-        </is>
-      </c>
-      <c r="D13" s="41" t="n"/>
-      <c r="E13" s="60" t="inlineStr">
+      <c r="B13" s="54" t="inlineStr">
+        <is>
+          <t>Dr. Pablo Esteban Vanegas Cedillo</t>
+        </is>
+      </c>
+      <c r="C13" s="54" t="inlineStr">
+        <is>
+          <t>Medicina Interna · Endocrinología · Obesidad y Trastornos de la Conducta Alimentaria</t>
+        </is>
+      </c>
+      <c r="D13" s="54" t="inlineStr">
+        <is>
+          <t>Hospital Santa Inés — Cuenca, Ecuador</t>
+        </is>
+      </c>
+      <c r="E13" s="54" t="inlineStr">
         <is>
           <t>pablo.vanegas90@gmail.com</t>
         </is>
@@ -2842,16 +2846,32 @@
           <t>+593 98 765 3136</t>
         </is>
       </c>
-      <c r="G13" s="41" t="n"/>
+      <c r="G13" s="54" t="inlineStr">
+        <is>
+          <t>0103838058 — leída de la cédula y contrastada con su declaración y su hoja de vida: coinciden</t>
+        </is>
+      </c>
       <c r="H13" s="41" t="n"/>
       <c r="I13" s="40" t="inlineStr">
         <is>
           <t>M1 · C2  /  M3 · C1</t>
         </is>
       </c>
-      <c r="J13" s="42" t="n"/>
-      <c r="K13" s="42" t="n"/>
-      <c r="L13" s="42" t="n"/>
+      <c r="J13" s="54" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="K13" s="54" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="L13" s="54" t="inlineStr">
+        <is>
+          <t>SÍ — DECLARA CONFLICTO: honorarios de Boehringer Ingelheim. Debe mencionarlo al inicio de la grabación de M3·C1. Falta completar producto/área, periodo y la fecha de firma.</t>
+        </is>
+      </c>
       <c r="M13" s="42" t="n"/>
       <c r="N13" s="44" t="inlineStr">
         <is>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -2335,18 +2335,22 @@
       <c r="A4" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="39" t="inlineStr">
-        <is>
-          <t>Dra. Omidres Pérez de Carvelli</t>
-        </is>
-      </c>
-      <c r="C4" s="40" t="inlineStr">
-        <is>
-          <t>Endocrinología · Medicina Interna</t>
-        </is>
-      </c>
-      <c r="D4" s="41" t="n"/>
-      <c r="E4" s="60" t="inlineStr">
+      <c r="B4" s="54" t="inlineStr">
+        <is>
+          <t>Dra. Omidres de la Consolación Pérez de Carvelli</t>
+        </is>
+      </c>
+      <c r="C4" s="54" t="inlineStr">
+        <is>
+          <t>Medicina Interna · Endocrinología y Metabolismo · Diabetología · Telemedicina y salud digital</t>
+        </is>
+      </c>
+      <c r="D4" s="54" t="inlineStr">
+        <is>
+          <t>Hospital Universitario del Río — Cuenca, Ecuador</t>
+        </is>
+      </c>
+      <c r="E4" s="54" t="inlineStr">
         <is>
           <t>info@draomidresperez.com</t>
         </is>
@@ -2356,16 +2360,36 @@
           <t>+593 98 206 2988</t>
         </is>
       </c>
-      <c r="G4" s="41" t="n"/>
-      <c r="H4" s="41" t="n"/>
+      <c r="G4" s="54" t="inlineStr">
+        <is>
+          <t>0961279080 — leída de la cédula (EXT*PERMANENTE) y contrastada con su hoja de vida: coinciden</t>
+        </is>
+      </c>
+      <c r="H4" s="54" t="inlineStr">
+        <is>
+          <t>Registro MSP Ecuador 116694452 · Investigadora acreditada SENESCYT INV-25-08756</t>
+        </is>
+      </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
           <t>M7 · C1  /  M7 · C4</t>
         </is>
       </c>
-      <c r="J4" s="42" t="n"/>
-      <c r="K4" s="42" t="n"/>
-      <c r="L4" s="42" t="n"/>
+      <c r="J4" s="54" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="K4" s="54" t="inlineStr">
+        <is>
+          <t>FALTA — su hoja de vida no trae retrato incrustado; hay que enviar una fotografía aparte</t>
+        </is>
+      </c>
+      <c r="L4" s="54" t="inlineStr">
+        <is>
+          <t>PRELLENADA, FALTA FIRMAR — declara vínculos: Omisalud (50 % y Presidencia), MEDDI Hub (CMO LATAM), OITT (Presidencia) y la dirección del diplomado en Salud eLearning</t>
+        </is>
+      </c>
       <c r="M4" s="42" t="inlineStr">
         <is>
           <t>03/12/2026</t>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -2382,7 +2382,7 @@
       </c>
       <c r="K4" s="54" t="inlineStr">
         <is>
-          <t>FALTA — su hoja de vida no trae retrato incrustado; hay que enviar una fotografía aparte</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="L4" s="54" t="inlineStr">

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -2912,12 +2912,16 @@
           <t>Dra. María Augusta Astudillo Calle</t>
         </is>
       </c>
-      <c r="C14" s="41" t="inlineStr">
-        <is>
-          <t>Endocrinología</t>
-        </is>
-      </c>
-      <c r="D14" s="41" t="n"/>
+      <c r="C14" s="54" t="inlineStr">
+        <is>
+          <t>Medicina Interna · Endocrinología</t>
+        </is>
+      </c>
+      <c r="D14" s="54" t="inlineStr">
+        <is>
+          <t>Hospital Santa Inés · Casa de la Diabetes — Cuenca, Ecuador (institución por confirmar: la letra del formulario no es del todo legible)</t>
+        </is>
+      </c>
       <c r="E14" s="54" t="inlineStr">
         <is>
           <t>medimagu@yahoo.com</t>
@@ -2928,7 +2932,11 @@
           <t>+593 99 811 1635</t>
         </is>
       </c>
-      <c r="G14" s="41" t="n"/>
+      <c r="G14" s="54" t="inlineStr">
+        <is>
+          <t>ILEGIBLE en el escaneo — escribió su cédula a mano y el número no se puede leer con certeza. Pedírselo o pedir copia del documento.</t>
+        </is>
+      </c>
       <c r="H14" s="41" t="n"/>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -2945,8 +2953,16 @@
           <t>SÍ — el archivo sigue en el correo, falta guardarlo en el expediente</t>
         </is>
       </c>
-      <c r="L14" s="42" t="n"/>
-      <c r="M14" s="42" t="n"/>
+      <c r="L14" s="54" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="M14" s="54" t="inlineStr">
+        <is>
+          <t>28 de octubre de 2026 (miércoles; el resto del módulo entrega en jueves — confirmar si quiso decir el 29)</t>
+        </is>
+      </c>
       <c r="N14" s="44" t="inlineStr">
         <is>
           <t>CONFIRMADO — declinó M4 · C1 el 25/09</t>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -2498,7 +2498,7 @@
       </c>
       <c r="G6" s="54" t="inlineStr">
         <is>
-          <t>POSIBLE — llegó una imagen de WhatsApp sin identificar el 06/10; hay que abrirla</t>
+          <t>YA PEDIDA por la coordinación el 09/10/2026. Había llegado una imagen de WhatsApp sin identificar que podría ser la cédula.</t>
         </is>
       </c>
       <c r="H6" s="41" t="n"/>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="D14" s="54" t="inlineStr">
         <is>
-          <t>Hospital Santa Inés · Casa de la Diabetes — Cuenca, Ecuador (institución por confirmar: la letra del formulario no es del todo legible)</t>
+          <t>Hospital Santa Inés · Casa de la Diabetes — Cuenca, Ecuador</t>
         </is>
       </c>
       <c r="E14" s="54" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="G14" s="54" t="inlineStr">
         <is>
-          <t>ILEGIBLE en el escaneo — escribió su cédula a mano y el número no se puede leer con certeza. Pedírselo o pedir copia del documento.</t>
+          <t>YA PEDIDA por la coordinación el 09/10/2026. Identidad dada por buena: la Dra. Omidres la verificó directamente con ella. El número manuscrito del formulario no es legible en el escaneo y por eso aquí no se transcribe ninguna cifra.</t>
         </is>
       </c>
       <c r="H14" s="41" t="n"/>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="M14" s="54" t="inlineStr">
         <is>
-          <t>28 de octubre de 2026 (miércoles; el resto del módulo entrega en jueves — confirmar si quiso decir el 29)</t>
+          <t>28 de octubre de 2026</t>
         </is>
       </c>
       <c r="N14" s="44" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="L20" s="54" t="inlineStr">
         <is>
-          <t>SÍ — recibida por correo el 07/10; el PDF no dice «signed» en el nombre, hay que abrirlo y confirmar que esté llena y firmada</t>
+          <t>YA PEDIDA la firma por la coordinación el 09/10/2026. Envió el formato el 07/10 pero el archivo no lleva «signed» en el nombre y no se ha podido abrir para comprobar que esté firmado.</t>
         </is>
       </c>
       <c r="M20" s="42" t="n"/>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C19" s="24" t="inlineStr">
         <is>
-          <t>Nutrición de precisión en diabetes y obesidad</t>
+          <t>Nutrición de precisión en diabetes y obesidad: innovación, equidad y desafíos para América Latina y Ecuador</t>
         </is>
       </c>
       <c r="D19" s="24" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="H19" s="24" t="inlineStr">
         <is>
-          <t>Aceptó el 28/09/2026. La propuso la Lcda. Daniela Vintimilla, Directora de la Carrera de Nutrición de la U. Cuenca. Condicionó su participación a recibir certificado de docente, que se le confirmó. Faltan sus documentos.</t>
+          <t>Aceptó el 28/09/2026. La propuso la Lcda. Daniela Vintimilla, Directora de la Carrera de Nutrición de la U. Cuenca. Condicionó su participación a recibir certificado de docente, que se le confirmó. Faltan sus documentos. TÍTULO ACTUALIZADO el 09/10/2026: la docente propuso ampliarlo en su formulario y la coordinación lo aprueba añadiendo «y Ecuador». Su declaración firmada lleva el título anterior, más corto; no hace falta rehacerla, pero el programa que va al expediente lleva este.</t>
         </is>
       </c>
     </row>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -3612,7 +3612,7 @@
     <row r="1">
       <c r="A1" s="20" t="inlineStr">
         <is>
-          <t>LAS 9 CLASES SIN PONENTE · Prioridad de gestión</t>
+          <t>CLASES QUE QUEDARON SIN PONENTE · Queda 1 vacante: M5 · C2 (al 09/10/2026)</t>
         </is>
       </c>
     </row>
@@ -3716,17 +3716,13 @@
       </c>
       <c r="E5" s="41" t="inlineStr">
         <is>
-          <t>Lcda. María Augusta Vásquez — nutrición</t>
-        </is>
-      </c>
-      <c r="F5" s="41" t="inlineStr">
-        <is>
-          <t>+593 99 994 9812</t>
-        </is>
-      </c>
+          <t>SIN CANDIDATO — VACANTE</t>
+        </is>
+      </c>
+      <c r="F5" s="41" t="n"/>
       <c r="G5" s="41" t="inlineStr">
         <is>
-          <t>La Dra. Gaby Villavicencio no respondió en seis días a la invitación del 23/09. Se reasigna la gestión el 29/09. PENDIENTE DE INVITAR.</t>
+          <t>VACANTE. Declinaron la Dra. Gaby Villavicencio (recomendó a otras personas, pendientes de contactar), la Carrera de Nutrición de la U. Cuenca (recibió los temas el 23/09 y no tomó este) y la Lcda. María Augusta Vásquez (05/10). Se mantiene vacante por decisión de la Dra. Omidres. No volver a contactar a esas tres para este tema.</t>
         </is>
       </c>
     </row>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -2752,7 +2752,7 @@
       </c>
       <c r="G11" s="41" t="inlineStr">
         <is>
-          <t>Pasaporte AAI843846 (vence 28/03/2033) · DNI 14.456.727</t>
+          <t>Pasaporte AAI843846 (vence 28/03/2033) · DNI 14.456.727 — copia archivada el 10/10/2026; los cinco dígitos de control de la zona de lectura mecánica son correctos y coinciden con estos datos</t>
         </is>
       </c>
       <c r="H11" s="41" t="n"/>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -2761,7 +2761,11 @@
           <t>M6 · C4 (MASLD y complicaciones metabólicas)</t>
         </is>
       </c>
-      <c r="J11" s="42" t="n"/>
+      <c r="J11" s="42" t="inlineStr">
+        <is>
+          <t>BORRADOR — la coordinación la armó el 10/10/2026 con los datos de la docente y PubMed (SEDA_HojaVida_Alvarez_BORRADOR.pdf). PENDIENTE de que la Dra. Álvarez la revise, complete su formación y la apruebe.</t>
+        </is>
+      </c>
       <c r="K11" s="42" t="inlineStr">
         <is>
           <t>PARCIAL — solo la del pasaporte</t>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -2082,7 +2082,7 @@
       </c>
       <c r="E29" s="24" t="inlineStr">
         <is>
-          <t>Dr. Fabrizio Salas</t>
+          <t>Dr. Fabricio Salas Guerrero</t>
         </is>
       </c>
       <c r="F29" s="27" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="J11" s="42" t="inlineStr">
         <is>
-          <t>BORRADOR — la coordinación la armó el 10/10/2026 con los datos de la docente y PubMed (SEDA_HojaVida_Alvarez_BORRADOR.pdf). PENDIENTE de que la Dra. Álvarez la revise, complete su formación y la apruebe.</t>
+          <t>POR CONFIRMAR — la coordinación cerró el 10/10/2026 la versión final (CV_Alvarez_Adriana-Mabel.pdf), pero falta saber si la Dra. Álvarez la aprobó. Esa versión da como suyas cinco publicaciones firmadas solo «Alvarez A».</t>
         </is>
       </c>
       <c r="K11" s="42" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="B25" s="52" t="inlineStr">
         <is>
-          <t>Dr. Fabrizio Salas</t>
+          <t>Dr. Ronald Fabricio Salas Guerrero</t>
         </is>
       </c>
       <c r="C25" s="53" t="inlineStr">
@@ -3509,10 +3509,14 @@
       </c>
       <c r="D25" s="53" t="inlineStr">
         <is>
-          <t>Ecuador (institución por confirmar)</t>
-        </is>
-      </c>
-      <c r="E25" s="41" t="n"/>
+          <t>Ministerio de Salud Pública del Ecuador (epidemiólogo, 2026)</t>
+        </is>
+      </c>
+      <c r="E25" s="41" t="inlineStr">
+        <is>
+          <t>fabriciosalasguerrero@gmail.com</t>
+        </is>
+      </c>
       <c r="F25" s="41" t="inlineStr">
         <is>
           <t>+593 99 381 4728</t>
@@ -3525,7 +3529,11 @@
           <t>M7 · C3</t>
         </is>
       </c>
-      <c r="J25" s="42" t="n"/>
+      <c r="J25" s="42" t="inlineStr">
+        <is>
+          <t>SÍ — recibida el 10/10/2026 y archivada (CV_Salas-Guerrero_Ronald-Fabricio.pdf). Ojo: los dos registros SENESCYT que figuran en ella parecen intercambiados entre el título de médico y la maestría.</t>
+        </is>
+      </c>
       <c r="K25" s="42" t="n"/>
       <c r="L25" s="42" t="n"/>
       <c r="M25" s="42" t="inlineStr">
@@ -3545,20 +3553,24 @@
       </c>
       <c r="B26" s="52" t="inlineStr">
         <is>
-          <t>Dra. Adriana González</t>
+          <t>Dra. Adriana Victoria González Neira</t>
         </is>
       </c>
       <c r="C26" s="53" t="inlineStr">
         <is>
-          <t>Endocrinología · Tesorera de ALAD</t>
+          <t>Medicina Interna · Endocrinología · Diabetes · Tesorera de ALAD (2026–2028)</t>
         </is>
       </c>
       <c r="D26" s="53" t="inlineStr">
         <is>
-          <t>Ecuador (institución y ciudad por confirmar)</t>
-        </is>
-      </c>
-      <c r="E26" s="41" t="n"/>
+          <t>Hospital Clínica Kennedy · Hospital General Naval (HOSNAG) — Guayaquil, Ecuador</t>
+        </is>
+      </c>
+      <c r="E26" s="41" t="inlineStr">
+        <is>
+          <t>adrianagn26@yahoo.com</t>
+        </is>
+      </c>
       <c r="F26" s="41" t="inlineStr">
         <is>
           <t>+593 99 602 1221</t>
@@ -3571,7 +3583,11 @@
           <t>M1 · C4</t>
         </is>
       </c>
-      <c r="J26" s="42" t="n"/>
+      <c r="J26" s="42" t="inlineStr">
+        <is>
+          <t>SÍ — recibida el 10/10/2026 y archivada (CV_Gonzalez-Neira_Adriana-Victoria.pdf)</t>
+        </is>
+      </c>
       <c r="K26" s="42" t="n"/>
       <c r="L26" s="42" t="n"/>
       <c r="M26" s="42" t="inlineStr">
@@ -3821,7 +3837,7 @@
       </c>
       <c r="E8" s="41" t="inlineStr">
         <is>
-          <t>Dr. Fabrizio Salas — médico epidemiólogo, experto en salud digital</t>
+          <t>Dr. Fabricio Salas Guerrero — médico epidemiólogo, experto en salud digital</t>
         </is>
       </c>
       <c r="F8" s="41" t="inlineStr">

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -2573,16 +2573,24 @@
       </c>
       <c r="B8" s="39" t="inlineStr">
         <is>
-          <t>Dra. Teresa Cuatecontzi</t>
-        </is>
-      </c>
-      <c r="C8" s="41" t="n"/>
+          <t>Dra. E. Teresa Cuatecontzi Xochitiotzi</t>
+        </is>
+      </c>
+      <c r="C8" s="41" t="inlineStr">
+        <is>
+          <t>Medicina Interna · Endocrinología · Alta especialidad en Obesidad · Maestría en Ciencias Médicas y Nutrición (INCMNSZ/UNAM)</t>
+        </is>
+      </c>
       <c r="D8" s="53" t="inlineStr">
         <is>
-          <t>México (institución y ciudad por confirmar)</t>
-        </is>
-      </c>
-      <c r="E8" s="41" t="n"/>
+          <t>Clínica Especializada en el Manejo de la Diabetes — Ciudad de México, México</t>
+        </is>
+      </c>
+      <c r="E8" s="41" t="inlineStr">
+        <is>
+          <t>xochitiotzi1@gmail.com</t>
+        </is>
+      </c>
       <c r="F8" s="41" t="inlineStr">
         <is>
           <t>+52 1 55 5405 6619</t>
@@ -2595,8 +2603,16 @@
           <t>M3 · C3</t>
         </is>
       </c>
-      <c r="J8" s="42" t="n"/>
-      <c r="K8" s="42" t="n"/>
+      <c r="J8" s="42" t="inlineStr">
+        <is>
+          <t>SÍ — recibida el 11/10/2026 y archivada (CV_Cuatecontzi-Xochitiotzi_Teresa.pdf). En el encabezado dice «TERES» por «TERESA».</t>
+        </is>
+      </c>
+      <c r="K8" s="42" t="inlineStr">
+        <is>
+          <t>SÍ — recibida el 11/10/2026 (441×478 px, retrato profesional), archivada como Foto_Cuatecontzi-Xochitiotzi_Teresa.jpg</t>
+        </is>
+      </c>
       <c r="L8" s="42" t="n"/>
       <c r="M8" s="42" t="n"/>
       <c r="N8" s="43" t="inlineStr">
@@ -2763,7 +2779,7 @@
       </c>
       <c r="J11" s="42" t="inlineStr">
         <is>
-          <t>POR CONFIRMAR — la coordinación cerró el 10/10/2026 la versión final (CV_Alvarez_Adriana-Mabel.pdf), pero falta saber si la Dra. Álvarez la aprobó. Esa versión da como suyas cinco publicaciones firmadas solo «Alvarez A».</t>
+          <t>SÍ — versión final cerrada por la coordinación el 10/10/2026 y APROBADA por la Dra. Álvarez, según la Dra. Omidres (10/10/2026). Archivada como CV_Alvarez_Adriana-Mabel.pdf. Incluye cinco publicaciones firmadas «Alvarez A» que ella da por suyas al aprobarla.</t>
         </is>
       </c>
       <c r="K11" s="42" t="inlineStr">

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -1760,7 +1760,7 @@
         <is>
           <t>SIN PONENTE. Perfil sugerido: nutricionista clínico con experiencia en diabetes.
 HISTORIAL DE GESTIÓN:
-· Dra. Gaby Villavicencio — DECLINÓ. Recomendó a otras personas, pendientes de contactar.
+· Dra. Gaby Villavicencio — DECLINÓ. Recomendó a otras personas: la Dra. Omidres les escribió y no respondieron (al 12/10/2026).
 · Carrera de Nutrición, U. Cuenca (Lcda. Daniela Vintimilla) — recibió la lista de temas el 23/09 y no tomó este.
 · Lcda. María Augusta Vásquez (+593 99 994 9812) — DECLINÓ el 05/10.
 Se mantiene vacante por decisión de la Dra. Omidres. NO volver a contactar a las tres anteriores para este tema.</t>
@@ -2135,6 +2135,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="C32" s="31" t="inlineStr">
         <is>
@@ -2190,6 +2191,7 @@
         <v/>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="C38" s="34" t="inlineStr">
         <is>
@@ -3758,7 +3760,7 @@
       <c r="F5" s="41" t="n"/>
       <c r="G5" s="41" t="inlineStr">
         <is>
-          <t>VACANTE. Declinaron la Dra. Gaby Villavicencio (recomendó a otras personas, pendientes de contactar), la Carrera de Nutrición de la U. Cuenca (recibió los temas el 23/09 y no tomó este) y la Lcda. María Augusta Vásquez (05/10). Se mantiene vacante por decisión de la Dra. Omidres. No volver a contactar a esas tres para este tema.</t>
+          <t>VACANTE. Declinaron la Dra. Gaby Villavicencio (recomendó a otras personas; se les escribió y no respondieron al 12/10/2026), la Carrera de Nutrición de la U. Cuenca (recibió los temas el 23/09 y no tomó este) y la Lcda. María Augusta Vásquez (05/10). Se mantiene vacante por decisión de la Dra. Omidres. No volver a contactar a esas tres para este tema.</t>
         </is>
       </c>
     </row>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -2135,7 +2135,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="C32" s="31" t="inlineStr">
         <is>
@@ -2191,7 +2190,6 @@
         <v/>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="C38" s="34" t="inlineStr">
         <is>
@@ -3227,7 +3225,11 @@
           <t>M4 · C1</t>
         </is>
       </c>
-      <c r="J19" s="42" t="n"/>
+      <c r="J19" s="42" t="inlineStr">
+        <is>
+          <t>POR CONFIRMAR — llegó por correo el 12/10/2026, enviada por la Dra. Ruilova («hoja de vida completa 22-9-2026.pdf», unos 17 MB). Falta abrirla, comprobar que es suya y guardarla en el expediente.</t>
+        </is>
+      </c>
       <c r="K19" s="42" t="n"/>
       <c r="L19" s="42" t="n"/>
       <c r="M19" s="42" t="inlineStr">

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -3227,7 +3227,7 @@
       </c>
       <c r="J19" s="42" t="inlineStr">
         <is>
-          <t>POR CONFIRMAR — llegó por correo el 12/10/2026, enviada por la Dra. Ruilova («hoja de vida completa 22-9-2026.pdf», unos 17 MB). Falta abrirla, comprobar que es suya y guardarla en el expediente.</t>
+          <t>SÍ — la envió la Dra. Ruilova por correo el 12/10/2026 («hoja de vida completa 22-9-2026.pdf»); la Dra. Omidres la revisó y la da por buena (12/10/2026). El archivo sigue en el correo, falta guardarlo en el expediente.</t>
         </is>
       </c>
       <c r="K19" s="42" t="n"/>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -2995,16 +2995,24 @@
       </c>
       <c r="B15" s="39" t="inlineStr">
         <is>
-          <t>Dra. Gabriela Jiménez</t>
+          <t>Dra. Marcia Gabriela Jiménez Encalada</t>
         </is>
       </c>
       <c r="C15" s="41" t="inlineStr">
         <is>
-          <t>Endocrinología</t>
-        </is>
-      </c>
-      <c r="D15" s="41" t="n"/>
-      <c r="E15" s="41" t="n"/>
+          <t>Medicina Interna · Endocrinología</t>
+        </is>
+      </c>
+      <c r="D15" s="41" t="inlineStr">
+        <is>
+          <t>Centro de Especialidades Médicas de la Universidad de Cuenca · Hospital Santa Inés — Cuenca, Ecuador</t>
+        </is>
+      </c>
+      <c r="E15" s="41" t="inlineStr">
+        <is>
+          <t>gabriela.jimeneze@ucuenca.edu.ec</t>
+        </is>
+      </c>
       <c r="F15" s="60" t="inlineStr">
         <is>
           <t>+593 99 807 8964</t>
@@ -3017,7 +3025,11 @@
           <t>M4 · C3</t>
         </is>
       </c>
-      <c r="J15" s="42" t="n"/>
+      <c r="J15" s="42" t="inlineStr">
+        <is>
+          <t>SÍ — recibida el 12/10/2026 y archivada (CV_Jimenez-Encalada_Marcia-Gabriela.docx). Última modificación del archivo: diciembre de 2024.</t>
+        </is>
+      </c>
       <c r="K15" s="42" t="n"/>
       <c r="L15" s="42" t="n"/>
       <c r="M15" s="42" t="n"/>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -2841,7 +2841,7 @@
       </c>
       <c r="J12" s="54" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>SÍ — archivada (CV_Ruilova-Gonzalez_Lizbet.pdf). La «actualizada» que reenvió el 12/10/2026 tiene el mismo contenido.</t>
         </is>
       </c>
       <c r="K12" s="54" t="inlineStr">
@@ -3216,15 +3216,19 @@
       </c>
       <c r="C19" s="53" t="inlineStr">
         <is>
-          <t>Endocrinología</t>
+          <t>Medicina Interna · Endocrinología · Alta especialidad en Enfermedades Tiroideas (UNAM)</t>
         </is>
       </c>
       <c r="D19" s="53" t="inlineStr">
         <is>
-          <t>Cuenca, Ecuador (institución por confirmar) — confirmado por la Dra. Ruilova el 29/09</t>
-        </is>
-      </c>
-      <c r="E19" s="41" t="n"/>
+          <t>Centro Metropolitano de Oncología Integral, Hospital Ángeles — Ciudad de México, México (según su hoja de vida de 22/09/2026)</t>
+        </is>
+      </c>
+      <c r="E19" s="41" t="inlineStr">
+        <is>
+          <t>mariapazcc22@hotmail.com</t>
+        </is>
+      </c>
       <c r="F19" s="41" t="inlineStr">
         <is>
           <t>+52 1 56 2489 0698</t>
@@ -3239,7 +3243,7 @@
       </c>
       <c r="J19" s="42" t="inlineStr">
         <is>
-          <t>SÍ — la envió la Dra. Ruilova por correo el 12/10/2026 («hoja de vida completa 22-9-2026.pdf»); la Dra. Omidres la revisó y la da por buena (12/10/2026). El archivo sigue en el correo, falta guardarlo en el expediente.</t>
+          <t>SÍ — llegó por la Dra. Ruilova el 12/10/2026; revisada y archivada (CV_Castillo-Cabrera_Maria-Paz.pdf). Ojo: su hoja de vida la sitúa trabajando en Ciudad de México desde junio de 2026, no en Cuenca, y no menciona ningún cargo en la Universidad de Cuenca.</t>
         </is>
       </c>
       <c r="K19" s="42" t="n"/>
@@ -3261,7 +3265,7 @@
       </c>
       <c r="B20" s="54" t="inlineStr">
         <is>
-          <t>Dr. Cristian Castillo Cabrera</t>
+          <t>Dr. Cristian Oswaldo Castillo Cabrera</t>
         </is>
       </c>
       <c r="C20" s="53" t="inlineStr">
@@ -3269,7 +3273,11 @@
           <t>Cirugía bariátrica y metabólica</t>
         </is>
       </c>
-      <c r="D20" s="53" t="n"/>
+      <c r="D20" s="53" t="inlineStr">
+        <is>
+          <t>Hospital Santa Inés — Cuenca, Ecuador</t>
+        </is>
+      </c>
       <c r="E20" s="54" t="inlineStr">
         <is>
           <t>cristiancastillodr@gmail.com</t>
@@ -3293,7 +3301,7 @@
       </c>
       <c r="J20" s="54" t="inlineStr">
         <is>
-          <t>SÍ — el archivo sigue en el correo, falta guardarlo en el expediente</t>
+          <t>SÍ — recibida el 07/10/2026 (y reenviada por la Dra. Ruilova el 12/10/2026); revisada y archivada (CV_Castillo-Cabrera_Cristian-Oswaldo.pdf)</t>
         </is>
       </c>
       <c r="K20" s="54" t="inlineStr">

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -3519,7 +3519,11 @@
           <t>M7 · C2</t>
         </is>
       </c>
-      <c r="J24" s="42" t="n"/>
+      <c r="J24" s="42" t="inlineStr">
+        <is>
+          <t>BORRADOR — la coordinación la armó el 12/10/2026 con PubMed (SEDA_HojaVida_Gomez_BORRADOR.pdf), suponiendo que es la Dra. Ana María Gómez Medina (Hospital Universitario San Ignacio, Javeriana). PENDIENTE de confirmar y de que ella la apruebe.</t>
+        </is>
+      </c>
       <c r="K24" s="42" t="n"/>
       <c r="L24" s="42" t="n"/>
       <c r="M24" s="42" t="inlineStr">

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -3493,17 +3493,17 @@
       </c>
       <c r="B24" s="52" t="inlineStr">
         <is>
-          <t>Dra. Ana María Gómez</t>
+          <t>Dra. Ana María Gómez Medina</t>
         </is>
       </c>
       <c r="C24" s="53" t="inlineStr">
         <is>
-          <t>Endocrinología · experta en monitoreo de glucosa</t>
+          <t>Medicina Interna · Endocrinología · Tecnología en diabetes</t>
         </is>
       </c>
       <c r="D24" s="53" t="inlineStr">
         <is>
-          <t>Colombia (institución y ciudad por confirmar)</t>
+          <t>Hospital Universitario San Ignacio · Pontificia Universidad Javeriana — Bogotá, Colombia</t>
         </is>
       </c>
       <c r="E24" s="41" t="n"/>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="J24" s="42" t="inlineStr">
         <is>
-          <t>BORRADOR — la coordinación la armó el 12/10/2026 con PubMed (SEDA_HojaVida_Gomez_BORRADOR.pdf), suponiendo que es la Dra. Ana María Gómez Medina (Hospital Universitario San Ignacio, Javeriana). PENDIENTE de confirmar y de que ella la apruebe.</t>
+          <t>SÍ — versión armada por la coordinación con PubMed y APROBADA por la Dra. Gómez, según la Dra. Omidres (12/10/2026). Archivada como CV_Gomez-Medina_Ana-Maria.pdf.</t>
         </is>
       </c>
       <c r="K24" s="42" t="n"/>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -3111,16 +3111,24 @@
       </c>
       <c r="B17" s="39" t="inlineStr">
         <is>
-          <t>Dra. Valeria Andrade</t>
-        </is>
-      </c>
-      <c r="C17" s="41" t="n"/>
+          <t>Dra. Andrea Valeria Andrade Izquierdo</t>
+        </is>
+      </c>
+      <c r="C17" s="41" t="inlineStr">
+        <is>
+          <t>Nefrología · Trasplante renal · PhD en Ciencias (Nefrología), Universidad de São Paulo</t>
+        </is>
+      </c>
       <c r="D17" s="41" t="inlineStr">
         <is>
-          <t>Ecuador (institución y ciudad por confirmar)</t>
-        </is>
-      </c>
-      <c r="E17" s="41" t="n"/>
+          <t>Hospital Santa Inés · Universidad de Cuenca — Cuenca, Ecuador</t>
+        </is>
+      </c>
+      <c r="E17" s="41" t="inlineStr">
+        <is>
+          <t>vale19_ec@yahoo.com</t>
+        </is>
+      </c>
       <c r="F17" s="41" t="inlineStr">
         <is>
           <t>+593 98 335 5686</t>
@@ -3133,7 +3141,11 @@
           <t>M6 · C1</t>
         </is>
       </c>
-      <c r="J17" s="42" t="n"/>
+      <c r="J17" s="42" t="inlineStr">
+        <is>
+          <t>SÍ — recibida el 12/10/2026 y archivada (CV_Andrade-Izquierdo_Andrea-Valeria.pdf). Fechada en septiembre de 2025.</t>
+        </is>
+      </c>
       <c r="K17" s="42" t="n"/>
       <c r="L17" s="42" t="n"/>
       <c r="M17" s="42" t="n"/>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -2118,7 +2118,7 @@
       </c>
       <c r="E30" s="24" t="inlineStr">
         <is>
-          <t>Dra. Omidres Pérez de Carvelli</t>
+          <t>Ing. Styp Canto</t>
         </is>
       </c>
       <c r="F30" s="27" t="inlineStr">
@@ -2226,7 +2226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
-          <t>M7 · C1  /  M7 · C4</t>
+          <t>M7 · C1</t>
         </is>
       </c>
       <c r="J4" s="54" t="inlineStr">
@@ -3656,6 +3656,52 @@
           <t>CONFIRMADO — falta toda la documentación</t>
         </is>
       </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="54" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="52" t="inlineStr">
+        <is>
+          <t>Ing. Styp Canto</t>
+        </is>
+      </c>
+      <c r="C27" s="53" t="inlineStr">
+        <is>
+          <t>Ingeniería — especialidad POR CONFIRMAR</t>
+        </is>
+      </c>
+      <c r="D27" s="53" t="inlineStr">
+        <is>
+          <t>POR CONFIRMAR</t>
+        </is>
+      </c>
+      <c r="E27" s="41" t="inlineStr">
+        <is>
+          <t>styp611@outlook.com</t>
+        </is>
+      </c>
+      <c r="F27" s="41" t="n"/>
+      <c r="G27" s="41" t="n"/>
+      <c r="H27" s="41" t="n"/>
+      <c r="I27" s="54" t="inlineStr">
+        <is>
+          <t>M7 · C4</t>
+        </is>
+      </c>
+      <c r="J27" s="42" t="n"/>
+      <c r="K27" s="42" t="n"/>
+      <c r="L27" s="42" t="inlineStr">
+        <is>
+          <t>PENDIENTE — debe declarar su vínculo profesional con la Dra. Omidres (MEDDI)</t>
+        </is>
+      </c>
+      <c r="M27" s="42" t="inlineStr">
+        <is>
+          <t>03/12/2026</t>
+        </is>
+      </c>
+      <c r="N27" s="65" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -3928,17 +3974,17 @@
       </c>
       <c r="E9" s="41" t="inlineStr">
         <is>
-          <t>Dra. Omidres Pérez de Carvelli</t>
+          <t>Ing. Styp Canto</t>
         </is>
       </c>
       <c r="F9" s="41" t="inlineStr">
         <is>
-          <t>info@draomidresperez.com</t>
+          <t>styp611@outlook.com · WhatsApp POR CONFIRMAR</t>
         </is>
       </c>
       <c r="G9" s="41" t="inlineStr">
         <is>
-          <t>CUBIERTA — la asume la Dra. Omidres (23/09/2026)</t>
+          <t>CUBIERTA — aceptó el 12/10/2026. La Dra. Omidres la tenía desde el 23/09 y se la cedió; ella conserva M7 · C1.</t>
         </is>
       </c>
     </row>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -2118,7 +2118,7 @@
       </c>
       <c r="E30" s="24" t="inlineStr">
         <is>
-          <t>Ing. Styp Canto</t>
+          <t>Ing. Styp Canto Rondón</t>
         </is>
       </c>
       <c r="F30" s="27" t="inlineStr">
@@ -3663,17 +3663,17 @@
       </c>
       <c r="B27" s="52" t="inlineStr">
         <is>
-          <t>Ing. Styp Canto</t>
+          <t>Ing. Styp Bill Roy Canto Rondón</t>
         </is>
       </c>
       <c r="C27" s="53" t="inlineStr">
         <is>
-          <t>Ingeniería — especialidad POR CONFIRMAR</t>
+          <t>Ingeniería de Telecomunicaciones · TI en salud, telemedicina e interoperabilidad (HL7 FHIR)</t>
         </is>
       </c>
       <c r="D27" s="53" t="inlineStr">
         <is>
-          <t>POR CONFIRMAR</t>
+          <t>Centro Nacional de Telemedicina (CENATE) – EsSalud · Lima, Perú</t>
         </is>
       </c>
       <c r="E27" s="41" t="inlineStr">
@@ -3681,19 +3681,31 @@
           <t>styp611@outlook.com</t>
         </is>
       </c>
-      <c r="F27" s="41" t="n"/>
+      <c r="F27" s="41" t="inlineStr">
+        <is>
+          <t>+51 956 194 180</t>
+        </is>
+      </c>
       <c r="G27" s="41" t="n"/>
-      <c r="H27" s="41" t="n"/>
+      <c r="H27" s="41" t="inlineStr">
+        <is>
+          <t>CIP 131278 (Colegio de Ingenieros del Perú)</t>
+        </is>
+      </c>
       <c r="I27" s="54" t="inlineStr">
         <is>
           <t>M7 · C4</t>
         </is>
       </c>
-      <c r="J27" s="42" t="n"/>
+      <c r="J27" s="42" t="inlineStr">
+        <is>
+          <t>PARCIAL — el contenido llegó pegado como texto el 12/10/2026; falta el archivo PDF o Word para el expediente</t>
+        </is>
+      </c>
       <c r="K27" s="42" t="n"/>
       <c r="L27" s="42" t="inlineStr">
         <is>
-          <t>PENDIENTE — debe declarar su vínculo profesional con la Dra. Omidres (MEDDI)</t>
+          <t>PENDIENTE — debe declarar: vínculo profesional con la Dra. Omidres en MEDDI Hub (su CV dice consultor 02/2022–12/2023, pero en 09/2026 usa styp@meddi.com: POR CONFIRMAR si sigue) y que es miembro vocal y fundador de la OITT, que preside la Dra. Omidres</t>
         </is>
       </c>
       <c r="M27" s="42" t="inlineStr">
@@ -3701,7 +3713,11 @@
           <t>03/12/2026</t>
         </is>
       </c>
-      <c r="N27" s="65" t="n"/>
+      <c r="N27" s="65" t="inlineStr">
+        <is>
+          <t>CONFIRMADO — aceptó el 12/10/2026</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -3974,12 +3990,12 @@
       </c>
       <c r="E9" s="41" t="inlineStr">
         <is>
-          <t>Ing. Styp Canto</t>
+          <t>Ing. Styp Canto Rondón — ingeniero en TI en salud, CENATE-EsSalud, Perú</t>
         </is>
       </c>
       <c r="F9" s="41" t="inlineStr">
         <is>
-          <t>styp611@outlook.com · WhatsApp POR CONFIRMAR</t>
+          <t>+51 956 194 180 · styp611@outlook.com</t>
         </is>
       </c>
       <c r="G9" s="41" t="inlineStr">

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -3705,7 +3705,7 @@
       <c r="K27" s="42" t="n"/>
       <c r="L27" s="42" t="inlineStr">
         <is>
-          <t>PENDIENTE — debe declarar: vínculo profesional con la Dra. Omidres en MEDDI Hub (su CV dice consultor 02/2022–12/2023, pero en 09/2026 usa styp@meddi.com: POR CONFIRMAR si sigue) y que es miembro vocal y fundador de la OITT, que preside la Dra. Omidres</t>
+          <t>PENDIENTE — debe declarar: (1) consultor externo vigente de MEDDI Hub, empresa en la que la Dra. Omidres es CMO LATAM; (2) miembro vocal y fundador de la OITT, que preside la Dra. Omidres. Sin vínculo con Omisalud (confirmado por la Dra. Omidres el 12/10/2026)</t>
         </is>
       </c>
       <c r="M27" s="42" t="inlineStr">

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -3699,7 +3699,7 @@
       </c>
       <c r="J27" s="42" t="inlineStr">
         <is>
-          <t>PARCIAL — el contenido llegó pegado como texto el 12/10/2026; falta el archivo PDF o Word para el expediente</t>
+          <t>PENDIENTE de aprobación — su PDF pesa demasiado; la coordinación armó SEDA_HojaVida_Canto_REVISION con su texto (12/10/2026). Cuenta cuando él la apruebe</t>
         </is>
       </c>
       <c r="K27" s="42" t="n"/>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -3699,7 +3699,7 @@
       </c>
       <c r="J27" s="42" t="inlineStr">
         <is>
-          <t>PENDIENTE de aprobación — su PDF pesa demasiado; la coordinación armó SEDA_HojaVida_Canto_REVISION con su texto (12/10/2026). Cuenta cuando él la apruebe</t>
+          <t>SÍ — llegó la versión original sin respaldos (10 páginas, 300 KB) el 12/10/2026 y se archivó como CV_Canto-Rondon_Styp-Bill-Roy.pdf. La versión armada por la coordinación ya no hace falta</t>
         </is>
       </c>
       <c r="K27" s="42" t="n"/>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -3143,7 +3143,7 @@
       </c>
       <c r="J17" s="42" t="inlineStr">
         <is>
-          <t>SÍ — recibida el 12/10/2026 y archivada (CV_Andrade-Izquierdo_Andrea-Valeria.pdf). Fechada en septiembre de 2025.</t>
+          <t>SÍ — versión actualizada 2026 recibida el 12/10/2026 y archivada como CV_Andrade-Izquierdo_Andrea-Valeria.pdf (reemplaza la de sept. 2025: ahora Presidenta de la Sociedad de Nefrología del Austro)</t>
         </is>
       </c>
       <c r="K17" s="42" t="n"/>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -1747,10 +1747,14 @@
           <t>Dieta mediterránea; restricción de carbohidratos; ayuno intermitente</t>
         </is>
       </c>
-      <c r="E20" s="28" t="inlineStr"/>
+      <c r="E20" s="28" t="inlineStr">
+        <is>
+          <t>Lcda. Isabel Reinoso</t>
+        </is>
+      </c>
       <c r="F20" s="29" t="inlineStr">
         <is>
-          <t>VACANTE</t>
+          <t>CONFIRMADO</t>
         </is>
       </c>
       <c r="G20" s="23" t="n">
@@ -2438,7 +2442,7 @@
       <c r="H5" s="41" t="n"/>
       <c r="I5" s="40" t="inlineStr">
         <is>
-          <t>M2 · C1</t>
+          <t>M2 · C1  /  M5 · C2</t>
         </is>
       </c>
       <c r="J5" s="54" t="inlineStr">
@@ -3750,7 +3754,7 @@
     <row r="1">
       <c r="A1" s="20" t="inlineStr">
         <is>
-          <t>CLASES QUE QUEDARON SIN PONENTE · Queda 1 vacante: M5 · C2 (al 09/10/2026)</t>
+          <t>CLASES QUE QUEDARON SIN PONENTE · No quedan vacantes: M5 · C2 asignada a la Lcda. Isabel Reinoso (13/10/2026)</t>
         </is>
       </c>
     </row>
@@ -3854,13 +3858,17 @@
       </c>
       <c r="E5" s="41" t="inlineStr">
         <is>
-          <t>SIN CANDIDATO — VACANTE</t>
-        </is>
-      </c>
-      <c r="F5" s="41" t="n"/>
+          <t>Lcda. María Isabel Reinoso Pesántez</t>
+        </is>
+      </c>
+      <c r="F5" s="41" t="inlineStr">
+        <is>
+          <t>+593 98 736 8816</t>
+        </is>
+      </c>
       <c r="G5" s="41" t="inlineStr">
         <is>
-          <t>VACANTE. Declinaron la Dra. Gaby Villavicencio (recomendó a otras personas; se les escribió y no respondieron al 12/10/2026), la Carrera de Nutrición de la U. Cuenca (recibió los temas el 23/09 y no tomó este) y la Lcda. María Augusta Vásquez (05/10). Se mantiene vacante por decisión de la Dra. Omidres. No volver a contactar a esas tres para este tema.</t>
+          <t>CUBIERTA — asignada por la Dra. Omidres el 13/10/2026, con enfoque en diabetes para no repetir M2 · C2. Antes declinaron la Dra. Villavicencio, la Carrera de Nutrición de la U. Cuenca y la Lcda. Vásquez.</t>
         </is>
       </c>
     </row>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -1747,14 +1747,10 @@
           <t>Dieta mediterránea; restricción de carbohidratos; ayuno intermitente</t>
         </is>
       </c>
-      <c r="E20" s="28" t="inlineStr">
-        <is>
-          <t>Lcda. Isabel Reinoso</t>
-        </is>
-      </c>
+      <c r="E20" s="28" t="n"/>
       <c r="F20" s="29" t="inlineStr">
         <is>
-          <t>CONFIRMADO</t>
+          <t>VACANTE</t>
         </is>
       </c>
       <c r="G20" s="23" t="n">
@@ -2442,7 +2438,7 @@
       <c r="H5" s="41" t="n"/>
       <c r="I5" s="40" t="inlineStr">
         <is>
-          <t>M2 · C1  /  M5 · C2</t>
+          <t>M2 · C1</t>
         </is>
       </c>
       <c r="J5" s="54" t="inlineStr">
@@ -3754,7 +3750,7 @@
     <row r="1">
       <c r="A1" s="20" t="inlineStr">
         <is>
-          <t>CLASES QUE QUEDARON SIN PONENTE · No quedan vacantes: M5 · C2 asignada a la Lcda. Isabel Reinoso (13/10/2026)</t>
+          <t>CLASES QUE QUEDARON SIN PONENTE · Queda 1 vacante: M5 · C2 (al 13/10/2026)</t>
         </is>
       </c>
     </row>
@@ -3858,17 +3854,13 @@
       </c>
       <c r="E5" s="41" t="inlineStr">
         <is>
-          <t>Lcda. María Isabel Reinoso Pesántez</t>
-        </is>
-      </c>
-      <c r="F5" s="41" t="inlineStr">
-        <is>
-          <t>+593 98 736 8816</t>
-        </is>
-      </c>
+          <t>SIN CANDIDATO — VACANTE</t>
+        </is>
+      </c>
+      <c r="F5" s="41" t="n"/>
       <c r="G5" s="41" t="inlineStr">
         <is>
-          <t>CUBIERTA — asignada por la Dra. Omidres el 13/10/2026, con enfoque en diabetes para no repetir M2 · C2. Antes declinaron la Dra. Villavicencio, la Carrera de Nutrición de la U. Cuenca y la Lcda. Vásquez.</t>
+          <t>VACANTE. Declinaron la Dra. Villavicencio, la Carrera de Nutrición de la U. Cuenca, la Lcda. Vásquez y la Lcda. Isabel Reinoso (13/10/2026). Las personas que recomendó la Dra. Villavicencio no respondieron.</t>
         </is>
       </c>
     </row>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -3854,13 +3854,13 @@
       </c>
       <c r="E5" s="41" t="inlineStr">
         <is>
-          <t>SIN CANDIDATO — VACANTE</t>
+          <t>Dr. Ramón de Cangas — propuesto por la Dra. Omidres (13/10/2026), invitación por enviar</t>
         </is>
       </c>
       <c r="F5" s="41" t="n"/>
       <c r="G5" s="41" t="inlineStr">
         <is>
-          <t>VACANTE. Declinaron la Dra. Villavicencio, la Carrera de Nutrición de la U. Cuenca, la Lcda. Vásquez y la Lcda. Isabel Reinoso (13/10/2026). Las personas que recomendó la Dra. Villavicencio no respondieron.</t>
+          <t>VACANTE. Declinaron la Dra. Villavicencio, la Carrera de Nutrición de la U. Cuenca, la Lcda. Vásquez, la Lcda. Isabel Reinoso y la Dra. Johanna Piedra (13/10/2026). Las personas que recomendó la Dra. Villavicencio no respondieron.</t>
         </is>
       </c>
     </row>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -1747,10 +1747,14 @@
           <t>Dieta mediterránea; restricción de carbohidratos; ayuno intermitente</t>
         </is>
       </c>
-      <c r="E20" s="28" t="n"/>
+      <c r="E20" s="28" t="inlineStr">
+        <is>
+          <t>Dr. Ramón de Cangas Morán</t>
+        </is>
+      </c>
       <c r="F20" s="29" t="inlineStr">
         <is>
-          <t>VACANTE</t>
+          <t>CONFIRMADO</t>
         </is>
       </c>
       <c r="G20" s="23" t="n">
@@ -2226,7 +2230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3716,6 +3720,56 @@
       <c r="N27" s="65" t="inlineStr">
         <is>
           <t>CONFIRMADO — aceptó el 12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="54" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="52" t="inlineStr">
+        <is>
+          <t>Dr. Ramón de Cangas Morán</t>
+        </is>
+      </c>
+      <c r="C28" s="53" t="inlineStr">
+        <is>
+          <t>Dietista-nutricionista · Biología · Doctor en Biología Funcional y Molecular</t>
+        </is>
+      </c>
+      <c r="D28" s="53" t="inlineStr">
+        <is>
+          <t>Clínicas Nutrigroup · Fundación Alimenta Tu Salud — Oviedo, España</t>
+        </is>
+      </c>
+      <c r="E28" s="41" t="n"/>
+      <c r="F28" s="41" t="n"/>
+      <c r="G28" s="41" t="n"/>
+      <c r="H28" s="41" t="n"/>
+      <c r="I28" s="54" t="inlineStr">
+        <is>
+          <t>M5 · C2</t>
+        </is>
+      </c>
+      <c r="J28" s="42" t="inlineStr">
+        <is>
+          <t>SÍ — resumen curricular armado por la coordinación y aprobado (13/10/2026); archivado como CV_de-Cangas-Moran_Ramon.pdf</t>
+        </is>
+      </c>
+      <c r="K28" s="42" t="n"/>
+      <c r="L28" s="42" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M28" s="42" t="inlineStr">
+        <is>
+          <t>Jueves 19 de noviembre de 2026</t>
+        </is>
+      </c>
+      <c r="N28" s="65" t="inlineStr">
+        <is>
+          <t>CONFIRMADO — aceptó el 13/10/2026</t>
         </is>
       </c>
     </row>
@@ -3750,7 +3804,7 @@
     <row r="1">
       <c r="A1" s="20" t="inlineStr">
         <is>
-          <t>CLASES QUE QUEDARON SIN PONENTE · Queda 1 vacante: M5 · C2 (al 13/10/2026)</t>
+          <t>CLASES QUE QUEDARON SIN PONENTE · No quedan vacantes (13/10/2026)</t>
         </is>
       </c>
     </row>
@@ -3854,13 +3908,17 @@
       </c>
       <c r="E5" s="41" t="inlineStr">
         <is>
-          <t>Dr. Ramón de Cangas — propuesto por la Dra. Omidres (13/10/2026), invitación por enviar</t>
-        </is>
-      </c>
-      <c r="F5" s="41" t="n"/>
+          <t>Dr. Ramón de Cangas Morán — dietista-nutricionista, Oviedo (España)</t>
+        </is>
+      </c>
+      <c r="F5" s="41" t="inlineStr">
+        <is>
+          <t>POR CONFIRMAR</t>
+        </is>
+      </c>
       <c r="G5" s="41" t="inlineStr">
         <is>
-          <t>VACANTE. Declinaron la Dra. Villavicencio, la Carrera de Nutrición de la U. Cuenca, la Lcda. Vásquez, la Lcda. Isabel Reinoso y la Dra. Johanna Piedra (13/10/2026). Las personas que recomendó la Dra. Villavicencio no respondieron.</t>
+          <t>CUBIERTA — aceptó el 13/10/2026. Antes declinaron la Dra. Villavicencio, la Carrera de Nutrición de la U. Cuenca, la Lcda. Vásquez, la Lcda. Isabel Reinoso y la Dra. Johanna Piedra.</t>
         </is>
       </c>
     </row>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -2969,7 +2969,7 @@
       </c>
       <c r="J14" s="54" t="inlineStr">
         <is>
-          <t>SÍ — el archivo sigue en el correo, falta guardarlo en el expediente</t>
+          <t>SÍ — recibida y archivada el 13/10/2026 (CV_Astudillo-Calle_Maria-Augusta.docx, fechada octubre 2024)</t>
         </is>
       </c>
       <c r="K14" s="54" t="inlineStr">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="D21" s="54" t="inlineStr">
         <is>
-          <t>Instituto Ecuatoriano de Seguridad Social (IESS) — Cuenca, Ecuador</t>
+          <t>Hospital de Especialidades José Carrasco Arteaga (IESS) — Cuenca, Ecuador</t>
         </is>
       </c>
       <c r="E21" s="54" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="J21" s="54" t="inlineStr">
         <is>
-          <t>SÍ — el archivo sigue en el correo, falta guardarlo en el expediente</t>
+          <t>SÍ — recibida y archivada el 13/10/2026 (CV_Castro-de-Gonzalez_Julia.pdf)</t>
         </is>
       </c>
       <c r="K21" s="54" t="inlineStr">
@@ -3475,12 +3475,24 @@
       </c>
       <c r="B23" s="52" t="inlineStr">
         <is>
-          <t>Dra. Gabriela Machado</t>
-        </is>
-      </c>
-      <c r="C23" s="53" t="n"/>
-      <c r="D23" s="53" t="n"/>
-      <c r="E23" s="41" t="n"/>
+          <t>Dra. María Gabriela Machado Orellana</t>
+        </is>
+      </c>
+      <c r="C23" s="53" t="inlineStr">
+        <is>
+          <t>Medicina · Nutrición clínica · Máster en Nutrición y Metabolismo (Universitat de Barcelona)</t>
+        </is>
+      </c>
+      <c r="D23" s="53" t="inlineStr">
+        <is>
+          <t>Consultorios Arupo · docente de la Facultad de Ciencias Médicas, Universidad de Cuenca — Cuenca, Ecuador</t>
+        </is>
+      </c>
+      <c r="E23" s="41" t="inlineStr">
+        <is>
+          <t>gabi_machado25@hotmail.com</t>
+        </is>
+      </c>
       <c r="F23" s="41" t="inlineStr">
         <is>
           <t>+593 99 502 5774</t>
@@ -3493,7 +3505,11 @@
           <t>M5 · C3</t>
         </is>
       </c>
-      <c r="J23" s="42" t="n"/>
+      <c r="J23" s="42" t="inlineStr">
+        <is>
+          <t>SÍ — recibida y archivada el 13/10/2026 (CV_Machado-Orellana_Maria-Gabriela.pdf, versión 2022)</t>
+        </is>
+      </c>
       <c r="K23" s="42" t="n"/>
       <c r="L23" s="42" t="n"/>
       <c r="M23" s="42" t="n"/>
@@ -3759,7 +3775,7 @@
       <c r="K28" s="42" t="n"/>
       <c r="L28" s="42" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>PENDIENTE — sin conflicto, según la Dra. Omidres (13/10/2026); no lo exige la Universidad</t>
         </is>
       </c>
       <c r="M28" s="42" t="inlineStr">

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -1453,7 +1453,7 @@
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>Dr. Frank Espinoza</t>
+          <t>Dra. Omidres Pérez de Carvelli</t>
         </is>
       </c>
       <c r="F12" s="27" t="inlineStr">
@@ -2230,7 +2230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N28"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
-          <t>M7 · C1</t>
+          <t>M3 · C2  /  M7 · C1</t>
         </is>
       </c>
       <c r="J4" s="54" t="inlineStr">
@@ -2539,30 +2539,46 @@
       </c>
       <c r="B7" s="39" t="inlineStr">
         <is>
-          <t>Dr. Frank Espinoza</t>
-        </is>
-      </c>
-      <c r="C7" s="41" t="n"/>
-      <c r="D7" s="41" t="inlineStr">
-        <is>
-          <t>Perú (institución y ciudad por confirmar)</t>
-        </is>
-      </c>
-      <c r="E7" s="41" t="n"/>
+          <t>Dra. E. Teresa Cuatecontzi Xochitiotzi</t>
+        </is>
+      </c>
+      <c r="C7" s="41" t="inlineStr">
+        <is>
+          <t>Medicina Interna · Endocrinología · Alta especialidad en Obesidad · Maestría en Ciencias Médicas y Nutrición (INCMNSZ/UNAM)</t>
+        </is>
+      </c>
+      <c r="D7" s="53" t="inlineStr">
+        <is>
+          <t>Clínica Especializada en el Manejo de la Diabetes — Ciudad de México, México</t>
+        </is>
+      </c>
+      <c r="E7" s="41" t="inlineStr">
+        <is>
+          <t>xochitiotzi1@gmail.com</t>
+        </is>
+      </c>
       <c r="F7" s="41" t="inlineStr">
         <is>
-          <t>+51 936 260 715</t>
+          <t>+52 1 55 5405 6619</t>
         </is>
       </c>
       <c r="G7" s="41" t="n"/>
       <c r="H7" s="41" t="n"/>
       <c r="I7" s="40" t="inlineStr">
         <is>
-          <t>M3 · C2</t>
-        </is>
-      </c>
-      <c r="J7" s="42" t="n"/>
-      <c r="K7" s="42" t="n"/>
+          <t>M3 · C3</t>
+        </is>
+      </c>
+      <c r="J7" s="42" t="inlineStr">
+        <is>
+          <t>SÍ — recibida el 11/10/2026 y archivada (CV_Cuatecontzi-Xochitiotzi_Teresa.pdf). En el encabezado dice «TERES» por «TERESA».</t>
+        </is>
+      </c>
+      <c r="K7" s="42" t="inlineStr">
+        <is>
+          <t>SÍ — recibida el 11/10/2026 (441×478 px, retrato profesional), archivada como Foto_Cuatecontzi-Xochitiotzi_Teresa.jpg</t>
+        </is>
+      </c>
       <c r="L7" s="42" t="n"/>
       <c r="M7" s="42" t="n"/>
       <c r="N7" s="43" t="inlineStr">
@@ -2575,46 +2591,46 @@
       <c r="A8" s="38" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="39" t="inlineStr">
-        <is>
-          <t>Dra. E. Teresa Cuatecontzi Xochitiotzi</t>
-        </is>
-      </c>
-      <c r="C8" s="41" t="inlineStr">
-        <is>
-          <t>Medicina Interna · Endocrinología · Alta especialidad en Obesidad · Maestría en Ciencias Médicas y Nutrición (INCMNSZ/UNAM)</t>
+      <c r="B8" s="52" t="inlineStr">
+        <is>
+          <t>Dra. Josefa Elizabeth Palacio Riofrío</t>
+        </is>
+      </c>
+      <c r="C8" s="53" t="inlineStr">
+        <is>
+          <t>Endocrinología · Diabetes y Metabolismo</t>
         </is>
       </c>
       <c r="D8" s="53" t="inlineStr">
         <is>
-          <t>Clínica Especializada en el Manejo de la Diabetes — Ciudad de México, México</t>
-        </is>
-      </c>
-      <c r="E8" s="41" t="inlineStr">
-        <is>
-          <t>xochitiotzi1@gmail.com</t>
-        </is>
-      </c>
-      <c r="F8" s="41" t="inlineStr">
-        <is>
-          <t>+52 1 55 5405 6619</t>
-        </is>
-      </c>
-      <c r="G8" s="41" t="n"/>
+          <t>Omni Hospital e Interhospital · Guayaquil, Ecuador</t>
+        </is>
+      </c>
+      <c r="E8" s="41" t="n"/>
+      <c r="F8" s="53" t="inlineStr">
+        <is>
+          <t>+593 96 816 1654</t>
+        </is>
+      </c>
+      <c r="G8" s="53" t="inlineStr">
+        <is>
+          <t>1103520233</t>
+        </is>
+      </c>
       <c r="H8" s="41" t="n"/>
       <c r="I8" s="40" t="inlineStr">
         <is>
-          <t>M3 · C3</t>
-        </is>
-      </c>
-      <c r="J8" s="42" t="inlineStr">
-        <is>
-          <t>SÍ — recibida el 11/10/2026 y archivada (CV_Cuatecontzi-Xochitiotzi_Teresa.pdf). En el encabezado dice «TERES» por «TERESA».</t>
-        </is>
-      </c>
-      <c r="K8" s="42" t="inlineStr">
-        <is>
-          <t>SÍ — recibida el 11/10/2026 (441×478 px, retrato profesional), archivada como Foto_Cuatecontzi-Xochitiotzi_Teresa.jpg</t>
+          <t>M4 · C2</t>
+        </is>
+      </c>
+      <c r="J8" s="54" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="K8" s="54" t="inlineStr">
+        <is>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="L8" s="42" t="n"/>
@@ -2631,34 +2647,38 @@
       </c>
       <c r="B9" s="52" t="inlineStr">
         <is>
-          <t>Dra. Josefa Elizabeth Palacio Riofrío</t>
+          <t>Dr. Chih Hao Chen Ku, M.Sc.</t>
         </is>
       </c>
       <c r="C9" s="53" t="inlineStr">
         <is>
-          <t>Endocrinología · Diabetes y Metabolismo</t>
+          <t>Endocrinología · Farmacología</t>
         </is>
       </c>
       <c r="D9" s="53" t="inlineStr">
         <is>
-          <t>Omni Hospital e Interhospital · Guayaquil, Ecuador</t>
-        </is>
-      </c>
-      <c r="E9" s="41" t="n"/>
-      <c r="F9" s="53" t="inlineStr">
-        <is>
-          <t>+593 96 816 1654</t>
-        </is>
-      </c>
-      <c r="G9" s="53" t="inlineStr">
-        <is>
-          <t>1103520233</t>
+          <t>Clínica Los Yoses · San José, Costa Rica</t>
+        </is>
+      </c>
+      <c r="E9" s="60" t="inlineStr">
+        <is>
+          <t>chenku2409@gmail.com</t>
+        </is>
+      </c>
+      <c r="F9" s="60" t="inlineStr">
+        <is>
+          <t>+506 8392 7083</t>
+        </is>
+      </c>
+      <c r="G9" s="54" t="inlineStr">
+        <is>
+          <t>Pasaporte de Costa Rica (copia en expediente)</t>
         </is>
       </c>
       <c r="H9" s="41" t="n"/>
       <c r="I9" s="40" t="inlineStr">
         <is>
-          <t>M4 · C2</t>
+          <t>M6 · C2  /  M6 · C3</t>
         </is>
       </c>
       <c r="J9" s="54" t="inlineStr">
@@ -2671,8 +2691,16 @@
           <t>SÍ</t>
         </is>
       </c>
-      <c r="L9" s="42" t="n"/>
-      <c r="M9" s="42" t="n"/>
+      <c r="L9" s="42" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="M9" s="42" t="inlineStr">
+        <is>
+          <t>26/11/2026</t>
+        </is>
+      </c>
       <c r="N9" s="43" t="inlineStr">
         <is>
           <t>CONFIRMADO</t>
@@ -2683,55 +2711,51 @@
       <c r="A10" s="38" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="52" t="inlineStr">
-        <is>
-          <t>Dr. Chih Hao Chen Ku, M.Sc.</t>
-        </is>
-      </c>
-      <c r="C10" s="53" t="inlineStr">
-        <is>
-          <t>Endocrinología · Farmacología</t>
-        </is>
-      </c>
-      <c r="D10" s="53" t="inlineStr">
-        <is>
-          <t>Clínica Los Yoses · San José, Costa Rica</t>
-        </is>
-      </c>
-      <c r="E10" s="60" t="inlineStr">
-        <is>
-          <t>chenku2409@gmail.com</t>
-        </is>
-      </c>
-      <c r="F10" s="60" t="inlineStr">
-        <is>
-          <t>+506 8392 7083</t>
-        </is>
-      </c>
-      <c r="G10" s="54" t="inlineStr">
-        <is>
-          <t>Pasaporte de Costa Rica (copia en expediente)</t>
+      <c r="B10" s="39" t="inlineStr">
+        <is>
+          <t>Dra. Adriana Mabel Álvarez</t>
+        </is>
+      </c>
+      <c r="C10" s="41" t="inlineStr">
+        <is>
+          <t>Endocrinología · Comité de Esteatosis Hepática Metabólica (SAD) · Coordinadora del Grupo Obesidad-MASH de ALAD · Vocal Región Sur de ALAD</t>
+        </is>
+      </c>
+      <c r="D10" s="41" t="inlineStr">
+        <is>
+          <t>Hospital Italiano de Buenos Aires · Buenos Aires, Argentina</t>
+        </is>
+      </c>
+      <c r="E10" s="41" t="n"/>
+      <c r="F10" s="41" t="inlineStr">
+        <is>
+          <t>+54 9 11 6708-1708</t>
+        </is>
+      </c>
+      <c r="G10" s="41" t="inlineStr">
+        <is>
+          <t>Pasaporte AAI843846 (vence 28/03/2033) · DNI 14.456.727 — copia archivada el 10/10/2026; los cinco dígitos de control de la zona de lectura mecánica son correctos y coinciden con estos datos</t>
         </is>
       </c>
       <c r="H10" s="41" t="n"/>
       <c r="I10" s="40" t="inlineStr">
         <is>
-          <t>M6 · C2  /  M6 · C3</t>
-        </is>
-      </c>
-      <c r="J10" s="54" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
-      <c r="K10" s="54" t="inlineStr">
-        <is>
-          <t>SÍ</t>
+          <t>M6 · C4 (MASLD y complicaciones metabólicas)</t>
+        </is>
+      </c>
+      <c r="J10" s="42" t="inlineStr">
+        <is>
+          <t>SÍ — versión final cerrada por la coordinación el 10/10/2026 y APROBADA por la Dra. Álvarez, según la Dra. Omidres (10/10/2026). Archivada como CV_Alvarez_Adriana-Mabel.pdf. Incluye cinco publicaciones firmadas «Alvarez A» que ella da por suyas al aprobarla.</t>
+        </is>
+      </c>
+      <c r="K10" s="42" t="inlineStr">
+        <is>
+          <t>PARCIAL — solo la del pasaporte</t>
         </is>
       </c>
       <c r="L10" s="42" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>PENDIENTE — declaró sin conflicto de palabra; falta el formato firmado</t>
         </is>
       </c>
       <c r="M10" s="42" t="inlineStr">
@@ -2741,7 +2765,7 @@
       </c>
       <c r="N10" s="43" t="inlineStr">
         <is>
-          <t>CONFIRMADO</t>
+          <t>CONFIRMADO — faltan hoja de vida, foto profesional y COI firmada</t>
         </is>
       </c>
     </row>
@@ -2749,61 +2773,57 @@
       <c r="A11" s="38" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="39" t="inlineStr">
-        <is>
-          <t>Dra. Adriana Mabel Álvarez</t>
-        </is>
-      </c>
-      <c r="C11" s="41" t="inlineStr">
-        <is>
-          <t>Endocrinología · Comité de Esteatosis Hepática Metabólica (SAD) · Coordinadora del Grupo Obesidad-MASH de ALAD · Vocal Región Sur de ALAD</t>
-        </is>
-      </c>
-      <c r="D11" s="41" t="inlineStr">
-        <is>
-          <t>Hospital Italiano de Buenos Aires · Buenos Aires, Argentina</t>
-        </is>
-      </c>
-      <c r="E11" s="41" t="n"/>
-      <c r="F11" s="41" t="inlineStr">
-        <is>
-          <t>+54 9 11 6708-1708</t>
-        </is>
-      </c>
-      <c r="G11" s="41" t="inlineStr">
-        <is>
-          <t>Pasaporte AAI843846 (vence 28/03/2033) · DNI 14.456.727 — copia archivada el 10/10/2026; los cinco dígitos de control de la zona de lectura mecánica son correctos y coinciden con estos datos</t>
-        </is>
-      </c>
+      <c r="B11" s="52" t="inlineStr">
+        <is>
+          <t>Dra. Lizbet Yolanda Ruilova González</t>
+        </is>
+      </c>
+      <c r="C11" s="53" t="inlineStr">
+        <is>
+          <t>Endocrinología · Medicina Interna</t>
+        </is>
+      </c>
+      <c r="D11" s="54" t="inlineStr">
+        <is>
+          <t>SOLCA Cuenca · Hospital Monte Sinaí · Universidad de Cuenca</t>
+        </is>
+      </c>
+      <c r="E11" s="54" t="inlineStr">
+        <is>
+          <t>lizrg@hotmail.com</t>
+        </is>
+      </c>
+      <c r="F11" s="60" t="inlineStr">
+        <is>
+          <t>+593 99 907 3471</t>
+        </is>
+      </c>
+      <c r="G11" s="41" t="n"/>
       <c r="H11" s="41" t="n"/>
       <c r="I11" s="40" t="inlineStr">
         <is>
-          <t>M6 · C4 (MASLD y complicaciones metabólicas)</t>
-        </is>
-      </c>
-      <c r="J11" s="42" t="inlineStr">
-        <is>
-          <t>SÍ — versión final cerrada por la coordinación el 10/10/2026 y APROBADA por la Dra. Álvarez, según la Dra. Omidres (10/10/2026). Archivada como CV_Alvarez_Adriana-Mabel.pdf. Incluye cinco publicaciones firmadas «Alvarez A» que ella da por suyas al aprobarla.</t>
-        </is>
-      </c>
-      <c r="K11" s="42" t="inlineStr">
-        <is>
-          <t>PARCIAL — solo la del pasaporte</t>
-        </is>
-      </c>
-      <c r="L11" s="42" t="inlineStr">
-        <is>
-          <t>PENDIENTE — declaró sin conflicto de palabra; falta el formato firmado</t>
-        </is>
-      </c>
-      <c r="M11" s="42" t="inlineStr">
-        <is>
-          <t>26/11/2026</t>
-        </is>
-      </c>
-      <c r="N11" s="43" t="inlineStr">
-        <is>
-          <t>CONFIRMADO — faltan hoja de vida, foto profesional y COI firmada</t>
+          <t>M1 · C1  /  M5 · C4</t>
+        </is>
+      </c>
+      <c r="J11" s="54" t="inlineStr">
+        <is>
+          <t>SÍ — archivada (CV_Ruilova-Gonzalez_Lizbet.pdf). La «actualizada» que reenvió el 12/10/2026 tiene el mismo contenido.</t>
+        </is>
+      </c>
+      <c r="K11" s="54" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="L11" s="54" t="inlineStr">
+        <is>
+          <t>EN BLANCO — el formato llegó sin llenar, sin casilla marcada y sin firma. Debe rehacerla.</t>
+        </is>
+      </c>
+      <c r="M11" s="42" t="n"/>
+      <c r="N11" s="44" t="inlineStr">
+        <is>
+          <t>CONFIRMADO</t>
         </is>
       </c>
     </row>
@@ -2811,41 +2831,45 @@
       <c r="A12" s="38" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="52" t="inlineStr">
-        <is>
-          <t>Dra. Lizbet Yolanda Ruilova González</t>
-        </is>
-      </c>
-      <c r="C12" s="53" t="inlineStr">
-        <is>
-          <t>Endocrinología · Medicina Interna</t>
+      <c r="B12" s="54" t="inlineStr">
+        <is>
+          <t>Dr. Pablo Esteban Vanegas Cedillo</t>
+        </is>
+      </c>
+      <c r="C12" s="54" t="inlineStr">
+        <is>
+          <t>Medicina Interna · Endocrinología · Obesidad y Trastornos de la Conducta Alimentaria</t>
         </is>
       </c>
       <c r="D12" s="54" t="inlineStr">
         <is>
-          <t>SOLCA Cuenca · Hospital Monte Sinaí · Universidad de Cuenca</t>
+          <t>Hospital Santa Inés — Cuenca, Ecuador</t>
         </is>
       </c>
       <c r="E12" s="54" t="inlineStr">
         <is>
-          <t>lizrg@hotmail.com</t>
+          <t>pablo.vanegas90@gmail.com</t>
         </is>
       </c>
       <c r="F12" s="60" t="inlineStr">
         <is>
-          <t>+593 99 907 3471</t>
-        </is>
-      </c>
-      <c r="G12" s="41" t="n"/>
+          <t>+593 98 765 3136</t>
+        </is>
+      </c>
+      <c r="G12" s="54" t="inlineStr">
+        <is>
+          <t>0103838058 — leída de la cédula y contrastada con su declaración y su hoja de vida: coinciden</t>
+        </is>
+      </c>
       <c r="H12" s="41" t="n"/>
       <c r="I12" s="40" t="inlineStr">
         <is>
-          <t>M1 · C1  /  M5 · C4</t>
+          <t>M1 · C2  /  M3 · C1</t>
         </is>
       </c>
       <c r="J12" s="54" t="inlineStr">
         <is>
-          <t>SÍ — archivada (CV_Ruilova-Gonzalez_Lizbet.pdf). La «actualizada» que reenvió el 12/10/2026 tiene el mismo contenido.</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="K12" s="54" t="inlineStr">
@@ -2855,7 +2879,7 @@
       </c>
       <c r="L12" s="54" t="inlineStr">
         <is>
-          <t>EN BLANCO — el formato llegó sin llenar, sin casilla marcada y sin firma. Debe rehacerla.</t>
+          <t>SÍ — DECLARA CONFLICTO: honorarios de Boehringer Ingelheim. Debe mencionarlo al inicio de la grabación de M3·C1. Falta completar producto/área, periodo y la fecha de firma.</t>
         </is>
       </c>
       <c r="M12" s="42" t="n"/>
@@ -2871,59 +2895,63 @@
       </c>
       <c r="B13" s="54" t="inlineStr">
         <is>
-          <t>Dr. Pablo Esteban Vanegas Cedillo</t>
+          <t>Dra. María Augusta Astudillo Calle</t>
         </is>
       </c>
       <c r="C13" s="54" t="inlineStr">
         <is>
-          <t>Medicina Interna · Endocrinología · Obesidad y Trastornos de la Conducta Alimentaria</t>
+          <t>Medicina Interna · Endocrinología</t>
         </is>
       </c>
       <c r="D13" s="54" t="inlineStr">
         <is>
-          <t>Hospital Santa Inés — Cuenca, Ecuador</t>
+          <t>Hospital Santa Inés · Casa de la Diabetes — Cuenca, Ecuador</t>
         </is>
       </c>
       <c r="E13" s="54" t="inlineStr">
         <is>
-          <t>pablo.vanegas90@gmail.com</t>
+          <t>medimagu@yahoo.com</t>
         </is>
       </c>
       <c r="F13" s="60" t="inlineStr">
         <is>
-          <t>+593 98 765 3136</t>
+          <t>+593 99 811 1635</t>
         </is>
       </c>
       <c r="G13" s="54" t="inlineStr">
         <is>
-          <t>0103838058 — leída de la cédula y contrastada con su declaración y su hoja de vida: coinciden</t>
+          <t>YA PEDIDA por la coordinación el 09/10/2026. Identidad dada por buena: la Dra. Omidres la verificó directamente con ella. El número manuscrito del formulario no es legible en el escaneo y por eso aquí no se transcribe ninguna cifra.</t>
         </is>
       </c>
       <c r="H13" s="41" t="n"/>
       <c r="I13" s="40" t="inlineStr">
         <is>
-          <t>M1 · C2  /  M3 · C1</t>
+          <t>M1 · C3</t>
         </is>
       </c>
       <c r="J13" s="54" t="inlineStr">
         <is>
+          <t>SÍ — recibida y archivada el 13/10/2026 (CV_Astudillo-Calle_Maria-Augusta.docx, fechada octubre 2024)</t>
+        </is>
+      </c>
+      <c r="K13" s="54" t="inlineStr">
+        <is>
+          <t>SÍ — el archivo sigue en el correo, falta guardarlo en el expediente</t>
+        </is>
+      </c>
+      <c r="L13" s="54" t="inlineStr">
+        <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="K13" s="54" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
-      <c r="L13" s="54" t="inlineStr">
-        <is>
-          <t>SÍ — DECLARA CONFLICTO: honorarios de Boehringer Ingelheim. Debe mencionarlo al inicio de la grabación de M3·C1. Falta completar producto/área, periodo y la fecha de firma.</t>
-        </is>
-      </c>
-      <c r="M13" s="42" t="n"/>
+      <c r="M13" s="54" t="inlineStr">
+        <is>
+          <t>28 de octubre de 2026</t>
+        </is>
+      </c>
       <c r="N13" s="44" t="inlineStr">
         <is>
-          <t>CONFIRMADO</t>
+          <t>CONFIRMADO — declinó M4 · C1 el 25/09</t>
         </is>
       </c>
     </row>
@@ -2931,65 +2959,49 @@
       <c r="A14" s="38" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="54" t="inlineStr">
-        <is>
-          <t>Dra. María Augusta Astudillo Calle</t>
-        </is>
-      </c>
-      <c r="C14" s="54" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
+        <is>
+          <t>Dra. Marcia Gabriela Jiménez Encalada</t>
+        </is>
+      </c>
+      <c r="C14" s="41" t="inlineStr">
         <is>
           <t>Medicina Interna · Endocrinología</t>
         </is>
       </c>
-      <c r="D14" s="54" t="inlineStr">
-        <is>
-          <t>Hospital Santa Inés · Casa de la Diabetes — Cuenca, Ecuador</t>
-        </is>
-      </c>
-      <c r="E14" s="54" t="inlineStr">
-        <is>
-          <t>medimagu@yahoo.com</t>
+      <c r="D14" s="41" t="inlineStr">
+        <is>
+          <t>Centro de Especialidades Médicas de la Universidad de Cuenca · Hospital Santa Inés — Cuenca, Ecuador</t>
+        </is>
+      </c>
+      <c r="E14" s="41" t="inlineStr">
+        <is>
+          <t>gabriela.jimeneze@ucuenca.edu.ec</t>
         </is>
       </c>
       <c r="F14" s="60" t="inlineStr">
         <is>
-          <t>+593 99 811 1635</t>
-        </is>
-      </c>
-      <c r="G14" s="54" t="inlineStr">
-        <is>
-          <t>YA PEDIDA por la coordinación el 09/10/2026. Identidad dada por buena: la Dra. Omidres la verificó directamente con ella. El número manuscrito del formulario no es legible en el escaneo y por eso aquí no se transcribe ninguna cifra.</t>
-        </is>
-      </c>
+          <t>+593 99 807 8964</t>
+        </is>
+      </c>
+      <c r="G14" s="41" t="n"/>
       <c r="H14" s="41" t="n"/>
       <c r="I14" s="40" t="inlineStr">
         <is>
-          <t>M1 · C3</t>
-        </is>
-      </c>
-      <c r="J14" s="54" t="inlineStr">
-        <is>
-          <t>SÍ — recibida y archivada el 13/10/2026 (CV_Astudillo-Calle_Maria-Augusta.docx, fechada octubre 2024)</t>
-        </is>
-      </c>
-      <c r="K14" s="54" t="inlineStr">
-        <is>
-          <t>SÍ — el archivo sigue en el correo, falta guardarlo en el expediente</t>
-        </is>
-      </c>
-      <c r="L14" s="54" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
-      <c r="M14" s="54" t="inlineStr">
-        <is>
-          <t>28 de octubre de 2026</t>
-        </is>
-      </c>
+          <t>M4 · C3</t>
+        </is>
+      </c>
+      <c r="J14" s="42" t="inlineStr">
+        <is>
+          <t>SÍ — recibida el 12/10/2026 y archivada (CV_Jimenez-Encalada_Marcia-Gabriela.docx). Última modificación del archivo: diciembre de 2024.</t>
+        </is>
+      </c>
+      <c r="K14" s="42" t="n"/>
+      <c r="L14" s="42" t="n"/>
+      <c r="M14" s="42" t="n"/>
       <c r="N14" s="44" t="inlineStr">
         <is>
-          <t>CONFIRMADO — declinó M4 · C1 el 25/09</t>
+          <t>CONFIRMADO — declinó M1 · C4 el 25/09</t>
         </is>
       </c>
     </row>
@@ -2997,49 +3009,65 @@
       <c r="A15" s="38" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="39" t="inlineStr">
-        <is>
-          <t>Dra. Marcia Gabriela Jiménez Encalada</t>
-        </is>
-      </c>
-      <c r="C15" s="41" t="inlineStr">
-        <is>
-          <t>Medicina Interna · Endocrinología</t>
-        </is>
-      </c>
-      <c r="D15" s="41" t="inlineStr">
-        <is>
-          <t>Centro de Especialidades Médicas de la Universidad de Cuenca · Hospital Santa Inés — Cuenca, Ecuador</t>
-        </is>
-      </c>
-      <c r="E15" s="41" t="inlineStr">
-        <is>
-          <t>gabriela.jimeneze@ucuenca.edu.ec</t>
+      <c r="B15" s="54" t="inlineStr">
+        <is>
+          <t>Dr. Juan Fernando Molina Galarza</t>
+        </is>
+      </c>
+      <c r="C15" s="54" t="inlineStr">
+        <is>
+          <t>Medicina Interna · Endocrinología · Máster en infección por VIH</t>
+        </is>
+      </c>
+      <c r="D15" s="54" t="inlineStr">
+        <is>
+          <t>Hospital General Vicente Corral Moscoso · Corporación Médica Monte Sinaí — Cuenca, Ecuador</t>
+        </is>
+      </c>
+      <c r="E15" s="54" t="inlineStr">
+        <is>
+          <t>molinagalarza.jf@gmail.com</t>
         </is>
       </c>
       <c r="F15" s="60" t="inlineStr">
         <is>
-          <t>+593 99 807 8964</t>
-        </is>
-      </c>
-      <c r="G15" s="41" t="n"/>
+          <t>+593 99 862 5711</t>
+        </is>
+      </c>
+      <c r="G15" s="54" t="inlineStr">
+        <is>
+          <t>0104904313 — la copia está en Drive (formulario), falta guardarla en el expediente</t>
+        </is>
+      </c>
       <c r="H15" s="41" t="n"/>
       <c r="I15" s="40" t="inlineStr">
         <is>
-          <t>M4 · C3</t>
-        </is>
-      </c>
-      <c r="J15" s="42" t="inlineStr">
-        <is>
-          <t>SÍ — recibida el 12/10/2026 y archivada (CV_Jimenez-Encalada_Marcia-Gabriela.docx). Última modificación del archivo: diciembre de 2024.</t>
-        </is>
-      </c>
-      <c r="K15" s="42" t="n"/>
-      <c r="L15" s="42" t="n"/>
-      <c r="M15" s="42" t="n"/>
+          <t>M4 · C4</t>
+        </is>
+      </c>
+      <c r="J15" s="54" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="K15" s="54" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="L15" s="54" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="M15" s="54" t="inlineStr">
+        <is>
+          <t>12 de noviembre de 2026</t>
+        </is>
+      </c>
       <c r="N15" s="44" t="inlineStr">
         <is>
-          <t>CONFIRMADO — declinó M1 · C4 el 25/09</t>
+          <t>CONFIRMADO</t>
         </is>
       </c>
     </row>
@@ -3047,115 +3075,111 @@
       <c r="A16" s="38" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="54" t="inlineStr">
-        <is>
-          <t>Dr. Juan Fernando Molina Galarza</t>
-        </is>
-      </c>
-      <c r="C16" s="54" t="inlineStr">
-        <is>
-          <t>Medicina Interna · Endocrinología · Máster en infección por VIH</t>
-        </is>
-      </c>
-      <c r="D16" s="54" t="inlineStr">
-        <is>
-          <t>Hospital General Vicente Corral Moscoso · Corporación Médica Monte Sinaí — Cuenca, Ecuador</t>
-        </is>
-      </c>
-      <c r="E16" s="54" t="inlineStr">
-        <is>
-          <t>molinagalarza.jf@gmail.com</t>
-        </is>
-      </c>
-      <c r="F16" s="60" t="inlineStr">
-        <is>
-          <t>+593 99 862 5711</t>
-        </is>
-      </c>
-      <c r="G16" s="54" t="inlineStr">
-        <is>
-          <t>0104904313 — la copia está en Drive (formulario), falta guardarla en el expediente</t>
-        </is>
-      </c>
+      <c r="B16" s="39" t="inlineStr">
+        <is>
+          <t>Dra. Andrea Valeria Andrade Izquierdo</t>
+        </is>
+      </c>
+      <c r="C16" s="41" t="inlineStr">
+        <is>
+          <t>Nefrología · Trasplante renal · PhD en Ciencias (Nefrología), Universidad de São Paulo</t>
+        </is>
+      </c>
+      <c r="D16" s="41" t="inlineStr">
+        <is>
+          <t>Hospital Santa Inés · Universidad de Cuenca — Cuenca, Ecuador</t>
+        </is>
+      </c>
+      <c r="E16" s="41" t="inlineStr">
+        <is>
+          <t>vale19_ec@yahoo.com</t>
+        </is>
+      </c>
+      <c r="F16" s="41" t="inlineStr">
+        <is>
+          <t>+593 98 335 5686</t>
+        </is>
+      </c>
+      <c r="G16" s="41" t="n"/>
       <c r="H16" s="41" t="n"/>
       <c r="I16" s="40" t="inlineStr">
         <is>
-          <t>M4 · C4</t>
-        </is>
-      </c>
-      <c r="J16" s="54" t="inlineStr">
+          <t>M6 · C1</t>
+        </is>
+      </c>
+      <c r="J16" s="42" t="inlineStr">
+        <is>
+          <t>SÍ — versión actualizada 2026 recibida el 12/10/2026 y archivada como CV_Andrade-Izquierdo_Andrea-Valeria.pdf (reemplaza la de sept. 2025: ahora Presidenta de la Sociedad de Nefrología del Austro)</t>
+        </is>
+      </c>
+      <c r="K16" s="42" t="n"/>
+      <c r="L16" s="42" t="n"/>
+      <c r="M16" s="42" t="n"/>
+      <c r="N16" s="44" t="inlineStr">
+        <is>
+          <t>CONFIRMADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="54" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="42" t="inlineStr">
+        <is>
+          <t>Dra. Marcia Janneth Bermeo Cabrera</t>
+        </is>
+      </c>
+      <c r="C17" s="53" t="inlineStr">
+        <is>
+          <t>Medicina Interna · Subespecialista en Endocrinología · Alta especialidad en Obesidad y Enfermedades Tiroideas (UNAM)</t>
+        </is>
+      </c>
+      <c r="D17" s="42" t="inlineStr">
+        <is>
+          <t>Hospital del Río · Cuenca, Ecuador</t>
+        </is>
+      </c>
+      <c r="E17" s="42" t="inlineStr">
+        <is>
+          <t>jbendocrino@hotmail.com</t>
+        </is>
+      </c>
+      <c r="F17" s="41" t="inlineStr">
+        <is>
+          <t>+593 96 198 1203</t>
+        </is>
+      </c>
+      <c r="G17" s="42" t="inlineStr">
+        <is>
+          <t>0104851001 (copia de cédula en expediente)</t>
+        </is>
+      </c>
+      <c r="H17" s="41" t="n"/>
+      <c r="I17" s="54" t="inlineStr">
+        <is>
+          <t>M2 · C3</t>
+        </is>
+      </c>
+      <c r="J17" s="42" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="K16" s="54" t="inlineStr">
+      <c r="K17" s="54" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="L16" s="54" t="inlineStr">
+      <c r="L17" s="42" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="M16" s="54" t="inlineStr">
-        <is>
-          <t>12 de noviembre de 2026</t>
-        </is>
-      </c>
-      <c r="N16" s="44" t="inlineStr">
-        <is>
-          <t>CONFIRMADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="38" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="39" t="inlineStr">
-        <is>
-          <t>Dra. Andrea Valeria Andrade Izquierdo</t>
-        </is>
-      </c>
-      <c r="C17" s="41" t="inlineStr">
-        <is>
-          <t>Nefrología · Trasplante renal · PhD en Ciencias (Nefrología), Universidad de São Paulo</t>
-        </is>
-      </c>
-      <c r="D17" s="41" t="inlineStr">
-        <is>
-          <t>Hospital Santa Inés · Universidad de Cuenca — Cuenca, Ecuador</t>
-        </is>
-      </c>
-      <c r="E17" s="41" t="inlineStr">
-        <is>
-          <t>vale19_ec@yahoo.com</t>
-        </is>
-      </c>
-      <c r="F17" s="41" t="inlineStr">
-        <is>
-          <t>+593 98 335 5686</t>
-        </is>
-      </c>
-      <c r="G17" s="41" t="n"/>
-      <c r="H17" s="41" t="n"/>
-      <c r="I17" s="40" t="inlineStr">
-        <is>
-          <t>M6 · C1</t>
-        </is>
-      </c>
-      <c r="J17" s="42" t="inlineStr">
-        <is>
-          <t>SÍ — versión actualizada 2026 recibida el 12/10/2026 y archivada como CV_Andrade-Izquierdo_Andrea-Valeria.pdf (reemplaza la de sept. 2025: ahora Presidenta de la Sociedad de Nefrología del Austro)</t>
-        </is>
-      </c>
-      <c r="K17" s="42" t="n"/>
-      <c r="L17" s="42" t="n"/>
       <c r="M17" s="42" t="n"/>
-      <c r="N17" s="44" t="inlineStr">
-        <is>
-          <t>CONFIRMADO</t>
+      <c r="N17" s="65" t="inlineStr">
+        <is>
+          <t>CONFIRMADO — declaración COI llena, pendiente de firma electrónica</t>
         </is>
       </c>
     </row>
@@ -3163,61 +3187,53 @@
       <c r="A18" s="54" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="42" t="inlineStr">
-        <is>
-          <t>Dra. Marcia Janneth Bermeo Cabrera</t>
+      <c r="B18" s="52" t="inlineStr">
+        <is>
+          <t>Dra. María Paz Castillo Cabrera</t>
         </is>
       </c>
       <c r="C18" s="53" t="inlineStr">
         <is>
-          <t>Medicina Interna · Subespecialista en Endocrinología · Alta especialidad en Obesidad y Enfermedades Tiroideas (UNAM)</t>
-        </is>
-      </c>
-      <c r="D18" s="42" t="inlineStr">
-        <is>
-          <t>Hospital del Río · Cuenca, Ecuador</t>
-        </is>
-      </c>
-      <c r="E18" s="42" t="inlineStr">
-        <is>
-          <t>jbendocrino@hotmail.com</t>
+          <t>Medicina Interna · Endocrinología · Alta especialidad en Enfermedades Tiroideas (UNAM)</t>
+        </is>
+      </c>
+      <c r="D18" s="53" t="inlineStr">
+        <is>
+          <t>Centro Metropolitano de Oncología Integral, Hospital Ángeles — Ciudad de México, México (según su hoja de vida de 22/09/2026)</t>
+        </is>
+      </c>
+      <c r="E18" s="41" t="inlineStr">
+        <is>
+          <t>mariapazcc22@hotmail.com</t>
         </is>
       </c>
       <c r="F18" s="41" t="inlineStr">
         <is>
-          <t>+593 96 198 1203</t>
-        </is>
-      </c>
-      <c r="G18" s="42" t="inlineStr">
-        <is>
-          <t>0104851001 (copia de cédula en expediente)</t>
-        </is>
-      </c>
+          <t>+52 1 56 2489 0698</t>
+        </is>
+      </c>
+      <c r="G18" s="41" t="n"/>
       <c r="H18" s="41" t="n"/>
       <c r="I18" s="54" t="inlineStr">
         <is>
-          <t>M2 · C3</t>
+          <t>M4 · C1</t>
         </is>
       </c>
       <c r="J18" s="42" t="inlineStr">
         <is>
-          <t>SÍ</t>
-        </is>
-      </c>
-      <c r="K18" s="54" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
-      <c r="L18" s="42" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
-      <c r="M18" s="42" t="n"/>
+          <t>SÍ — llegó por la Dra. Ruilova el 12/10/2026; revisada y archivada (CV_Castillo-Cabrera_Maria-Paz.pdf). Ojo: su hoja de vida la sitúa trabajando en Ciudad de México desde junio de 2026, no en Cuenca, y no menciona ningún cargo en la Universidad de Cuenca.</t>
+        </is>
+      </c>
+      <c r="K18" s="42" t="n"/>
+      <c r="L18" s="42" t="n"/>
+      <c r="M18" s="42" t="inlineStr">
+        <is>
+          <t>12/11/2026</t>
+        </is>
+      </c>
       <c r="N18" s="65" t="inlineStr">
         <is>
-          <t>CONFIRMADO — declaración COI llena, pendiente de firma electrónica</t>
+          <t>CONFIRMADO — ponente nacional · PENDIENTE aclarar si interviene en el trámite del aval</t>
         </is>
       </c>
     </row>
@@ -3225,53 +3241,61 @@
       <c r="A19" s="54" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="52" t="inlineStr">
-        <is>
-          <t>Dra. María Paz Castillo Cabrera</t>
+      <c r="B19" s="54" t="inlineStr">
+        <is>
+          <t>Dr. Cristian Oswaldo Castillo Cabrera</t>
         </is>
       </c>
       <c r="C19" s="53" t="inlineStr">
         <is>
-          <t>Medicina Interna · Endocrinología · Alta especialidad en Enfermedades Tiroideas (UNAM)</t>
+          <t>Cirugía bariátrica y metabólica</t>
         </is>
       </c>
       <c r="D19" s="53" t="inlineStr">
         <is>
-          <t>Centro Metropolitano de Oncología Integral, Hospital Ángeles — Ciudad de México, México (según su hoja de vida de 22/09/2026)</t>
-        </is>
-      </c>
-      <c r="E19" s="41" t="inlineStr">
-        <is>
-          <t>mariapazcc22@hotmail.com</t>
+          <t>Hospital Santa Inés — Cuenca, Ecuador</t>
+        </is>
+      </c>
+      <c r="E19" s="54" t="inlineStr">
+        <is>
+          <t>cristiancastillodr@gmail.com</t>
         </is>
       </c>
       <c r="F19" s="41" t="inlineStr">
         <is>
-          <t>+52 1 56 2489 0698</t>
-        </is>
-      </c>
-      <c r="G19" s="41" t="n"/>
+          <t>+593 97 965 3154</t>
+        </is>
+      </c>
+      <c r="G19" s="54" t="inlineStr">
+        <is>
+          <t>SÍ — el archivo sigue en el correo, falta guardarlo en el expediente</t>
+        </is>
+      </c>
       <c r="H19" s="41" t="n"/>
       <c r="I19" s="54" t="inlineStr">
         <is>
-          <t>M4 · C1</t>
-        </is>
-      </c>
-      <c r="J19" s="42" t="inlineStr">
-        <is>
-          <t>SÍ — llegó por la Dra. Ruilova el 12/10/2026; revisada y archivada (CV_Castillo-Cabrera_Maria-Paz.pdf). Ojo: su hoja de vida la sitúa trabajando en Ciudad de México desde junio de 2026, no en Cuenca, y no menciona ningún cargo en la Universidad de Cuenca.</t>
-        </is>
-      </c>
-      <c r="K19" s="42" t="n"/>
-      <c r="L19" s="42" t="n"/>
-      <c r="M19" s="42" t="inlineStr">
-        <is>
-          <t>12/11/2026</t>
-        </is>
-      </c>
+          <t>M3 · C4</t>
+        </is>
+      </c>
+      <c r="J19" s="54" t="inlineStr">
+        <is>
+          <t>SÍ — recibida el 07/10/2026 (y reenviada por la Dra. Ruilova el 12/10/2026); revisada y archivada (CV_Castillo-Cabrera_Cristian-Oswaldo.pdf)</t>
+        </is>
+      </c>
+      <c r="K19" s="54" t="inlineStr">
+        <is>
+          <t>SÍ — el archivo sigue en el correo, falta guardarlo en el expediente</t>
+        </is>
+      </c>
+      <c r="L19" s="54" t="inlineStr">
+        <is>
+          <t>YA PEDIDA la firma por la coordinación el 09/10/2026. Envió el formato el 07/10 pero el archivo no lleva «signed» en el nombre y no se ha podido abrir para comprobar que esté firmado.</t>
+        </is>
+      </c>
+      <c r="M19" s="42" t="n"/>
       <c r="N19" s="65" t="inlineStr">
         <is>
-          <t>CONFIRMADO — ponente nacional · PENDIENTE aclarar si interviene en el trámite del aval</t>
+          <t>CONFIRMADO — falta documentación</t>
         </is>
       </c>
     </row>
@@ -3281,59 +3305,63 @@
       </c>
       <c r="B20" s="54" t="inlineStr">
         <is>
-          <t>Dr. Cristian Oswaldo Castillo Cabrera</t>
-        </is>
-      </c>
-      <c r="C20" s="53" t="inlineStr">
-        <is>
-          <t>Cirugía bariátrica y metabólica</t>
-        </is>
-      </c>
-      <c r="D20" s="53" t="inlineStr">
-        <is>
-          <t>Hospital Santa Inés — Cuenca, Ecuador</t>
+          <t>Dra. Julia Castro de González</t>
+        </is>
+      </c>
+      <c r="C20" s="54" t="inlineStr">
+        <is>
+          <t>Medicina Física y Rehabilitación</t>
+        </is>
+      </c>
+      <c r="D20" s="54" t="inlineStr">
+        <is>
+          <t>Hospital de Especialidades José Carrasco Arteaga (IESS) — Cuenca, Ecuador</t>
         </is>
       </c>
       <c r="E20" s="54" t="inlineStr">
         <is>
-          <t>cristiancastillodr@gmail.com</t>
+          <t>dracastrorehabilitacion@gmail.com (escribió desde castromezajulia@gmail.com — confirmar cuál usar)</t>
         </is>
       </c>
       <c r="F20" s="41" t="inlineStr">
         <is>
-          <t>+593 97 965 3154</t>
+          <t>+593 99 208 7747</t>
         </is>
       </c>
       <c r="G20" s="54" t="inlineStr">
         <is>
-          <t>SÍ — el archivo sigue en el correo, falta guardarlo en el expediente</t>
+          <t>0151826435 — dígito verificador correcto; copia enviada por correo, falta guardarla en el expediente</t>
         </is>
       </c>
       <c r="H20" s="41" t="n"/>
       <c r="I20" s="54" t="inlineStr">
         <is>
-          <t>M3 · C4</t>
+          <t>M2 · C4</t>
         </is>
       </c>
       <c r="J20" s="54" t="inlineStr">
         <is>
-          <t>SÍ — recibida el 07/10/2026 (y reenviada por la Dra. Ruilova el 12/10/2026); revisada y archivada (CV_Castillo-Cabrera_Cristian-Oswaldo.pdf)</t>
+          <t>SÍ — recibida y archivada el 13/10/2026 (CV_Castro-de-Gonzalez_Julia.pdf)</t>
         </is>
       </c>
       <c r="K20" s="54" t="inlineStr">
         <is>
-          <t>SÍ — el archivo sigue en el correo, falta guardarlo en el expediente</t>
+          <t>PROVISIONAL — solo hay una miniatura de 150×150 px (4 KB), insuficiente para el expediente. Pedirle el archivo original.</t>
         </is>
       </c>
       <c r="L20" s="54" t="inlineStr">
         <is>
-          <t>YA PEDIDA la firma por la coordinación el 09/10/2026. Envió el formato el 07/10 pero el archivo no lleva «signed» en el nombre y no se ha podido abrir para comprobar que esté firmado.</t>
-        </is>
-      </c>
-      <c r="M20" s="42" t="n"/>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="M20" s="54" t="inlineStr">
+        <is>
+          <t>29 de octubre de 2026</t>
+        </is>
+      </c>
       <c r="N20" s="65" t="inlineStr">
         <is>
-          <t>CONFIRMADO — falta documentación</t>
+          <t>CONFIRMADO — falta documentación · ENTREGA MÁS PRÓXIMA DEL CURSO</t>
         </is>
       </c>
     </row>
@@ -3343,48 +3371,48 @@
       </c>
       <c r="B21" s="54" t="inlineStr">
         <is>
-          <t>Dra. Julia Castro de González</t>
+          <t>Lcda. Gabriela Estefanía Molina Ochoa, Mgt.</t>
         </is>
       </c>
       <c r="C21" s="54" t="inlineStr">
         <is>
-          <t>Medicina Física y Rehabilitación</t>
+          <t>Nutrición · Diplomado en Educación en Diabetes · Máster en Antropología · Máster en Salud Pública</t>
         </is>
       </c>
       <c r="D21" s="54" t="inlineStr">
         <is>
-          <t>Hospital de Especialidades José Carrasco Arteaga (IESS) — Cuenca, Ecuador</t>
+          <t>Universidad de Cuenca — Cuenca, Ecuador</t>
         </is>
       </c>
       <c r="E21" s="54" t="inlineStr">
         <is>
-          <t>dracastrorehabilitacion@gmail.com (escribió desde castromezajulia@gmail.com — confirmar cuál usar)</t>
+          <t>gabrielamolinaochoa@gmail.com</t>
         </is>
       </c>
       <c r="F21" s="41" t="inlineStr">
         <is>
-          <t>+593 99 208 7747</t>
+          <t>+593 99 551 4286</t>
         </is>
       </c>
       <c r="G21" s="54" t="inlineStr">
         <is>
-          <t>0151826435 — dígito verificador correcto; copia enviada por correo, falta guardarla en el expediente</t>
+          <t>0105111827</t>
         </is>
       </c>
       <c r="H21" s="41" t="n"/>
       <c r="I21" s="54" t="inlineStr">
         <is>
-          <t>M2 · C4</t>
+          <t>M5 · C1</t>
         </is>
       </c>
       <c r="J21" s="54" t="inlineStr">
         <is>
-          <t>SÍ — recibida y archivada el 13/10/2026 (CV_Castro-de-Gonzalez_Julia.pdf)</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="K21" s="54" t="inlineStr">
         <is>
-          <t>PROVISIONAL — solo hay una miniatura de 150×150 px (4 KB), insuficiente para el expediente. Pedirle el archivo original.</t>
+          <t>SÍ</t>
         </is>
       </c>
       <c r="L21" s="54" t="inlineStr">
@@ -3394,12 +3422,12 @@
       </c>
       <c r="M21" s="54" t="inlineStr">
         <is>
-          <t>29 de octubre de 2026</t>
+          <t>Jueves 19 de noviembre de 2026</t>
         </is>
       </c>
       <c r="N21" s="65" t="inlineStr">
         <is>
-          <t>CONFIRMADO — falta documentación · ENTREGA MÁS PRÓXIMA DEL CURSO</t>
+          <t>CONFIRMADO — faltan todos los documentos</t>
         </is>
       </c>
     </row>
@@ -3407,65 +3435,49 @@
       <c r="A22" s="54" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="54" t="inlineStr">
-        <is>
-          <t>Lcda. Gabriela Estefanía Molina Ochoa, Mgt.</t>
-        </is>
-      </c>
-      <c r="C22" s="54" t="inlineStr">
-        <is>
-          <t>Nutrición · Diplomado en Educación en Diabetes · Máster en Antropología · Máster en Salud Pública</t>
-        </is>
-      </c>
-      <c r="D22" s="54" t="inlineStr">
-        <is>
-          <t>Universidad de Cuenca — Cuenca, Ecuador</t>
-        </is>
-      </c>
-      <c r="E22" s="54" t="inlineStr">
-        <is>
-          <t>gabrielamolinaochoa@gmail.com</t>
+      <c r="B22" s="52" t="inlineStr">
+        <is>
+          <t>Dra. María Gabriela Machado Orellana</t>
+        </is>
+      </c>
+      <c r="C22" s="53" t="inlineStr">
+        <is>
+          <t>Medicina · Nutrición clínica · Máster en Nutrición y Metabolismo (Universitat de Barcelona)</t>
+        </is>
+      </c>
+      <c r="D22" s="53" t="inlineStr">
+        <is>
+          <t>Consultorios Arupo · docente de la Facultad de Ciencias Médicas, Universidad de Cuenca — Cuenca, Ecuador</t>
+        </is>
+      </c>
+      <c r="E22" s="41" t="inlineStr">
+        <is>
+          <t>gabi_machado25@hotmail.com</t>
         </is>
       </c>
       <c r="F22" s="41" t="inlineStr">
         <is>
-          <t>+593 99 551 4286</t>
-        </is>
-      </c>
-      <c r="G22" s="54" t="inlineStr">
-        <is>
-          <t>0105111827</t>
-        </is>
-      </c>
+          <t>+593 99 502 5774</t>
+        </is>
+      </c>
+      <c r="G22" s="41" t="n"/>
       <c r="H22" s="41" t="n"/>
       <c r="I22" s="54" t="inlineStr">
         <is>
-          <t>M5 · C1</t>
-        </is>
-      </c>
-      <c r="J22" s="54" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
-      <c r="K22" s="54" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
-      <c r="L22" s="54" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
-      <c r="M22" s="54" t="inlineStr">
-        <is>
-          <t>Jueves 19 de noviembre de 2026</t>
-        </is>
-      </c>
+          <t>M5 · C3</t>
+        </is>
+      </c>
+      <c r="J22" s="42" t="inlineStr">
+        <is>
+          <t>SÍ — recibida y archivada el 13/10/2026 (CV_Machado-Orellana_Maria-Gabriela.pdf, versión 2022)</t>
+        </is>
+      </c>
+      <c r="K22" s="42" t="n"/>
+      <c r="L22" s="42" t="n"/>
+      <c r="M22" s="42" t="n"/>
       <c r="N22" s="65" t="inlineStr">
         <is>
-          <t>CONFIRMADO — faltan todos los documentos</t>
+          <t>CONFIRMADO — faltan especialidad, institución y documentación</t>
         </is>
       </c>
     </row>
@@ -3475,47 +3487,47 @@
       </c>
       <c r="B23" s="52" t="inlineStr">
         <is>
-          <t>Dra. María Gabriela Machado Orellana</t>
+          <t>Dra. Ana María Gómez Medina</t>
         </is>
       </c>
       <c r="C23" s="53" t="inlineStr">
         <is>
-          <t>Medicina · Nutrición clínica · Máster en Nutrición y Metabolismo (Universitat de Barcelona)</t>
+          <t>Medicina Interna · Endocrinología · Tecnología en diabetes</t>
         </is>
       </c>
       <c r="D23" s="53" t="inlineStr">
         <is>
-          <t>Consultorios Arupo · docente de la Facultad de Ciencias Médicas, Universidad de Cuenca — Cuenca, Ecuador</t>
-        </is>
-      </c>
-      <c r="E23" s="41" t="inlineStr">
-        <is>
-          <t>gabi_machado25@hotmail.com</t>
-        </is>
-      </c>
+          <t>Hospital Universitario San Ignacio · Pontificia Universidad Javeriana — Bogotá, Colombia</t>
+        </is>
+      </c>
+      <c r="E23" s="41" t="n"/>
       <c r="F23" s="41" t="inlineStr">
         <is>
-          <t>+593 99 502 5774</t>
+          <t>+57 310 488 4626</t>
         </is>
       </c>
       <c r="G23" s="41" t="n"/>
       <c r="H23" s="41" t="n"/>
       <c r="I23" s="54" t="inlineStr">
         <is>
-          <t>M5 · C3</t>
+          <t>M7 · C2</t>
         </is>
       </c>
       <c r="J23" s="42" t="inlineStr">
         <is>
-          <t>SÍ — recibida y archivada el 13/10/2026 (CV_Machado-Orellana_Maria-Gabriela.pdf, versión 2022)</t>
+          <t>SÍ — versión armada por la coordinación con PubMed y APROBADA por la Dra. Gómez, según la Dra. Omidres (12/10/2026). Archivada como CV_Gomez-Medina_Ana-Maria.pdf.</t>
         </is>
       </c>
       <c r="K23" s="42" t="n"/>
       <c r="L23" s="42" t="n"/>
-      <c r="M23" s="42" t="n"/>
+      <c r="M23" s="42" t="inlineStr">
+        <is>
+          <t>03/12/2026</t>
+        </is>
+      </c>
       <c r="N23" s="65" t="inlineStr">
         <is>
-          <t>CONFIRMADO — faltan especialidad, institución y documentación</t>
+          <t>CONFIRMADO — falta toda la documentación</t>
         </is>
       </c>
     </row>
@@ -3525,35 +3537,39 @@
       </c>
       <c r="B24" s="52" t="inlineStr">
         <is>
-          <t>Dra. Ana María Gómez Medina</t>
+          <t>Dr. Ronald Fabricio Salas Guerrero</t>
         </is>
       </c>
       <c r="C24" s="53" t="inlineStr">
         <is>
-          <t>Medicina Interna · Endocrinología · Tecnología en diabetes</t>
+          <t>Medicina · Epidemiología · Salud digital e interoperabilidad</t>
         </is>
       </c>
       <c r="D24" s="53" t="inlineStr">
         <is>
-          <t>Hospital Universitario San Ignacio · Pontificia Universidad Javeriana — Bogotá, Colombia</t>
-        </is>
-      </c>
-      <c r="E24" s="41" t="n"/>
+          <t>Ministerio de Salud Pública del Ecuador (epidemiólogo, 2026)</t>
+        </is>
+      </c>
+      <c r="E24" s="41" t="inlineStr">
+        <is>
+          <t>fabriciosalasguerrero@gmail.com</t>
+        </is>
+      </c>
       <c r="F24" s="41" t="inlineStr">
         <is>
-          <t>+57 310 488 4626</t>
+          <t>+593 99 381 4728</t>
         </is>
       </c>
       <c r="G24" s="41" t="n"/>
       <c r="H24" s="41" t="n"/>
       <c r="I24" s="54" t="inlineStr">
         <is>
-          <t>M7 · C2</t>
+          <t>M7 · C3</t>
         </is>
       </c>
       <c r="J24" s="42" t="inlineStr">
         <is>
-          <t>SÍ — versión armada por la coordinación con PubMed y APROBADA por la Dra. Gómez, según la Dra. Omidres (12/10/2026). Archivada como CV_Gomez-Medina_Ana-Maria.pdf.</t>
+          <t>SÍ — recibida el 10/10/2026 y archivada (CV_Salas-Guerrero_Ronald-Fabricio.pdf). Ojo: los dos registros SENESCYT que figuran en ella parecen intercambiados entre el título de médico y la maestría.</t>
         </is>
       </c>
       <c r="K24" s="42" t="n"/>
@@ -3575,46 +3591,46 @@
       </c>
       <c r="B25" s="52" t="inlineStr">
         <is>
-          <t>Dr. Ronald Fabricio Salas Guerrero</t>
+          <t>Dra. Adriana Victoria González Neira</t>
         </is>
       </c>
       <c r="C25" s="53" t="inlineStr">
         <is>
-          <t>Medicina · Epidemiología · Salud digital e interoperabilidad</t>
+          <t>Medicina Interna · Endocrinología · Diabetes · Tesorera de ALAD (2026–2028)</t>
         </is>
       </c>
       <c r="D25" s="53" t="inlineStr">
         <is>
-          <t>Ministerio de Salud Pública del Ecuador (epidemiólogo, 2026)</t>
+          <t>Hospital Clínica Kennedy · Hospital General Naval (HOSNAG) — Guayaquil, Ecuador</t>
         </is>
       </c>
       <c r="E25" s="41" t="inlineStr">
         <is>
-          <t>fabriciosalasguerrero@gmail.com</t>
+          <t>adrianagn26@yahoo.com</t>
         </is>
       </c>
       <c r="F25" s="41" t="inlineStr">
         <is>
-          <t>+593 99 381 4728</t>
+          <t>+593 99 602 1221</t>
         </is>
       </c>
       <c r="G25" s="41" t="n"/>
       <c r="H25" s="41" t="n"/>
       <c r="I25" s="54" t="inlineStr">
         <is>
-          <t>M7 · C3</t>
+          <t>M1 · C4</t>
         </is>
       </c>
       <c r="J25" s="42" t="inlineStr">
         <is>
-          <t>SÍ — recibida el 10/10/2026 y archivada (CV_Salas-Guerrero_Ronald-Fabricio.pdf). Ojo: los dos registros SENESCYT que figuran en ella parecen intercambiados entre el título de médico y la maestría.</t>
+          <t>SÍ — recibida el 10/10/2026 y archivada (CV_Gonzalez-Neira_Adriana-Victoria.pdf)</t>
         </is>
       </c>
       <c r="K25" s="42" t="n"/>
       <c r="L25" s="42" t="n"/>
       <c r="M25" s="42" t="inlineStr">
         <is>
-          <t>03/12/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="N25" s="65" t="inlineStr">
@@ -3629,51 +3645,59 @@
       </c>
       <c r="B26" s="52" t="inlineStr">
         <is>
-          <t>Dra. Adriana Victoria González Neira</t>
+          <t>Ing. Styp Bill Roy Canto Rondón</t>
         </is>
       </c>
       <c r="C26" s="53" t="inlineStr">
         <is>
-          <t>Medicina Interna · Endocrinología · Diabetes · Tesorera de ALAD (2026–2028)</t>
+          <t>Ingeniería de Telecomunicaciones · TI en salud, telemedicina e interoperabilidad (HL7 FHIR)</t>
         </is>
       </c>
       <c r="D26" s="53" t="inlineStr">
         <is>
-          <t>Hospital Clínica Kennedy · Hospital General Naval (HOSNAG) — Guayaquil, Ecuador</t>
+          <t>Centro Nacional de Telemedicina (CENATE) – EsSalud · Lima, Perú</t>
         </is>
       </c>
       <c r="E26" s="41" t="inlineStr">
         <is>
-          <t>adrianagn26@yahoo.com</t>
+          <t>styp611@outlook.com</t>
         </is>
       </c>
       <c r="F26" s="41" t="inlineStr">
         <is>
-          <t>+593 99 602 1221</t>
+          <t>+51 956 194 180</t>
         </is>
       </c>
       <c r="G26" s="41" t="n"/>
-      <c r="H26" s="41" t="n"/>
+      <c r="H26" s="41" t="inlineStr">
+        <is>
+          <t>CIP 131278 (Colegio de Ingenieros del Perú)</t>
+        </is>
+      </c>
       <c r="I26" s="54" t="inlineStr">
         <is>
-          <t>M1 · C4</t>
+          <t>M7 · C4</t>
         </is>
       </c>
       <c r="J26" s="42" t="inlineStr">
         <is>
-          <t>SÍ — recibida el 10/10/2026 y archivada (CV_Gonzalez-Neira_Adriana-Victoria.pdf)</t>
+          <t>SÍ — llegó la versión original sin respaldos (10 páginas, 300 KB) el 12/10/2026 y se archivó como CV_Canto-Rondon_Styp-Bill-Roy.pdf. La versión armada por la coordinación ya no hace falta</t>
         </is>
       </c>
       <c r="K26" s="42" t="n"/>
-      <c r="L26" s="42" t="n"/>
+      <c r="L26" s="42" t="inlineStr">
+        <is>
+          <t>PENDIENTE — debe declarar: (1) consultor externo vigente de MEDDI Hub, empresa en la que la Dra. Omidres es CMO LATAM; (2) miembro vocal y fundador de la OITT, que preside la Dra. Omidres. Sin vínculo con Omisalud (confirmado por la Dra. Omidres el 12/10/2026)</t>
+        </is>
+      </c>
       <c r="M26" s="42" t="inlineStr">
         <is>
-          <t>29/10/2026</t>
+          <t>03/12/2026</t>
         </is>
       </c>
       <c r="N26" s="65" t="inlineStr">
         <is>
-          <t>CONFIRMADO — falta toda la documentación</t>
+          <t>CONFIRMADO — aceptó el 12/10/2026</t>
         </is>
       </c>
     </row>
@@ -3683,107 +3707,45 @@
       </c>
       <c r="B27" s="52" t="inlineStr">
         <is>
-          <t>Ing. Styp Bill Roy Canto Rondón</t>
+          <t>Dr. Ramón de Cangas Morán</t>
         </is>
       </c>
       <c r="C27" s="53" t="inlineStr">
         <is>
-          <t>Ingeniería de Telecomunicaciones · TI en salud, telemedicina e interoperabilidad (HL7 FHIR)</t>
+          <t>Dietista-nutricionista · Biología · Doctor en Biología Funcional y Molecular</t>
         </is>
       </c>
       <c r="D27" s="53" t="inlineStr">
         <is>
-          <t>Centro Nacional de Telemedicina (CENATE) – EsSalud · Lima, Perú</t>
-        </is>
-      </c>
-      <c r="E27" s="41" t="inlineStr">
-        <is>
-          <t>styp611@outlook.com</t>
-        </is>
-      </c>
-      <c r="F27" s="41" t="inlineStr">
-        <is>
-          <t>+51 956 194 180</t>
-        </is>
-      </c>
+          <t>Clínicas Nutrigroup · Fundación Alimenta Tu Salud — Oviedo, España</t>
+        </is>
+      </c>
+      <c r="E27" s="41" t="n"/>
+      <c r="F27" s="41" t="n"/>
       <c r="G27" s="41" t="n"/>
-      <c r="H27" s="41" t="inlineStr">
-        <is>
-          <t>CIP 131278 (Colegio de Ingenieros del Perú)</t>
-        </is>
-      </c>
+      <c r="H27" s="41" t="n"/>
       <c r="I27" s="54" t="inlineStr">
         <is>
-          <t>M7 · C4</t>
+          <t>M5 · C2</t>
         </is>
       </c>
       <c r="J27" s="42" t="inlineStr">
         <is>
-          <t>SÍ — llegó la versión original sin respaldos (10 páginas, 300 KB) el 12/10/2026 y se archivó como CV_Canto-Rondon_Styp-Bill-Roy.pdf. La versión armada por la coordinación ya no hace falta</t>
+          <t>SÍ — resumen curricular armado por la coordinación y aprobado (13/10/2026); archivado como CV_de-Cangas-Moran_Ramon.pdf</t>
         </is>
       </c>
       <c r="K27" s="42" t="n"/>
       <c r="L27" s="42" t="inlineStr">
         <is>
-          <t>PENDIENTE — debe declarar: (1) consultor externo vigente de MEDDI Hub, empresa en la que la Dra. Omidres es CMO LATAM; (2) miembro vocal y fundador de la OITT, que preside la Dra. Omidres. Sin vínculo con Omisalud (confirmado por la Dra. Omidres el 12/10/2026)</t>
+          <t>PENDIENTE — sin conflicto, según la Dra. Omidres (13/10/2026); no lo exige la Universidad</t>
         </is>
       </c>
       <c r="M27" s="42" t="inlineStr">
         <is>
-          <t>03/12/2026</t>
+          <t>Jueves 19 de noviembre de 2026</t>
         </is>
       </c>
       <c r="N27" s="65" t="inlineStr">
-        <is>
-          <t>CONFIRMADO — aceptó el 12/10/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="54" t="n">
-        <v>25</v>
-      </c>
-      <c r="B28" s="52" t="inlineStr">
-        <is>
-          <t>Dr. Ramón de Cangas Morán</t>
-        </is>
-      </c>
-      <c r="C28" s="53" t="inlineStr">
-        <is>
-          <t>Dietista-nutricionista · Biología · Doctor en Biología Funcional y Molecular</t>
-        </is>
-      </c>
-      <c r="D28" s="53" t="inlineStr">
-        <is>
-          <t>Clínicas Nutrigroup · Fundación Alimenta Tu Salud — Oviedo, España</t>
-        </is>
-      </c>
-      <c r="E28" s="41" t="n"/>
-      <c r="F28" s="41" t="n"/>
-      <c r="G28" s="41" t="n"/>
-      <c r="H28" s="41" t="n"/>
-      <c r="I28" s="54" t="inlineStr">
-        <is>
-          <t>M5 · C2</t>
-        </is>
-      </c>
-      <c r="J28" s="42" t="inlineStr">
-        <is>
-          <t>SÍ — resumen curricular armado por la coordinación y aprobado (13/10/2026); archivado como CV_de-Cangas-Moran_Ramon.pdf</t>
-        </is>
-      </c>
-      <c r="K28" s="42" t="n"/>
-      <c r="L28" s="42" t="inlineStr">
-        <is>
-          <t>PENDIENTE — sin conflicto, según la Dra. Omidres (13/10/2026); no lo exige la Universidad</t>
-        </is>
-      </c>
-      <c r="M28" s="42" t="inlineStr">
-        <is>
-          <t>Jueves 19 de noviembre de 2026</t>
-        </is>
-      </c>
-      <c r="N28" s="65" t="inlineStr">
         <is>
           <t>CONFIRMADO — aceptó el 13/10/2026</t>
         </is>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -2606,7 +2606,11 @@
           <t>Omni Hospital e Interhospital · Guayaquil, Ecuador</t>
         </is>
       </c>
-      <c r="E8" s="41" t="n"/>
+      <c r="E8" s="41" t="inlineStr">
+        <is>
+          <t>josefapalacio27@gmail.com</t>
+        </is>
+      </c>
       <c r="F8" s="53" t="inlineStr">
         <is>
           <t>+593 96 816 1654</t>
@@ -2625,15 +2629,19 @@
       </c>
       <c r="J8" s="54" t="inlineStr">
         <is>
+          <t>SÍ — versión 2026 recibida el 13/10/2026 (agrega el podcast En Rango); archivada</t>
+        </is>
+      </c>
+      <c r="K8" s="54" t="inlineStr">
+        <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="K8" s="54" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
-      <c r="L8" s="42" t="n"/>
+      <c r="L8" s="42" t="inlineStr">
+        <is>
+          <t>POR CONFIRMAR — llenada el 13/10/2026 (declara NO tener conflicto) pero SIN FIRMA ni fecha; falta firmarla</t>
+        </is>
+      </c>
       <c r="M8" s="42" t="n"/>
       <c r="N8" s="43" t="inlineStr">
         <is>

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -3389,7 +3389,7 @@
       </c>
       <c r="D21" s="54" t="inlineStr">
         <is>
-          <t>Universidad de Cuenca — Cuenca, Ecuador</t>
+          <t>Universidad de Cuenca · Universidad Católica de Cuenca · Casa de la Diabetes — Cuenca, Ecuador</t>
         </is>
       </c>
       <c r="E21" s="54" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="J21" s="54" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>SÍ — llegó por el formulario el 06/10/2026 (Drive: «CV_Gabriela_Molina julio 2026 - Gabriela Molina.docx»); contenido verificado el 13/10/2026. FALTA copiarla a expediente/hojas-de-vida/</t>
         </is>
       </c>
       <c r="K21" s="54" t="inlineStr">

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -3415,7 +3415,7 @@
       </c>
       <c r="J21" s="54" t="inlineStr">
         <is>
-          <t>SÍ — llegó por el formulario el 06/10/2026 (Drive: «CV_Gabriela_Molina julio 2026 - Gabriela Molina.docx»); contenido verificado el 13/10/2026. FALTA copiarla a expediente/hojas-de-vida/</t>
+          <t>SÍ — llegó por el formulario el 06/10/2026; archivada el 13/10/2026 como CV_Molina-Ochoa_Gabriela-Estefania.docx</t>
         </is>
       </c>
       <c r="K21" s="54" t="inlineStr">

--- a/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
+++ b/curso-obesidad-seda/SEDA_Matriz_Ponentes_Curso_Obesidad.xlsx
@@ -2624,7 +2624,11 @@
           <t>Omni Hospital e Interhospital · Guayaquil, Ecuador</t>
         </is>
       </c>
-      <c r="E9" s="41" t="n"/>
+      <c r="E9" s="54" t="inlineStr">
+        <is>
+          <t>josefapalacio27@gmail.com</t>
+        </is>
+      </c>
       <c r="F9" s="53" t="inlineStr">
         <is>
           <t>+593 96 816 1654</t>
@@ -2651,7 +2655,11 @@
           <t>SÍ</t>
         </is>
       </c>
-      <c r="L9" s="42" t="n"/>
+      <c r="L9" s="54" t="inlineStr">
+        <is>
+          <t>YA PEDIDA la firma el 13/10/2026. Envió la declaración completa pero sin firma ni fecha al pie.</t>
+        </is>
+      </c>
       <c r="M9" s="42" t="n"/>
       <c r="N9" s="43" t="inlineStr">
         <is>
@@ -3101,7 +3109,11 @@
           <t>M6 · C1</t>
         </is>
       </c>
-      <c r="J17" s="42" t="n"/>
+      <c r="J17" s="54" t="inlineStr">
+        <is>
+          <t>SÍ — enviada por la Dra. Ruilova el 12/10/2026; el archivo sigue en el correo, falta guardarlo en el expediente</t>
+        </is>
+      </c>
       <c r="K17" s="42" t="n"/>
       <c r="L17" s="42" t="n"/>
       <c r="M17" s="42" t="n"/>
@@ -3205,7 +3217,11 @@
           <t>M4 · C1</t>
         </is>
       </c>
-      <c r="J19" s="42" t="n"/>
+      <c r="J19" s="54" t="inlineStr">
+        <is>
+          <t>SÍ — enviada por la Dra. Ruilova el 12/10/2026; el archivo sigue en el correo, falta guardarlo en el expediente</t>
+        </is>
+      </c>
       <c r="K19" s="42" t="n"/>
       <c r="L19" s="42" t="n"/>
       <c r="M19" s="42" t="inlineStr">
